--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Saudi_Pro_" displayName="AveragesTable_Saudi_Pro_" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>105</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="K2" t="n">
-        <v>7.25</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>63.25</v>
+        <v>56.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>13.75</v>
+        <v>13.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>61.25</v>
+        <v>54.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>14.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>14.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BR2" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BU2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.91</v>
+        <v>4.74</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.43</v>
+        <v>5.21</v>
       </c>
       <c r="CC2" t="n">
         <v>1.58</v>
@@ -1622,43 +1622,43 @@
         <v>1.66</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CI2" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL2" t="n">
         <v>2.11</v>
       </c>
-      <c r="CJ2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>2.09</v>
-      </c>
       <c r="CM2" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="CR2" t="n">
         <v>1.31</v>
@@ -1673,7 +1673,7 @@
         <v>1.63</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW2" t="n">
         <v>1.78</v>
@@ -1691,88 +1691,88 @@
         <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.5</v>
+        <v>88.56</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.12</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>52.5</v>
+        <v>49.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.88</v>
+        <v>10.56</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>6.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>55.5</v>
+        <v>52.56</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.38</v>
+        <v>13.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.25</v>
+        <v>8.56</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="EA2" t="n">
-        <v>14.25</v>
+        <v>14.89</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" t="n">
-        <v>70.25</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.75</v>
+        <v>41.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.75</v>
+        <v>11.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43</v>
+        <v>40.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.880000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.5</v>
+        <v>4.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.25</v>
+        <v>3.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW4" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY4" t="n">
         <v>2.6</v>
@@ -2416,70 +2416,70 @@
         <v>2.68</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.21</v>
+        <v>4.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.27</v>
+        <v>5.83</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.38</v>
+        <v>7.11</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.38</v>
+        <v>7.61</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.53</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="CT4" t="n">
         <v>3.26</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW4" t="n">
         <v>1.56</v>
@@ -2488,97 +2488,97 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.5</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="DB4" t="n">
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>78</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>17</v>
+      </c>
+      <c r="EB4" t="n">
         <v>1.53</v>
       </c>
-      <c r="DD4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>50</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>7</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>17.38</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>1.64</v>
-      </c>
       <c r="EC4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>51.25</v>
+        <v>66</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AK5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT5" t="n">
         <v>2</v>
       </c>
-      <c r="AL5" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AU5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.5</v>
+        <v>45.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.75</v>
+        <v>11.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.75</v>
+        <v>16.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY5" t="n">
         <v>3.02</v>
@@ -2819,55 +2819,55 @@
         <v>3.12</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.87</v>
+        <v>3.79</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.04</v>
+        <v>3.95</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.45</v>
+        <v>4.87</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.24</v>
+        <v>5.51</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK5" t="n">
         <v>1.34</v>
       </c>
-      <c r="CF5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.51</v>
-      </c>
       <c r="CL5" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DH5" t="n">
-        <v>62.62</v>
+        <v>69.56</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM5" t="n">
-        <v>24.75</v>
+        <v>30</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.88</v>
+        <v>7.22</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>44.62</v>
+        <v>46.44</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.619999999999999</v>
+        <v>11</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>16.75</v>
+        <v>17.33</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.75</v>
+        <v>58.2</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>25.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.25</v>
+        <v>13.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.75</v>
+        <v>43.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.25</v>
+        <v>10.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY6" t="n">
         <v>7.84</v>
@@ -3222,31 +3222,31 @@
         <v>7.04</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="CE6" t="n">
         <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.69</v>
@@ -3255,22 +3255,22 @@
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.33</v>
@@ -3285,106 +3285,106 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.29</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DH6" t="n">
-        <v>66.25</v>
+        <v>63.78</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DK6" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>30</v>
+        <v>29.89</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.5</v>
+        <v>14.11</v>
       </c>
       <c r="DQ6" t="n">
-        <v>9.619999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.12</v>
+        <v>46.33</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.25</v>
+        <v>10.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.25</v>
+        <v>3.89</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.25</v>
+        <v>18.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.9</v>
+        <v>1.01</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>128</v>
+        <v>124.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>83.25</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.75</v>
+        <v>10.6</v>
       </c>
       <c r="R7" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>65.25</v>
+        <v>65.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.25</v>
+        <v>17.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.25</v>
+        <v>20.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.62</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BV7" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.91</v>
+        <v>6.19</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.77</v>
+        <v>7.17</v>
       </c>
       <c r="CC7" t="n">
         <v>1.57</v>
@@ -3640,146 +3640,146 @@
         <v>1.19</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.03</v>
+        <v>4.19</v>
       </c>
       <c r="CH7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CJ7" t="n">
         <v>1.75</v>
       </c>
-      <c r="CI7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.77</v>
-      </c>
       <c r="CK7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CO7" t="n">
         <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
         <v>1.13</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.5</v>
+        <v>105.89</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>66.5</v>
+        <v>69.11</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.38</v>
+        <v>2.89</v>
       </c>
       <c r="DP7" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.880000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.25</v>
+        <v>60.22</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.25</v>
+        <v>16.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.5</v>
+        <v>17.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="8">
@@ -3789,61 +3789,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="n">
         <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="R8" t="n">
-        <v>8.75</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3855,28 +3855,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>47</v>
+        <v>45.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.25</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3960,70 +3960,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.04</v>
+        <v>3.79</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="CC8" t="n">
         <v>2.99</v>
@@ -4032,43 +4032,43 @@
         <v>3.03</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4110,79 +4110,79 @@
         <v>2.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>53.62</v>
+        <v>54.33</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.44</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>27</v>
+        <v>27.11</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.25</v>
+        <v>10.56</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.75</v>
+        <v>10.11</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.88</v>
+        <v>50.44</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>9</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.25</v>
+        <v>5.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.38</v>
+        <v>14.56</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="9">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -4204,49 +4204,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>65.75</v>
+        <v>70</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>31.5</v>
+        <v>37</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>11.75</v>
+        <v>12.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>61</v>
+        <v>61.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>12.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
         <v>0.5</v>
@@ -4363,70 +4363,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.94</v>
+        <v>2.61</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.31</v>
+        <v>4.56</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.54</v>
+        <v>4.77</v>
       </c>
       <c r="CC9" t="n">
         <v>1.66</v>
@@ -4438,28 +4438,28 @@
         <v>1.21</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CK9" t="n">
         <v>1.42</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CN9" t="n">
         <v>2.01</v>
@@ -4471,30 +4471,30 @@
         <v>1.44</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CR9" t="inlineStr"/>
       <c r="CS9" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CT9" t="inlineStr"/>
       <c r="CU9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY9" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DA9" t="n">
         <v>1.98</v>
@@ -4503,52 +4503,52 @@
         <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.88</v>
+        <v>83.33</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>43.25</v>
+        <v>45</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.62</v>
+        <v>12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.12</v>
+        <v>10.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>61.88</v>
+        <v>62.22</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.12</v>
+        <v>15.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="10">
@@ -4994,94 +4994,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="F11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="G11" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>78</v>
+        <v>72.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>40.33</v>
+        <v>41.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.33</v>
+        <v>15.5</v>
       </c>
       <c r="R11" t="n">
-        <v>8.33</v>
+        <v>8.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46</v>
+        <v>49.5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.67</v>
+        <v>17.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5165,34 +5165,34 @@
         <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BH11" t="n">
         <v>9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BJ11" t="n">
         <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="BQ11" t="n">
         <v>4</v>
@@ -5201,34 +5201,34 @@
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT11" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU11" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.63</v>
+        <v>4.49</v>
       </c>
       <c r="CC11" t="n">
         <v>6.02</v>
@@ -5240,40 +5240,40 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK11" t="n">
         <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CM11" t="n">
         <v>2.3</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5288,106 +5288,106 @@
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
         <v>2.02</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA11" t="n">
         <v>1.84</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DH11" t="n">
-        <v>79.5</v>
+        <v>76.89</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.12</v>
+        <v>41.56</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.12</v>
+        <v>11.56</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.87</v>
+        <v>14.44</v>
       </c>
       <c r="DR11" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>8.619999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.37</v>
+        <v>3.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5490,136 +5490,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP12" t="n">
         <v>2</v>
       </c>
-      <c r="AI12" t="n">
-        <v>76.75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AQ12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC12" t="n">
         <v>3</v>
       </c>
-      <c r="AL12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>39</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="BD12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG12" t="n">
         <v>3</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BH12" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>1</v>
       </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>5.44</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BR12" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
         <v>8.82</v>
@@ -5628,70 +5628,70 @@
         <v>8.66</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.59</v>
+        <v>4.48</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.2</v>
+        <v>5.03</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CI12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW12" t="n">
         <v>1.78</v>
@@ -5709,55 +5709,55 @@
         <v>1.8</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG12" t="n">
         <v>1.67</v>
       </c>
-      <c r="DD12" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="DH12" t="n">
-        <v>58.38</v>
+        <v>57.67</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>27.62</v>
+        <v>29.11</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.38</v>
+        <v>13.78</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.12</v>
+        <v>7.67</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.75</v>
+        <v>46</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.88</v>
+        <v>6.11</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="EB12" t="n">
         <v>0.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6199,13 +6199,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
         <v>0.5</v>
@@ -6289,52 +6289,52 @@
         <v>0.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>2</v>
       </c>
-      <c r="AI14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AL14" t="n">
-        <v>4.75</v>
+        <v>5.8</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.5</v>
+        <v>55.8</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.75</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6346,73 +6346,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>52.5</v>
+        <v>56.2</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.25</v>
+        <v>11.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT14" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6421,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY14" t="n">
         <v>1.44</v>
@@ -6430,55 +6430,55 @@
         <v>1.45</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.11</v>
+        <v>4.03</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.54</v>
+        <v>4.41</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.43</v>
+        <v>3.34</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6493,10 +6493,10 @@
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6511,88 +6511,88 @@
         <v>1.92</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.12</v>
+        <v>98.78</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM14" t="n">
-        <v>53</v>
+        <v>59.22</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="DP14" t="n">
-        <v>12</v>
+        <v>11.56</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>54.88</v>
+        <v>56.67</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.75</v>
+        <v>12.89</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="15">
@@ -6602,13 +6602,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0.25</v>
@@ -6695,136 +6695,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>68.5</v>
+        <v>69.8</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>32.5</v>
+        <v>35.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP15" t="n">
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.75</v>
+        <v>10.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.75</v>
+        <v>9.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>38.25</v>
+        <v>37.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BH15" t="n">
-        <v>12.12</v>
+        <v>11.78</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY15" t="n">
         <v>2.87</v>
@@ -6833,28 +6833,28 @@
         <v>2.74</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.32</v>
+        <v>6.36</v>
       </c>
       <c r="CC15" t="n">
-        <v>12.23</v>
+        <v>11.58</v>
       </c>
       <c r="CD15" t="n">
-        <v>15.8</v>
+        <v>14.9</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CG15" t="n">
         <v>3.5</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CI15" t="n">
         <v>1.91</v>
@@ -6863,139 +6863,139 @@
         <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM15" t="n">
         <v>2.34</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="CR15" t="n">
         <v>1.33</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CT15" t="n">
         <v>3.16</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV15" t="n">
         <v>1.99</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DC15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DG15" t="n">
         <v>1.67</v>
       </c>
-      <c r="DD15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="DE15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DG15" t="n">
-        <v>1.62</v>
-      </c>
       <c r="DH15" t="n">
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DK15" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DM15" t="n">
-        <v>24.75</v>
+        <v>27.33</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP15" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37.5</v>
+        <v>37.22</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.62</v>
+        <v>15.89</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="16">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>4</v>
@@ -7823,49 +7823,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>90.75</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>37.25</v>
+        <v>45.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.25</v>
+        <v>13.2</v>
       </c>
       <c r="R18" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7877,28 +7877,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.75</v>
+        <v>54.2</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.25</v>
+        <v>11.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>26.25</v>
+        <v>25.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7982,70 +7982,70 @@
         <v>1.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>7.88</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="BP18" t="n">
-        <v>3.12</v>
+        <v>4.22</v>
       </c>
       <c r="BQ18" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BS18" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BY18" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC18" t="n">
         <v>4.15</v>
@@ -8057,58 +8057,58 @@
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX18" t="n">
         <v>1.75</v>
@@ -8126,85 +8126,85 @@
         <v>1.27</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>60.75</v>
+        <v>62.33</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.88</v>
+        <v>4.89</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DM18" t="n">
-        <v>28</v>
+        <v>33.44</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.62</v>
+        <v>2.56</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.38</v>
+        <v>12.89</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.38</v>
+        <v>12.89</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.5</v>
+        <v>52.44</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DX18" t="n">
-        <v>10</v>
+        <v>10.56</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.62</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.88</v>
+        <v>21.78</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>41.25</v>
+        <v>47.2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>7.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q3" t="n">
         <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.25</v>
+        <v>17.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK3" t="n">
         <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.29</v>
+        <v>4.18</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.96</v>
+        <v>4.77</v>
       </c>
       <c r="CC3" t="n">
         <v>8.279999999999999</v>
@@ -2025,124 +2025,124 @@
         <v>9.92</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI3" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="CV3" t="n">
         <v>1.89</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX3" t="n">
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DH3" t="n">
-        <v>49.25</v>
+        <v>51.67</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>22.62</v>
+        <v>24.22</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.75</v>
+        <v>10.11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.62</v>
+        <v>11.44</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.25</v>
+        <v>40.56</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>14.88</v>
+        <v>15.78</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="4">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -4681,139 +4681,139 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="AO10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BF10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.12</v>
+        <v>9.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BV10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY10" t="n">
         <v>2.5</v>
@@ -4822,28 +4822,28 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.72</v>
+        <v>4.26</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>4.39</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.38</v>
+        <v>5.1</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.32</v>
+        <v>5.48</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="CI10" t="n">
         <v>2.19</v>
@@ -4858,19 +4858,19 @@
         <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4885,106 +4885,106 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>57.25</v>
+        <v>56.89</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.62</v>
+        <v>28.67</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.75</v>
+        <v>10.44</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.62</v>
+        <v>12.89</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.38</v>
+        <v>48</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.38</v>
+        <v>15.22</v>
       </c>
       <c r="EB10" t="n">
         <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="11">
@@ -5550,10 +5550,10 @@
         <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
@@ -5562,7 +5562,7 @@
         <v>13.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF12" t="n">
         <v>2.4</v>
@@ -5775,10 +5775,10 @@
         <v>0.33</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.11</v>
+        <v>6.22</v>
       </c>
       <c r="DZ12" t="n">
         <v>2.56</v>
@@ -5787,7 +5787,7 @@
         <v>14.78</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5800,94 +5800,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="H13" t="n">
-        <v>117.25</v>
+        <v>116.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K13" t="n">
-        <v>10.75</v>
+        <v>9.4</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>77.25</v>
+        <v>71.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>64</v>
+        <v>62.2</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.75</v>
+        <v>11.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.75</v>
+        <v>14.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0.5</v>
@@ -5971,37 +5971,37 @@
         <v>1.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="BH13" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6010,19 +6010,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BV13" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BW13" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
         <v>1.13</v>
@@ -6031,7 +6031,7 @@
         <v>1.11</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.64</v>
+        <v>6.85</v>
       </c>
       <c r="CB13" t="n">
         <v>8.93</v>
@@ -6046,40 +6046,40 @@
         <v>1.16</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.67</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL13" t="n">
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6090,7 +6090,7 @@
         <v>2.03</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW13" t="n">
         <v>1.75</v>
@@ -6099,13 +6099,13 @@
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.11</v>
@@ -6114,82 +6114,82 @@
         <v>1.25</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DG13" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.88</v>
+        <v>108.44</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>8.380000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>68.62</v>
+        <v>66.22</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.380000000000001</v>
+        <v>10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="DR13" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.25</v>
+        <v>59.67</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.75</v>
+        <v>12.56</v>
       </c>
       <c r="DZ13" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.62</v>
+        <v>15.44</v>
       </c>
       <c r="EB13" t="n">
         <v>2.42</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="14">
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7098,49 +7098,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>69.33</v>
+        <v>79.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>36.67</v>
+        <v>38.25</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP16" t="n">
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.67</v>
+        <v>9.75</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.33</v>
+        <v>8.25</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7152,25 +7152,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>38</v>
+        <v>42.75</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.33</v>
+        <v>17.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="BF16" t="n">
         <v>2</v>
@@ -7179,55 +7179,55 @@
         <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.5</v>
+        <v>9.33</v>
       </c>
       <c r="BI16" t="n">
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>1.66</v>
@@ -7236,34 +7236,34 @@
         <v>1.75</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.57</v>
+        <v>4.69</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.28</v>
+        <v>4.5</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CK16" t="n">
         <v>1.5</v>
@@ -7272,133 +7272,133 @@
         <v>1.92</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CZ16" t="n">
         <v>2.39</v>
       </c>
-      <c r="CT16" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>2.41</v>
-      </c>
       <c r="DA16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DH16" t="n">
-        <v>63</v>
+        <v>68.33</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DK16" t="n">
         <v>5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DM16" t="n">
-        <v>33.25</v>
+        <v>34.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.25</v>
+        <v>6.67</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>47.12</v>
+        <v>48.22</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.25</v>
+        <v>12.22</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.62</v>
+        <v>18.78</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="17">
@@ -7408,94 +7408,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>66</v>
+        <v>61.8</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>32.25</v>
+        <v>33.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>46.75</v>
+        <v>47.2</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.75</v>
+        <v>14.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7579,70 +7579,70 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT17" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BV17" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BW17" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.69</v>
+        <v>4.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="CC17" t="n">
         <v>2.55</v>
@@ -7657,55 +7657,55 @@
         <v>2.62</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CH17" t="n">
         <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
         <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CR17" t="n">
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
         <v>1.58</v>
@@ -7726,82 +7726,82 @@
         <v>1.89</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="DG17" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DH17" t="n">
-        <v>62.88</v>
+        <v>60.89</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DK17" t="n">
-        <v>2.88</v>
+        <v>3.44</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="DM17" t="n">
-        <v>29</v>
+        <v>29.89</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.62</v>
+        <v>12.44</v>
       </c>
       <c r="DQ17" t="n">
-        <v>9.880000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.38</v>
+        <v>48.44</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.88</v>
+        <v>11.44</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.62</v>
+        <v>12.67</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="18">
@@ -8214,13 +8214,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8304,139 +8304,139 @@
         <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>62.25</v>
+        <v>60.8</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN19" t="n">
-        <v>25.25</v>
+        <v>26.4</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.25</v>
+        <v>12.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.5</v>
+        <v>53.8</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.25</v>
+        <v>12.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.25</v>
+        <v>8.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT19" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BV19" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BY19" t="n">
         <v>3.47</v>
@@ -8445,43 +8445,43 @@
         <v>3.63</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN19" t="n">
         <v>1.84</v>
@@ -8490,28 +8490,28 @@
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CT19" t="n">
         <v>3.16</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX19" t="n">
         <v>1.58</v>
@@ -8526,88 +8526,88 @@
         <v>1.86</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DH19" t="n">
-        <v>60.75</v>
+        <v>60.11</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM19" t="n">
-        <v>27.62</v>
+        <v>28</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DP19" t="n">
-        <v>12</v>
+        <v>12.44</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.62</v>
+        <v>13.22</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53</v>
+        <v>52.78</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.38</v>
+        <v>12.67</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="EA19" t="n">
-        <v>15.5</v>
+        <v>16.11</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
@@ -2600,49 +2600,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H5" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>28.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>10.25</v>
+        <v>10.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.5</v>
+        <v>12.2</v>
       </c>
       <c r="R5" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>47.75</v>
+        <v>49.2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.75</v>
+        <v>19.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BU5" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CC5" t="n">
         <v>4.87</v>
@@ -2831,124 +2831,124 @@
         <v>5.51</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
         <v>2.72</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CL5" t="n">
         <v>1.8</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CQ5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CS5" t="n">
         <v>2.79</v>
       </c>
-      <c r="CR5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.69</v>
-      </c>
       <c r="CT5" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CX5" t="n">
         <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>69.56</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM5" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.22</v>
+        <v>7.2</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.44</v>
+        <v>47.3</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.109999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.33</v>
+        <v>17.9</v>
       </c>
       <c r="EB5" t="n">
         <v>1.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>58.2</v>
+        <v>61</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN6" t="n">
-        <v>25.8</v>
+        <v>28.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AP6" t="n">
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA6" t="n">
         <v>10</v>
       </c>
-      <c r="AS6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV6" t="n">
+      <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.44</v>
-      </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY6" t="n">
         <v>7.84</v>
@@ -3222,169 +3222,169 @@
         <v>7.04</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.6</v>
+        <v>4.47</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CK6" t="n">
         <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="CU6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CX6" t="n">
         <v>1.59</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
         <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>63.78</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DM6" t="n">
-        <v>29.89</v>
+        <v>31.1</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DP6" t="n">
-        <v>14.11</v>
+        <v>13.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.33</v>
+        <v>46.2</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.67</v>
+        <v>18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0.4</v>
@@ -3882,136 +3882,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>47.25</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>27.5</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.75</v>
+        <v>11.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>10.75</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56.75</v>
+        <v>58.6</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.25</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.85</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.67</v>
+        <v>9.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT8" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BU8" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BY8" t="n">
         <v>3.79</v>
@@ -4020,28 +4020,28 @@
         <v>3.79</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.03</v>
+        <v>2.85</v>
       </c>
       <c r="CE8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CH8" t="n">
         <v>1.16</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
         <v>2.06</v>
@@ -4050,25 +4050,25 @@
         <v>1.74</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4110,79 +4110,79 @@
         <v>2.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DH8" t="n">
-        <v>54.33</v>
+        <v>60</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>27.11</v>
+        <v>32.4</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.56</v>
+        <v>10.1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.56</v>
+        <v>10.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>10.11</v>
+        <v>9.5</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.44</v>
+        <v>52</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>8.779999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.56</v>
+        <v>15.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5490,136 +5490,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.6</v>
+        <v>13.17</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>13.8</v>
+        <v>14.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
         <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.56</v>
+        <v>11.2</v>
       </c>
       <c r="BI12" t="n">
         <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BM12" t="n">
         <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
         <v>8.82</v>
@@ -5628,61 +5628,61 @@
         <v>8.66</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.48</v>
+        <v>4.63</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.03</v>
+        <v>5.14</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.13</v>
+        <v>5.11</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.33</v>
+        <v>5.2</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
         <v>3.33</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN12" t="n">
         <v>1.79</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CT12" t="n">
         <v>3.06</v>
@@ -5691,79 +5691,79 @@
         <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DH12" t="n">
-        <v>57.67</v>
+        <v>58.3</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
-        <v>29.11</v>
+        <v>29.9</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.78</v>
+        <v>13.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.67</v>
+        <v>7.8</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
@@ -5772,25 +5772,25 @@
         <v>46</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>14.78</v>
+        <v>15.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -6602,61 +6602,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="n">
-        <v>36.5</v>
+        <v>41.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="M15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>15.25</v>
+        <v>15.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6668,28 +6668,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>36.75</v>
+        <v>36.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.25</v>
+        <v>16.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6773,70 +6773,70 @@
         <v>1.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.78</v>
+        <v>11</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.11</v>
+        <v>4.7</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT15" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BY15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>2.87</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>2.74</v>
-      </c>
       <c r="CA15" t="n">
-        <v>5.5</v>
+        <v>5.28</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.36</v>
+        <v>6.08</v>
       </c>
       <c r="CC15" t="n">
         <v>11.58</v>
@@ -6845,43 +6845,43 @@
         <v>14.9</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL15" t="n">
         <v>1.8</v>
       </c>
-      <c r="CK15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>2.01</v>
-      </c>
       <c r="CM15" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="CR15" t="n">
         <v>1.33</v>
@@ -6923,79 +6923,79 @@
         <v>2.57</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH15" t="n">
-        <v>55</v>
+        <v>55.5</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.33</v>
+        <v>27.8</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.89</v>
+        <v>13.1</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>37.22</v>
+        <v>36.9</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.89</v>
+        <v>15.4</v>
       </c>
       <c r="EB15" t="n">
         <v>0.84</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
@@ -8226,49 +8226,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>59.25</v>
+        <v>60.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>31.8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8280,28 +8280,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>14.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AF19" t="n">
         <v>0.4</v>
@@ -8388,67 +8388,67 @@
         <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="BI19" t="n">
         <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.47</v>
+        <v>3.06</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.63</v>
+        <v>3.15</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.97</v>
+        <v>4.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.23</v>
+        <v>4.42</v>
       </c>
       <c r="CC19" t="n">
         <v>3.06</v>
@@ -8457,28 +8457,28 @@
         <v>3.12</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM19" t="n">
         <v>2.33</v>
@@ -8487,127 +8487,127 @@
         <v>1.84</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CT19" t="n">
         <v>3.16</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>60.11</v>
+        <v>60.7</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>28</v>
+        <v>29.1</v>
       </c>
       <c r="DN19" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.44</v>
+        <v>12.4</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.22</v>
+        <v>12.8</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.78</v>
+        <v>52.9</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.67</v>
+        <v>12.6</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.11</v>
+        <v>16.7</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1472,46 +1472,46 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>76</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>41.75</v>
+        <v>51.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.75</v>
+        <v>51.2</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.25</v>
+        <v>13.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>15</v>
+        <v>18.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS2" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>1.79</v>
@@ -1610,55 +1610,55 @@
         <v>1.75</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="CC2" t="n">
         <v>1.58</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CR2" t="n">
         <v>1.31</v>
@@ -1700,79 +1700,79 @@
         <v>2.51</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="DH2" t="n">
-        <v>88.56</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.44</v>
+        <v>5.8</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.78</v>
+        <v>53.8</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.56</v>
+        <v>10.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.56</v>
+        <v>53</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.56</v>
+        <v>13.9</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="EA2" t="n">
-        <v>14.89</v>
+        <v>16.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1878,46 +1878,46 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>57.25</v>
+        <v>54</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.25</v>
+        <v>22.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.75</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.25</v>
+        <v>13.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
         <v>3</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="BI3" t="n">
         <v>3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.89</v>
+        <v>4.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>3.17</v>
@@ -2013,94 +2013,94 @@
         <v>3.27</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.18</v>
+        <v>4.64</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.77</v>
+        <v>5.6</v>
       </c>
       <c r="CC3" t="n">
-        <v>8.279999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="CD3" t="n">
-        <v>9.92</v>
+        <v>11.93</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="CT3" t="n">
         <v>3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX3" t="n">
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2109,40 +2109,40 @@
         <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DH3" t="n">
-        <v>51.67</v>
+        <v>50.6</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="DM3" t="n">
-        <v>24.22</v>
+        <v>23.6</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.44</v>
+        <v>11.6</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.67</v>
+        <v>9.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.56</v>
+        <v>40</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.220000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.78</v>
+        <v>15.6</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -2197,34 +2197,34 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>91.25</v>
+        <v>88.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>58.25</v>
+        <v>49.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
         <v>12</v>
@@ -2233,46 +2233,46 @@
         <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>47.5</v>
+        <v>46.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.75</v>
+        <v>13.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.25</v>
+        <v>16.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,70 +2356,70 @@
         <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV4" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BX4" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.68</v>
+        <v>3.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="CC4" t="n">
         <v>7.11</v>
@@ -2428,37 +2428,37 @@
         <v>7.61</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.91</v>
+        <v>3.52</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="CP4" t="n">
         <v>1.5</v>
@@ -2506,79 +2506,79 @@
         <v>2.25</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="EB4" t="n">
         <v>1.44</v>
       </c>
-      <c r="DG4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>78</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>48.89</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>11.78</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>43.78</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>5</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>17</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="EC4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>124.2</v>
+        <v>120</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>84.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="P7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.6</v>
+        <v>10.83</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>65.8</v>
+        <v>63.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.2</v>
+        <v>17.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.8</v>
+        <v>19.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>1.75</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BH7" t="n">
         <v>10</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BX7" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>1.24</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="CA7" t="n">
-        <v>6.19</v>
+        <v>6.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.17</v>
+        <v>7.24</v>
       </c>
       <c r="CC7" t="n">
         <v>1.57</v>
@@ -3637,22 +3637,22 @@
         <v>1.64</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CK7" t="n">
         <v>1.4</v>
@@ -3661,33 +3661,33 @@
         <v>1.79</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
@@ -3698,88 +3698,88 @@
         <v>2.22</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.89</v>
+        <v>105.2</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>69.11</v>
+        <v>68.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.89</v>
+        <v>6.1</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.22</v>
+        <v>59.2</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.33</v>
+        <v>16.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.44</v>
+        <v>7.8</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.22</v>
+        <v>16.7</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -4204,49 +4204,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>70</v>
+        <v>79.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6.17</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>37</v>
+        <v>46.67</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="P9" t="n">
-        <v>12.4</v>
+        <v>12.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>61.8</v>
+        <v>62.83</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>12.6</v>
+        <v>13.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.4</v>
+        <v>18.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0.5</v>
@@ -4363,70 +4363,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.779999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV9" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BW9" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.77</v>
+        <v>4.8</v>
       </c>
       <c r="CC9" t="n">
         <v>1.66</v>
@@ -4435,57 +4435,61 @@
         <v>1.68</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO9" t="n">
         <v>1.12</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CR9" t="inlineStr"/>
+        <v>2.17</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.31</v>
+      </c>
       <c r="CS9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CT9" t="inlineStr"/>
+        <v>2.19</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>3.31</v>
+      </c>
       <c r="CU9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="CX9" t="n">
         <v>1.51</v>
@@ -4500,55 +4504,55 @@
         <v>1.98</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.33</v>
+        <v>87.7</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.67</v>
+        <v>6.3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="DP9" t="n">
         <v>12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.22</v>
+        <v>62.8</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.11</v>
+        <v>13.5</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.22</v>
+        <v>5.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.67</v>
+        <v>16.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4591,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -4681,139 +4685,139 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>52.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="AL10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.11</v>
-      </c>
       <c r="BH10" t="n">
-        <v>9.67</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
         <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BU10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BV10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BY10" t="n">
         <v>2.5</v>
@@ -4822,28 +4826,28 @@
         <v>2.44</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.26</v>
+        <v>4.58</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.39</v>
+        <v>4.74</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.1</v>
+        <v>5.92</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.48</v>
+        <v>6.34</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CI10" t="n">
         <v>2.19</v>
@@ -4852,139 +4856,139 @@
         <v>1.61</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="CT10" t="n">
         <v>3.1</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DH10" t="n">
-        <v>56.89</v>
+        <v>58.8</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>28.67</v>
+        <v>29.6</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.44</v>
+        <v>10.6</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.22</v>
+        <v>14.9</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -4994,94 +4998,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>72.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>41.5</v>
+        <v>45.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="R11" t="n">
-        <v>8.75</v>
+        <v>7.4</v>
       </c>
       <c r="S11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.75</v>
+        <v>18.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5165,70 +5169,70 @@
         <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="BH11" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT11" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.49</v>
+        <v>4.38</v>
       </c>
       <c r="CC11" t="n">
         <v>6.02</v>
@@ -5237,16 +5241,16 @@
         <v>6.8</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CI11" t="n">
         <v>2.11</v>
@@ -5258,136 +5262,136 @@
         <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO11" t="n">
         <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="DH11" t="n">
-        <v>76.89</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.56</v>
+        <v>4.4</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.56</v>
+        <v>43.4</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.56</v>
+        <v>11.3</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14.44</v>
+        <v>14</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.109999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DY11" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="EA11" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -5544,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.5</v>
+        <v>49.33</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.17</v>
@@ -5769,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="DW12" t="n">
         <v>0.3</v>
@@ -5800,94 +5804,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="H13" t="n">
-        <v>116.4</v>
+        <v>110.67</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="K13" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M13" t="n">
-        <v>71.2</v>
+        <v>69.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="R13" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>62.2</v>
+        <v>62.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>20.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.6</v>
+        <v>11.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.6</v>
+        <v>15.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>0.5</v>
@@ -5971,37 +5975,37 @@
         <v>1.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.56</v>
+        <v>10.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.78</v>
+        <v>6.1</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6010,31 +6014,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU13" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BW13" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BZ13" t="n">
         <v>1.11</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.85</v>
+        <v>7.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>8.93</v>
+        <v>9.34</v>
       </c>
       <c r="CC13" t="n">
         <v>1.33</v>
@@ -6046,31 +6050,31 @@
         <v>1.16</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.55</v>
+        <v>4.64</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="CO13" t="n">
         <v>1.06</v>
@@ -6079,18 +6083,18 @@
         <v>1.29</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CW13" t="n">
         <v>1.75</v>
@@ -6099,97 +6103,97 @@
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DB13" t="n">
         <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DG13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.44</v>
+        <v>105.8</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DM13" t="n">
-        <v>66.22</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="DR13" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>59.67</v>
+        <v>60.2</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>21.22</v>
+        <v>20.6</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="DZ13" t="n">
-        <v>8.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.44</v>
+        <v>16.1</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="14">
@@ -6199,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>88.25</v>
+        <v>97</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>7.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M14" t="n">
-        <v>63.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="R14" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>57.25</v>
+        <v>59.8</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.25</v>
+        <v>14.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.75</v>
+        <v>19.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6370,49 +6374,49 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.11</v>
+        <v>10.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6421,19 +6425,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.41</v>
+        <v>4.58</v>
       </c>
       <c r="CC14" t="n">
         <v>2.76</v>
@@ -6442,43 +6446,43 @@
         <v>2.9</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.34</v>
+        <v>3.01</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6520,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.78</v>
+        <v>102.1</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.67</v>
+        <v>7.8</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.22</v>
+        <v>63.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.56</v>
+        <v>11.8</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.33</v>
+        <v>6.8</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>56.67</v>
+        <v>58</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.89</v>
+        <v>13.1</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.78</v>
+        <v>16.6</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="15">
@@ -7005,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7098,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.75</v>
+        <v>78.2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.25</v>
+        <v>37.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.75</v>
+        <v>10.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7152,25 +7156,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.75</v>
+        <v>40.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.25</v>
+        <v>15.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="n">
         <v>2</v>
@@ -7179,55 +7183,55 @@
         <v>2</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI16" t="n">
         <v>2</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT16" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>1.66</v>
@@ -7236,16 +7240,16 @@
         <v>1.75</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.69</v>
+        <v>5.46</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="CE16" t="n">
         <v>1.28</v>
@@ -7254,67 +7258,67 @@
         <v>2.37</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CH16" t="n">
         <v>1.54</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CK16" t="n">
         <v>1.5</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN16" t="n">
         <v>1.92</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP16" t="n">
         <v>1.63</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CT16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB16" t="n">
         <v>1.23</v>
@@ -7323,82 +7327,82 @@
         <v>1.73</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="DH16" t="n">
-        <v>68.33</v>
+        <v>68.7</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.33</v>
+        <v>34.4</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.67</v>
+        <v>7.2</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>48.22</v>
+        <v>46.6</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.22</v>
+        <v>11.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.78</v>
+        <v>17.8</v>
       </c>
       <c r="EB16" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
@@ -7408,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0.2</v>
@@ -7501,49 +7505,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>59.75</v>
+        <v>62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
         <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>25.75</v>
+        <v>27.4</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14.75</v>
+        <v>13.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.25</v>
+        <v>10.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7555,82 +7559,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.5</v>
+        <v>12.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.33</v>
+        <v>9.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
         <v>1</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BV17" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BW17" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>3.56</v>
@@ -7639,28 +7643,28 @@
         <v>4.19</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="CD17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CF17" t="n">
         <v>2.64</v>
       </c>
-      <c r="CE17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>2.62</v>
-      </c>
       <c r="CG17" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI17" t="n">
         <v>2.03</v>
@@ -7672,13 +7676,13 @@
         <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO17" t="n">
         <v>1.25</v>
@@ -7693,115 +7697,115 @@
         <v>1.38</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
         <v>2.06</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="DH17" t="n">
-        <v>60.89</v>
+        <v>61.9</v>
       </c>
       <c r="DI17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DM17" t="n">
-        <v>29.89</v>
+        <v>30.3</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.44</v>
+        <v>12.2</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.56</v>
+        <v>10.4</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.56</v>
+        <v>8.4</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.44</v>
+        <v>48.1</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.44</v>
+        <v>11.1</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="18">
@@ -7811,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7901,139 +7905,139 @@
         <v>3.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>30.75</v>
+        <v>35.2</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.75</v>
+        <v>18.2</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.75</v>
+        <v>11.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.75</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>50.25</v>
+        <v>46.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.75</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.109999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.22</v>
+        <v>4.6</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT18" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU18" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BY18" t="n">
         <v>2.77</v>
@@ -8042,55 +8046,55 @@
         <v>3.11</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.15</v>
+        <v>5.52</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.35</v>
+        <v>5.59</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="CI18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CL18" t="n">
         <v>2</v>
       </c>
-      <c r="CJ18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>2.22</v>
-      </c>
       <c r="CM18" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8132,79 +8136,79 @@
         <v>3.1</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DH18" t="n">
-        <v>62.33</v>
+        <v>61.4</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DM18" t="n">
-        <v>33.44</v>
+        <v>31.7</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.89</v>
+        <v>12.3</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.56</v>
+        <v>10.2</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>52.44</v>
+        <v>50.2</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.56</v>
+        <v>10.1</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.109999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.78</v>
+        <v>21</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -8280,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="Y19" t="n">
         <v>0.2</v>
@@ -8586,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="DW19" t="n">
         <v>0.1</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1905,7 +1905,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AR3" t="n">
         <v>13.2</v>
@@ -2136,7 +2136,7 @@
         <v>1.4</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="DQ3" t="n">
         <v>11.6</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>67.40000000000001</v>
+        <v>58.17</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.4</v>
+        <v>43</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.6</v>
+        <v>12.17</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.8</v>
+        <v>10.17</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.6</v>
+        <v>17.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.2</v>
+        <v>10.18</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.7</v>
+        <v>4.18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT4" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW4" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BX4" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY4" t="n">
         <v>3.06</v>
@@ -2416,49 +2416,49 @@
         <v>3.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.71</v>
+        <v>5.54</v>
       </c>
       <c r="CC4" t="n">
-        <v>7.11</v>
+        <v>6.43</v>
       </c>
       <c r="CD4" t="n">
-        <v>7.61</v>
+        <v>6.91</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CG4" t="n">
         <v>3.52</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CP4" t="n">
         <v>1.5</v>
@@ -2479,7 +2479,7 @@
         <v>1.77</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CW4" t="n">
         <v>1.56</v>
@@ -2500,85 +2500,85 @@
         <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>78.09999999999999</v>
+        <v>72.09</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.4</v>
+        <v>45.91</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.8</v>
+        <v>12.09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.9</v>
+        <v>11.46</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.7</v>
+        <v>42.73</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.4</v>
+        <v>12.37</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.2</v>
+        <v>17.09</v>
       </c>
       <c r="EB4" t="n">
         <v>1.44</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>61</v>
+        <v>63.71</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>28.5</v>
+        <v>31.29</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP6" t="n">
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.83</v>
+        <v>8.57</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44</v>
+        <v>44.71</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA6" t="n">
         <v>10</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.33</v>
+        <v>18.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.5</v>
+        <v>8.91</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY6" t="n">
         <v>7.84</v>
@@ -3222,31 +3222,31 @@
         <v>7.04</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.72</v>
@@ -3267,124 +3267,124 @@
         <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="DH6" t="n">
-        <v>64.90000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM6" t="n">
-        <v>31.1</v>
+        <v>32.64</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.4</v>
+        <v>13.27</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.4</v>
+        <v>10.18</v>
       </c>
       <c r="DR6" t="n">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.2</v>
+        <v>46.45</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>18</v>
+        <v>17.82</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="7">
@@ -4264,19 +4264,19 @@
         <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="AA9" t="n">
         <v>8.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AC9" t="n">
         <v>18.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
         <v>1.67</v>
@@ -4570,19 +4570,19 @@
         <v>0.3</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="DY9" t="n">
         <v>8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="EA9" t="n">
         <v>16.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC9" t="n">
         <v>2</v>
@@ -4595,94 +4595,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="H10" t="n">
-        <v>68</v>
+        <v>58.2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>33.75</v>
+        <v>38.4</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.75</v>
+        <v>13.2</v>
       </c>
       <c r="R10" t="n">
-        <v>4.25</v>
+        <v>6.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51</v>
+        <v>54.2</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.25</v>
+        <v>12.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0.33</v>
@@ -4766,70 +4766,70 @@
         <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BU10" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BV10" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX10" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.74</v>
+        <v>4.66</v>
       </c>
       <c r="CC10" t="n">
         <v>5.92</v>
@@ -4841,40 +4841,40 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CG10" t="n">
         <v>3.58</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CK10" t="n">
         <v>1.46</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM10" t="n">
         <v>2.51</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4889,10 +4889,10 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
@@ -4907,88 +4907,88 @@
         <v>2.03</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
         <v>1.62</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="DH10" t="n">
-        <v>58.8</v>
+        <v>55.18</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DM10" t="n">
-        <v>29.6</v>
+        <v>32.09</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.6</v>
+        <v>10.27</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.2</v>
+        <v>49.91</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.1</v>
+        <v>8.18</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.7</v>
+        <v>4.27</v>
       </c>
       <c r="EA10" t="n">
-        <v>14.9</v>
+        <v>15.55</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="11">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.25</v>
@@ -5494,136 +5494,136 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>39</v>
+        <v>37.57</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.17</v>
+        <v>9.43</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.33</v>
+        <v>47.86</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT12" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU12" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BY12" t="n">
         <v>8.82</v>
@@ -5632,16 +5632,16 @@
         <v>8.66</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.11</v>
+        <v>5.27</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.2</v>
+        <v>5.41</v>
       </c>
       <c r="CE12" t="n">
         <v>1.28</v>
@@ -5656,22 +5656,22 @@
         <v>1.54</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CM12" t="n">
         <v>2.31</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
@@ -5680,121 +5680,121 @@
         <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DH12" t="n">
-        <v>58.3</v>
+        <v>61</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM12" t="n">
-        <v>29.9</v>
+        <v>29.82</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.5</v>
+        <v>13.45</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.8</v>
+        <v>8.27</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.9</v>
+        <v>45.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.9</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.2</v>
+        <v>15.36</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="13">
@@ -5846,7 +5846,7 @@
         <v>4.33</v>
       </c>
       <c r="P13" t="n">
-        <v>10.17</v>
+        <v>10.5</v>
       </c>
       <c r="Q13" t="n">
         <v>10.83</v>
@@ -6154,7 +6154,7 @@
         <v>4.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="DQ13" t="n">
         <v>11.7</v>
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AB14" t="n">
         <v>5.2</v>
@@ -6287,7 +6287,7 @@
         <v>19.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AE14" t="n">
         <v>0.6</v>
@@ -6581,10 +6581,10 @@
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.4</v>
@@ -6593,7 +6593,7 @@
         <v>16.6</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="EC14" t="n">
         <v>1.3</v>
@@ -6606,61 +6606,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="H15" t="n">
-        <v>41.2</v>
+        <v>51.83</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>24.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="P15" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="R15" t="n">
-        <v>7.4</v>
+        <v>6.83</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6672,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>36.2</v>
+        <v>38.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.199999999999999</v>
+        <v>10.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.8</v>
+        <v>18.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6777,70 @@
         <v>1.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BH15" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="BZ15" t="n">
         <v>2.87</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.28</v>
+        <v>5.08</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.08</v>
+        <v>5.82</v>
       </c>
       <c r="CC15" t="n">
         <v>11.58</v>
@@ -6849,58 +6849,58 @@
         <v>14.9</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CH15" t="n">
         <v>1.42</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.79</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="CP15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CU15" t="n">
         <v>1.65</v>
       </c>
-      <c r="CQ15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>1.68</v>
-      </c>
       <c r="CV15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
         <v>1.86</v>
@@ -6909,7 +6909,7 @@
         <v>1.61</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.32</v>
@@ -6918,88 +6918,88 @@
         <v>1.88</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="DH15" t="n">
-        <v>55.5</v>
+        <v>60</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM15" t="n">
-        <v>27.8</v>
+        <v>29.37</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.1</v>
+        <v>12.64</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>36.9</v>
+        <v>38.18</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX15" t="n">
-        <v>8.6</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.3</v>
+        <v>5.91</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.4</v>
+        <v>16.55</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="16">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="H17" t="n">
+        <v>71</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>5.17</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M17" t="n">
-        <v>33.2</v>
+        <v>38.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.2</v>
+        <v>49.5</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.8</v>
+        <v>7.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.4</v>
+        <v>14.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>1.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.6</v>
+        <v>9.73</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BM17" t="n">
         <v>1</v>
       </c>
-      <c r="BL17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BN17" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU17" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BV17" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BW17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.56</v>
+        <v>3.21</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.19</v>
+        <v>3.73</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.9</v>
+        <v>3.99</v>
       </c>
       <c r="CC17" t="n">
         <v>2.45</v>
@@ -7655,28 +7655,28 @@
         <v>2.54</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
         <v>1.54</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM17" t="n">
         <v>2.35</v>
@@ -7685,34 +7685,34 @@
         <v>1.87</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
@@ -7727,85 +7727,85 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>1</v>
+        <v>1.54</v>
       </c>
       <c r="DH17" t="n">
-        <v>61.9</v>
+        <v>66.91</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DM17" t="n">
-        <v>30.3</v>
+        <v>33.27</v>
       </c>
       <c r="DN17" t="n">
         <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.2</v>
+        <v>12.27</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.4</v>
+        <v>10.46</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.4</v>
+        <v>7.82</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.1</v>
+        <v>49.27</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.1</v>
+        <v>11.46</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.4</v>
+        <v>7.09</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.8</v>
+        <v>13.18</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>2.43</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="H2" t="n">
-        <v>98.59999999999999</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>3.57</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>5.14</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>56.2</v>
+        <v>46.43</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>13.8</v>
+        <v>14.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.6</v>
+        <v>10.14</v>
       </c>
       <c r="R2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.8</v>
+        <v>48.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.6</v>
+        <v>14.14</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="BK2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM2" t="n">
         <v>0.5</v>
       </c>
-      <c r="BL2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="BN2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="BR2" t="n">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>10</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
         <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.69</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="CC2" t="n">
         <v>1.58</v>
@@ -1622,16 +1622,16 @@
         <v>1.63</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="CI2" t="n">
         <v>2.1</v>
@@ -1640,25 +1640,25 @@
         <v>1.72</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CR2" t="n">
         <v>1.31</v>
@@ -1673,10 +1673,10 @@
         <v>1.63</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1685,10 +1685,10 @@
         <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.19</v>
@@ -1700,79 +1700,79 @@
         <v>2.51</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.09999999999999</v>
+        <v>85.17</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.8</v>
+        <v>5.41</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>53.8</v>
+        <v>48.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.7</v>
+        <v>10.83</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.3</v>
+        <v>7.08</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53</v>
+        <v>49.75</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.9</v>
+        <v>13.75</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.1</v>
+        <v>5.17</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.5</v>
+        <v>15.75</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1797,46 +1797,46 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H3" t="n">
-        <v>47.2</v>
+        <v>59.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.4</v>
+        <v>5.83</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>27.83</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q3" t="n">
         <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>8.17</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.2</v>
+        <v>46.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.6</v>
+        <v>20.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.2</v>
+        <v>21.17</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.2</v>
+        <v>12.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,139 +1929,139 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>35.8</v>
+        <v>35.83</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.6</v>
+        <v>12.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.9</v>
+        <v>4.42</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.64</v>
+        <v>4.42</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.6</v>
+        <v>5.22</v>
       </c>
       <c r="CC3" t="n">
-        <v>10.22</v>
+        <v>9.41</v>
       </c>
       <c r="CD3" t="n">
-        <v>11.93</v>
+        <v>10.81</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
@@ -2076,73 +2076,73 @@
         <v>1.58</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DG3" t="n">
         <v>2</v>
       </c>
-      <c r="DG3" t="n">
-        <v>1.6</v>
-      </c>
       <c r="DH3" t="n">
-        <v>50.6</v>
+        <v>56.92</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.4</v>
+        <v>4.58</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DM3" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DP3" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.6</v>
+        <v>11.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.5</v>
+        <v>8.83</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.8</v>
+        <v>8.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.6</v>
+        <v>16.58</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="H4" t="n">
-        <v>88.8</v>
+        <v>86.67</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>49.4</v>
+        <v>47.33</v>
       </c>
       <c r="N4" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>13.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14.17</v>
       </c>
       <c r="R4" t="n">
-        <v>7.2</v>
+        <v>7.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.6</v>
+        <v>48.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.8</v>
+        <v>16.83</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,70 +2356,70 @@
         <v>2.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.18</v>
+        <v>10.58</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.18</v>
+        <v>4.83</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BX4" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.55</v>
+        <v>4.46</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.54</v>
+        <v>5.37</v>
       </c>
       <c r="CC4" t="n">
         <v>6.43</v>
@@ -2428,157 +2428,157 @@
         <v>6.91</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.52</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="CT4" t="n">
         <v>3.26</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CV4" t="n">
         <v>2.44</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.5</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.09</v>
+        <v>72.42</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.91</v>
+        <v>45.16</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.09</v>
+        <v>12.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.46</v>
+        <v>12.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.73</v>
+        <v>44</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.37</v>
+        <v>12.42</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.09</v>
+        <v>17.08</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="5">
@@ -2588,142 +2588,142 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H5" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>28.8</v>
+        <v>30.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AB5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AC5" t="n">
-        <v>19.6</v>
+        <v>19.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>66</v>
+        <v>70.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.4</v>
+        <v>11.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,220 +2735,220 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.4</v>
+        <v>48.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.4</v>
+        <v>10.83</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CH5" t="n">
         <v>1.3</v>
       </c>
-      <c r="BO5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>80</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="CI5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY5" t="n">
         <v>1.96</v>
       </c>
-      <c r="CJ5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CW5" t="n">
+      <c r="CZ5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA5" t="n">
         <v>1.86</v>
       </c>
-      <c r="CX5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.85</v>
-      </c>
       <c r="DB5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="DG5" t="n">
         <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>70.40000000000001</v>
+        <v>73.42</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.7</v>
+        <v>5.34</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.6</v>
+        <v>31.67</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.6</v>
+        <v>11.17</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.7</v>
+        <v>10.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.2</v>
+        <v>6.84</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>47.3</v>
+        <v>48.83</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.8</v>
+        <v>10.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.9</v>
+        <v>18.42</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="6">
@@ -3144,10 +3144,10 @@
         <v>0.14</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.57</v>
+        <v>5.71</v>
       </c>
       <c r="BC6" t="n">
         <v>4.43</v>
@@ -3156,7 +3156,7 @@
         <v>18.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
@@ -3369,10 +3369,10 @@
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.09</v>
+        <v>10.18</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.09</v>
+        <v>6.18</v>
       </c>
       <c r="DZ6" t="n">
         <v>4</v>
@@ -3381,7 +3381,7 @@
         <v>17.82</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC6" t="n">
         <v>2.91</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>83</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.75</v>
+        <v>53.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.75</v>
+        <v>10.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.25</v>
+        <v>55.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.25</v>
+        <v>17</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.25</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>12.75</v>
+        <v>13.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BH7" t="n">
-        <v>10</v>
+        <v>10.18</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK7" t="n">
         <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU7" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BV7" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BW7" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY7" t="n">
         <v>1.23</v>
@@ -3625,16 +3625,16 @@
         <v>1.24</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.32</v>
+        <v>6.35</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.24</v>
+        <v>7.2</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="CE7" t="n">
         <v>1.18</v>
@@ -3643,34 +3643,34 @@
         <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CH7" t="n">
         <v>1.82</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.73</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
         <v>1.07</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CQ7" t="n">
         <v>1.95</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CV7" t="n">
         <v>2.23</v>
@@ -3691,95 +3691,95 @@
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DD7" t="n">
         <v>1.92</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.2</v>
+        <v>105.64</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.5</v>
+        <v>6.82</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>68.5</v>
+        <v>68.45</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.5</v>
+        <v>10.54</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.2</v>
+        <v>59.64</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.5</v>
+        <v>17.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.699999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.7</v>
+        <v>16.73</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="8">
@@ -3789,94 +3789,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>66.14</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>26.8</v>
+        <v>28.57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.6</v>
+        <v>8.43</v>
       </c>
       <c r="R8" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>45.4</v>
+        <v>46.29</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.4</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6</v>
+        <v>4.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3960,70 +3960,70 @@
         <v>2.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.1</v>
+        <v>9.92</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.3</v>
+        <v>4.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>5.08</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
         <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="CA8" t="n">
         <v>3.79</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>3.54</v>
-      </c>
       <c r="CB8" t="n">
-        <v>3.76</v>
+        <v>3.97</v>
       </c>
       <c r="CC8" t="n">
         <v>2.83</v>
@@ -4032,73 +4032,73 @@
         <v>2.85</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="CH8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK8" t="n">
         <v>1.16</v>
       </c>
-      <c r="CI8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="CT8" t="n">
         <v>3.04</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX8" t="n">
         <v>1.65</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4110,79 +4110,79 @@
         <v>2.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>60</v>
+        <v>63.58</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.1</v>
+        <v>9.92</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.1</v>
+        <v>9.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52</v>
+        <v>51.42</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.4</v>
+        <v>9.59</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.9</v>
+        <v>5.58</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.2</v>
+        <v>14.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="9">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4207,271 +4207,271 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="H9" t="n">
-        <v>79.5</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K9" t="n">
-        <v>6.17</v>
+        <v>6.29</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M9" t="n">
-        <v>46.67</v>
+        <v>51.14</v>
       </c>
       <c r="N9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>94</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AO9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>11</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>62.83</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AP9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO9" t="n">
         <v>1.67</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>62.75</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BP9" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
         <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.59</v>
+        <v>4.51</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CD9" t="n">
         <v>1.68</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CN9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
@@ -4486,73 +4486,73 @@
         <v>1.7</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB9" t="n">
         <v>1.16</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DD9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>2.25</v>
       </c>
-      <c r="DE9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="DK9" t="n">
-        <v>6.3</v>
+        <v>6.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>50</v>
+        <v>52.83</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="DP9" t="n">
-        <v>12</v>
+        <v>12.42</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.1</v>
+        <v>9.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.8</v>
+        <v>62.17</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.2</v>
+        <v>16.25</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0.4</v>
@@ -4685,139 +4685,139 @@
         <v>1.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>52.67</v>
+        <v>57.14</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>26.83</v>
+        <v>28.71</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.67</v>
+        <v>12.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.83</v>
+        <v>12.29</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>10.29</v>
       </c>
       <c r="AT10" t="n">
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.33</v>
+        <v>46.71</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.33</v>
+        <v>8.57</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.5</v>
+        <v>14.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
         <v>2.42</v>
@@ -4826,61 +4826,61 @@
         <v>2.36</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.92</v>
+        <v>5.3</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.34</v>
+        <v>5.66</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.59</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT10" t="n">
         <v>3.1</v>
@@ -4889,106 +4889,106 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
         <v>2.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="DH10" t="n">
-        <v>55.18</v>
+        <v>57.58</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>32.09</v>
+        <v>32.75</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.27</v>
+        <v>10.75</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.91</v>
+        <v>8.67</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.91</v>
+        <v>49.83</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.45</v>
+        <v>12.75</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.18</v>
+        <v>8.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.55</v>
+        <v>15.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -4998,40 +4998,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="H11" t="n">
-        <v>78.40000000000001</v>
+        <v>74.83</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>45.2</v>
+        <v>40.67</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
@@ -5040,211 +5040,211 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>13.8</v>
+        <v>13.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="R11" t="n">
-        <v>7.4</v>
+        <v>8.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.6</v>
+        <v>48.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.6</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>79.83</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BK11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.8</v>
-      </c>
       <c r="BL11" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>90</v>
+        <v>91.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BU11" t="n">
-        <v>30</v>
+        <v>41.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>58.33</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.86</v>
+        <v>3.84</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.38</v>
+        <v>4.49</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.02</v>
+        <v>5.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.8</v>
+        <v>6.32</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG11" t="n">
         <v>3.22</v>
@@ -5253,22 +5253,22 @@
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CO11" t="n">
         <v>1.22</v>
@@ -5277,121 +5277,121 @@
         <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CU11" t="n">
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.29</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>79.40000000000001</v>
+        <v>77.33</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.4</v>
+        <v>41.08</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.3</v>
+        <v>11.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>14</v>
+        <v>13.25</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.4</v>
+        <v>9.08</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.7</v>
+        <v>47.75</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="DY11" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.4</v>
+        <v>17.42</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -5401,61 +5401,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>40</v>
+        <v>52.8</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>16.25</v>
+        <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="R12" t="n">
-        <v>6.75</v>
+        <v>7.8</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5467,28 +5467,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>40.75</v>
+        <v>42.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47.86</v>
+        <v>48</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.14</v>
@@ -5572,70 +5572,70 @@
         <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.82</v>
+        <v>7.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>8.66</v>
+        <v>7.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="CC12" t="n">
         <v>5.27</v>
@@ -5650,22 +5650,22 @@
         <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK12" t="n">
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM12" t="n">
         <v>2.31</v>
@@ -5677,7 +5677,7 @@
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.67</v>
@@ -5692,22 +5692,22 @@
         <v>3.11</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
         <v>1.83</v>
@@ -5719,82 +5719,82 @@
         <v>1.7</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>61</v>
+        <v>64.58</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM12" t="n">
-        <v>29.82</v>
+        <v>30.67</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.45</v>
+        <v>13.66</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.27</v>
+        <v>8.58</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.27</v>
+        <v>45.83</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.36</v>
+        <v>2.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.36</v>
+        <v>15.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5894,118 +5894,118 @@
         <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>98.5</v>
+        <v>107.17</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AL13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BM13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6014,19 +6014,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>40</v>
+        <v>41.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="BY13" t="n">
         <v>1.12</v>
@@ -6035,81 +6035,81 @@
         <v>1.11</v>
       </c>
       <c r="CA13" t="n">
-        <v>7.04</v>
+        <v>6.78</v>
       </c>
       <c r="CB13" t="n">
-        <v>9.34</v>
+        <v>8.69</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="CF13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CN13" t="n">
         <v>1.85</v>
       </c>
-      <c r="CG13" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>2.01</v>
-      </c>
       <c r="CO13" t="n">
-        <v>1.06</v>
+        <v>0.97</v>
       </c>
       <c r="CP13" t="n">
         <v>1.29</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX13" t="n">
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="DB13" t="n">
         <v>1.11</v>
@@ -6121,79 +6121,79 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.8</v>
+        <v>108.92</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.9</v>
+        <v>8.25</v>
       </c>
       <c r="DL13" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="DM13" t="n">
-        <v>65.59999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.1</v>
+        <v>4.58</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.3</v>
+        <v>10.34</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="DR13" t="n">
-        <v>3.3</v>
+        <v>4.08</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.2</v>
+        <v>61.58</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.3</v>
+        <v>13.16</v>
       </c>
       <c r="DZ13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.1</v>
+        <v>16.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.4</v>
@@ -6293,139 +6293,139 @@
         <v>0.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG14" t="n">
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AI14" t="n">
-        <v>107.2</v>
+        <v>108.67</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.8</v>
+        <v>56.67</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP14" t="n">
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.2</v>
+        <v>11.83</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.8</v>
+        <v>10.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.2</v>
+        <v>57.17</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.8</v>
+        <v>11.67</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.4</v>
+        <v>14.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.3</v>
+        <v>5.64</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU14" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY14" t="n">
         <v>1.4</v>
@@ -6434,55 +6434,55 @@
         <v>1.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.07</v>
+        <v>0.97</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6524,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.1</v>
+        <v>103.37</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.8</v>
+        <v>7.63</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
-        <v>63.6</v>
+        <v>63.37</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DO14" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.8</v>
+        <v>12.09</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58</v>
+        <v>58.37</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.3</v>
+        <v>13.09</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.6</v>
+        <v>16.82</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="15">
@@ -7009,292 +7009,292 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>65.83</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P16" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CH16" t="n">
         <v>1.4</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M16" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>70</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>5</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>1.54</v>
-      </c>
       <c r="CI16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CT16" t="n">
         <v>3.08</v>
@@ -7303,22 +7303,22 @@
         <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.42</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DB16" t="n">
         <v>1.23</v>
@@ -7333,76 +7333,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="DH16" t="n">
-        <v>68.7</v>
+        <v>72</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.6</v>
+        <v>5.08</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="DM16" t="n">
-        <v>34.4</v>
+        <v>37.92</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.1</v>
+        <v>12</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.6</v>
+        <v>11.75</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.8</v>
+        <v>18.08</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7478,7 +7478,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.5</v>
+        <v>49.33</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -7505,49 +7505,49 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.4</v>
+        <v>-0.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>27.4</v>
+        <v>26.33</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.8</v>
+        <v>12.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.8</v>
+        <v>11.83</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -7559,82 +7559,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB17" t="n">
         <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>11.2</v>
+        <v>11.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.21</v>
@@ -7643,55 +7643,55 @@
         <v>3.73</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.99</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.54</v>
+        <v>3.16</v>
       </c>
       <c r="CE17" t="n">
         <v>1.34</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH17" t="n">
         <v>1.44</v>
       </c>
       <c r="CI17" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CL17" t="n">
         <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7706,10 +7706,10 @@
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
@@ -7724,88 +7724,88 @@
         <v>1.87</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="DH17" t="n">
-        <v>66.91</v>
+        <v>67</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>33.27</v>
+        <v>32.25</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.27</v>
+        <v>11.66</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.46</v>
+        <v>11</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.27</v>
+        <v>48.16</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.46</v>
+        <v>11.08</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,139 +7905,139 @@
         <v>3.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>35.2</v>
+        <v>43.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.2</v>
+        <v>20.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.6</v>
+        <v>11.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.8</v>
+        <v>11.83</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.2</v>
+        <v>45.83</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BA18" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BD18" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="BE18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.55</v>
       </c>
-      <c r="BF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.6</v>
-      </c>
       <c r="BN18" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.6</v>
+        <v>4.82</v>
       </c>
       <c r="BR18" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS18" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY18" t="n">
         <v>2.77</v>
@@ -8046,55 +8046,55 @@
         <v>3.11</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.52</v>
+        <v>5.05</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.59</v>
+        <v>5.08</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CH18" t="n">
         <v>1.27</v>
       </c>
       <c r="CI18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL18" t="n">
         <v>1.99</v>
       </c>
-      <c r="CJ18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CK18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CL18" t="n">
-        <v>2</v>
-      </c>
       <c r="CM18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8109,106 +8109,106 @@
         <v>1.44</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DH18" t="n">
-        <v>61.4</v>
+        <v>63.55</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DM18" t="n">
-        <v>31.7</v>
+        <v>31.63</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.3</v>
+        <v>12.09</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13</v>
+        <v>12.45</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.2</v>
+        <v>10.18</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.2</v>
+        <v>49.63</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DX18" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.6</v>
+        <v>7.18</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="EA18" t="n">
-        <v>21</v>
+        <v>20.73</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="19">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
@@ -8230,49 +8230,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
-        <v>60.6</v>
+        <v>66</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M19" t="n">
-        <v>31.8</v>
+        <v>33.67</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>13.6</v>
+        <v>13.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="R19" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>52.2</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.4</v>
+        <v>12.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.6</v>
+        <v>8.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0.4</v>
@@ -8389,70 +8389,70 @@
         <v>2.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU19" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="CC19" t="n">
         <v>3.06</v>
@@ -8464,40 +8464,40 @@
         <v>1.29</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CH19" t="n">
         <v>1.52</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK19" t="n">
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CM19" t="n">
         <v>2.33</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO19" t="n">
         <v>1.19</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -8512,10 +8512,10 @@
         <v>1.53</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8533,85 +8533,85 @@
         <v>1.2</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="DH19" t="n">
-        <v>60.7</v>
+        <v>63.64</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="DK19" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>29.1</v>
+        <v>30.37</v>
       </c>
       <c r="DN19" t="n">
         <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.4</v>
+        <v>12.27</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>53</v>
+        <v>52.27</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>8.27</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.7</v>
+        <v>17.09</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1502,7 +1502,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="AR2" t="n">
         <v>11.8</v>
@@ -1733,7 +1733,7 @@
         <v>2.25</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="DQ2" t="n">
         <v>10.83</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="G3" t="n">
         <v>1.67</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>5.83</v>
@@ -1851,7 +1851,7 @@
         <v>46.17</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Z3" t="n">
         <v>11.17</v>
@@ -1869,13 +1869,13 @@
         <v>1.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="n">
         <v>2.33</v>
@@ -1884,10 +1884,10 @@
         <v>54.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="AL3" t="n">
         <v>3.33</v>
@@ -1950,7 +1950,7 @@
         <v>0.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
         <v>2.75</v>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="DG3" t="n">
         <v>2</v>
@@ -2115,10 +2115,10 @@
         <v>56.92</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="DK3" t="n">
         <v>4.58</v>
@@ -2157,7 +2157,7 @@
         <v>41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="DX3" t="n">
         <v>8.08</v>
@@ -2175,7 +2175,7 @@
         <v>0.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4">
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
         <v>0.83</v>
@@ -2609,10 +2609,10 @@
         <v>76.5</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -2675,7 +2675,7 @@
         <v>1.11</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="DG5" t="n">
         <v>2</v>
@@ -2921,10 +2921,10 @@
         <v>73.42</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="DK5" t="n">
         <v>5.34</v>
@@ -2981,7 +2981,7 @@
         <v>1.04</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>70.75</v>
+        <v>75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>14.75</v>
+        <v>14.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="R6" t="n">
-        <v>11.75</v>
+        <v>10.4</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.25</v>
+        <v>10.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>19.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.45</v>
+        <v>4.17</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.84</v>
+        <v>6.96</v>
       </c>
       <c r="BZ6" t="n">
-        <v>7.04</v>
+        <v>6.36</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CC6" t="n">
         <v>3.5</v>
@@ -3234,43 +3234,43 @@
         <v>3.42</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN6" t="n">
         <v>1.87</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3285,10 +3285,10 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
@@ -3297,10 +3297,10 @@
         <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
@@ -3309,82 +3309,82 @@
         <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DH6" t="n">
-        <v>66.27</v>
+        <v>68.41</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.46</v>
+        <v>3.33</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM6" t="n">
-        <v>32.64</v>
+        <v>34.92</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.27</v>
+        <v>13.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.73</v>
+        <v>9.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.45</v>
+        <v>47</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.18</v>
+        <v>10.33</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.18</v>
+        <v>6.58</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.82</v>
+        <v>19</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>88.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.4</v>
+        <v>53.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>6.83</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.4</v>
+        <v>56.33</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>17</v>
+        <v>16.83</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>8.4</v>
+        <v>7.83</v>
       </c>
       <c r="BD7" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.18</v>
+        <v>10.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
         <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY7" t="n">
         <v>1.23</v>
@@ -3625,34 +3625,34 @@
         <v>1.24</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.35</v>
+        <v>6.33</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="CE7" t="n">
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
@@ -3667,119 +3667,119 @@
         <v>2.09</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.64</v>
+        <v>106.75</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.82</v>
+        <v>7</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>68.45</v>
+        <v>67.42</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.09</v>
+        <v>9.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.54</v>
+        <v>10.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.36</v>
+        <v>6.58</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.64</v>
+        <v>59.75</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.73</v>
+        <v>16.66</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="8">
@@ -4267,16 +4267,16 @@
         <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC9" t="n">
         <v>18.71</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1.57</v>
@@ -4573,16 +4573,16 @@
         <v>13.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.33</v>
+        <v>5.41</v>
       </c>
       <c r="EA9" t="n">
         <v>16.25</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC9" t="n">
         <v>1.75</v>
@@ -5413,7 +5413,7 @@
         <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
         <v>1.4</v>
@@ -5425,7 +5425,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -5443,7 +5443,7 @@
         <v>0.8</v>
       </c>
       <c r="P12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
         <v>14.4</v>
@@ -5488,7 +5488,7 @@
         <v>0.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5725,7 +5725,7 @@
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
         <v>1.75</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="DK12" t="n">
         <v>3.42</v>
@@ -5755,7 +5755,7 @@
         <v>1.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.92</v>
+        <v>8.83</v>
       </c>
       <c r="DQ12" t="n">
         <v>13.66</v>
@@ -5794,7 +5794,7 @@
         <v>0.92</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13">
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="n">
-        <v>97</v>
+        <v>95.83</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M14" t="n">
-        <v>71.40000000000001</v>
+        <v>67.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="P14" t="n">
-        <v>12.4</v>
+        <v>12.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.8</v>
+        <v>8.83</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.8</v>
+        <v>60.17</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.8</v>
+        <v>14.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.8</v>
+        <v>18.67</v>
       </c>
       <c r="AD14" t="n">
         <v>1.81</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6374,70 +6374,70 @@
         <v>1.83</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.36</v>
+        <v>5.58</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.54</v>
+        <v>4.63</v>
       </c>
       <c r="CC14" t="n">
         <v>2.56</v>
@@ -6446,43 +6446,43 @@
         <v>2.69</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6524,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="DH14" t="n">
-        <v>103.37</v>
+        <v>102.25</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.63</v>
+        <v>7.75</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM14" t="n">
-        <v>63.37</v>
+        <v>62.17</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.73</v>
+        <v>9.58</v>
       </c>
       <c r="DR14" t="n">
         <v>7</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.37</v>
+        <v>58.67</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.82</v>
+        <v>16.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6699,112 +6699,112 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>69.8</v>
+        <v>71.33</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN15" t="n">
-        <v>35.6</v>
+        <v>38.33</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AP15" t="n">
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
         <v>11</v>
       </c>
-      <c r="AR15" t="n">
-        <v>10.8</v>
-      </c>
       <c r="AS15" t="n">
-        <v>9.4</v>
+        <v>8.83</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.6</v>
+        <v>37.67</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>4.83</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BD15" t="n">
-        <v>14</v>
+        <v>14.67</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.18</v>
+        <v>11.33</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="BQ15" t="n">
         <v>5</v>
@@ -6813,22 +6813,22 @@
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.82</v>
@@ -6837,55 +6837,55 @@
         <v>2.87</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.82</v>
+        <v>5.8</v>
       </c>
       <c r="CC15" t="n">
-        <v>11.58</v>
+        <v>11.17</v>
       </c>
       <c r="CD15" t="n">
-        <v>14.9</v>
+        <v>13.67</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.13</v>
+        <v>2.87</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.08</v>
+        <v>0.99</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CR15" t="n">
         <v>1.35</v>
@@ -6927,79 +6927,79 @@
         <v>2.71</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DH15" t="n">
-        <v>60</v>
+        <v>61.58</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DM15" t="n">
-        <v>29.37</v>
+        <v>31.25</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.64</v>
+        <v>13.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.73</v>
+        <v>9.92</v>
       </c>
       <c r="DR15" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>38.18</v>
+        <v>38.17</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.539999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.91</v>
+        <v>6.16</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.55</v>
+        <v>16.67</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="H18" t="n">
-        <v>87.59999999999999</v>
+        <v>84.83</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M18" t="n">
-        <v>45.2</v>
+        <v>41.33</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>12.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.2</v>
+        <v>12.33</v>
       </c>
       <c r="R18" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,34 +7881,34 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>54.2</v>
+        <v>51.67</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.2</v>
+        <v>10.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>25.2</v>
+        <v>23.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AF18" t="n">
         <v>0.33</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="n">
         <v>1.17</v>
@@ -7920,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="AL18" t="n">
         <v>3</v>
@@ -7965,7 +7965,7 @@
         <v>45.83</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BA18" t="n">
         <v>8.5</v>
@@ -7986,70 +7986,70 @@
         <v>1.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.77</v>
+        <v>4.34</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.11</v>
+        <v>4.48</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.64</v>
+        <v>3.85</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="CC18" t="n">
         <v>5.05</v>
@@ -8061,154 +8061,154 @@
         <v>1.23</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CM18" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="CO18" t="n">
         <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="CT18" t="n">
         <v>3.04</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CX18" t="n">
         <v>1.72</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="DH18" t="n">
-        <v>63.55</v>
+        <v>64.17</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>31.63</v>
+        <v>30.83</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DP18" t="n">
-        <v>12.09</v>
+        <v>11.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.45</v>
+        <v>12.08</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.63</v>
+        <v>48.75</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.73</v>
+        <v>20.25</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8308,139 +8308,139 @@
         <v>2.33</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>60.8</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.4</v>
+        <v>26.83</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.6</v>
+        <v>12.83</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53.8</v>
+        <v>52.67</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.8</v>
+        <v>12.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.4</v>
+        <v>7.83</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BY19" t="n">
         <v>3.2</v>
@@ -8449,40 +8449,40 @@
         <v>3.35</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM19" t="n">
         <v>2.33</v>
@@ -8491,13 +8491,13 @@
         <v>1.83</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -8530,88 +8530,88 @@
         <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DH19" t="n">
-        <v>63.64</v>
+        <v>65.5</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>30.37</v>
+        <v>30.25</v>
       </c>
       <c r="DN19" t="n">
         <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.27</v>
+        <v>12.17</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.27</v>
+        <v>8.58</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.27</v>
+        <v>51.84</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.73</v>
+        <v>12.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.09</v>
+        <v>17.5</v>
       </c>
       <c r="EB19" t="n">
         <v>1.22</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.43</v>
@@ -1472,46 +1472,46 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>83.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>51.4</v>
+        <v>50.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.6</v>
+        <v>14.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.2</v>
+        <v>50.83</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.2</v>
+        <v>18.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BR2" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY2" t="n">
         <v>2.05</v>
@@ -1610,73 +1610,73 @@
         <v>2</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CL2" t="n">
         <v>1.76</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CN2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CP2" t="n">
         <v>1.57</v>
       </c>
-      <c r="CO2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CQ2" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="CT2" t="n">
         <v>3.2</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1691,88 +1691,88 @@
         <v>1.91</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.17</v>
+        <v>86.16</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.41</v>
+        <v>5.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.5</v>
+        <v>48.23</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="DP2" t="n">
-        <v>14</v>
+        <v>14.47</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.83</v>
+        <v>10.77</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.75</v>
+        <v>49.69</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.75</v>
+        <v>13.61</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.75</v>
+        <v>16</v>
       </c>
       <c r="EB2" t="n">
         <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="G3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="n">
-        <v>59.33</v>
+        <v>61.71</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="K3" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>27.83</v>
+        <v>27.86</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="P3" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11.43</v>
       </c>
       <c r="R3" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.17</v>
+        <v>46.86</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.17</v>
+        <v>10.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.83</v>
+        <v>21.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,67 +1953,67 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BN3" t="n">
         <v>1.08</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.08</v>
+        <v>3.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.25</v>
+        <v>3.96</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="CB3" t="n">
         <v>5.22</v>
@@ -2028,25 +2028,25 @@
         <v>1.22</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM3" t="n">
         <v>2.3</v>
@@ -2055,31 +2055,31 @@
         <v>1.79</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.71</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
@@ -2097,52 +2097,52 @@
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DG3" t="n">
         <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>56.92</v>
+        <v>58.38</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>24.5</v>
+        <v>24.77</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.42</v>
+        <v>12.08</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41</v>
+        <v>41.77</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.08</v>
+        <v>7.85</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.58</v>
+        <v>17.23</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>2.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>58.17</v>
+        <v>62.43</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>43</v>
+        <v>41.86</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.17</v>
+        <v>10.57</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.17</v>
+        <v>10.71</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.33</v>
+        <v>18.57</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.58</v>
+        <v>10.77</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY4" t="n">
         <v>2.93</v>
@@ -2416,73 +2416,73 @@
         <v>3.09</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.37</v>
+        <v>5.26</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.43</v>
+        <v>5.97</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.91</v>
+        <v>6.62</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM4" t="n">
         <v>2.5</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
@@ -2500,85 +2500,85 @@
         <v>1.18</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.42</v>
+        <v>73.62</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="DL4" t="n">
         <v>0.08</v>
       </c>
       <c r="DM4" t="n">
-        <v>45.16</v>
+        <v>44.38</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.67</v>
+        <v>12.62</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44</v>
+        <v>43.92</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.42</v>
+        <v>12.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.67</v>
+        <v>7.54</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.08</v>
+        <v>17.77</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>70.33</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>32.5</v>
+        <v>30.57</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.5</v>
+        <v>10.43</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.17</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.33</v>
+        <v>47.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>7.43</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BD5" t="n">
-        <v>17</v>
+        <v>16.71</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.58</v>
+        <v>4.85</v>
       </c>
       <c r="BR5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
         <v>2.67</v>
@@ -2819,67 +2819,67 @@
         <v>2.75</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.89</v>
+        <v>4.52</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.53</v>
+        <v>5.06</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM5" t="n">
         <v>2.18</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV5" t="n">
         <v>1.93</v>
@@ -2900,55 +2900,55 @@
         <v>1.86</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>73.42</v>
+        <v>70.69</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.34</v>
+        <v>5.16</v>
       </c>
       <c r="DL5" t="n">
         <v>0.08</v>
       </c>
       <c r="DM5" t="n">
-        <v>31.67</v>
+        <v>30.69</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.17</v>
+        <v>11.15</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.75</v>
+        <v>11.15</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.84</v>
+        <v>7.31</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.83</v>
+        <v>48.23</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.75</v>
+        <v>10.54</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.84</v>
+        <v>7.54</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.42</v>
+        <v>18.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,223 +3084,223 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>63.71</v>
+        <v>65.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.29</v>
+        <v>33</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP6" t="n">
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.43</v>
+        <v>11.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.57</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.71</v>
+        <v>44</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.14</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.86</v>
+        <v>18.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="BF6" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="BR6" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY6" t="n">
         <v>6.96</v>
       </c>
       <c r="BZ6" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>4.34</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.29</v>
+        <v>4.63</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.5</v>
+        <v>4.57</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.42</v>
+        <v>4.47</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.19</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CX6" t="n">
         <v>1.59</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.32</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
@@ -3309,82 +3309,82 @@
         <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DH6" t="n">
-        <v>68.41</v>
+        <v>69.31</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM6" t="n">
-        <v>34.92</v>
+        <v>35.69</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DO6" t="n">
         <v>1.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.33</v>
+        <v>12.85</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.17</v>
+        <v>10.15</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.33</v>
+        <v>8.92</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47</v>
+        <v>46.38</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.58</v>
+        <v>6.46</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="EA6" t="n">
         <v>19</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="L7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>81</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD7" t="n">
         <v>2.17</v>
       </c>
-      <c r="P7" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.25</v>
+        <v>10.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BM7" t="n">
         <v>1</v>
       </c>
-      <c r="BL7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BN7" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU7" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>1.23</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="CA7" t="n">
-        <v>6.33</v>
+        <v>6.46</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.25</v>
+        <v>7.34</v>
       </c>
       <c r="CC7" t="n">
         <v>1.42</v>
@@ -3640,7 +3640,7 @@
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CG7" t="n">
         <v>4.16</v>
@@ -3649,42 +3649,42 @@
         <v>1.8</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="CP7" t="n">
         <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CW7" t="n">
         <v>1.75</v>
@@ -3695,91 +3695,91 @@
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DC7" t="n">
         <v>1.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DE7" t="n">
         <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.75</v>
+        <v>106.15</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DK7" t="n">
         <v>7</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>67.42</v>
+        <v>67.61</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DP7" t="n">
         <v>9.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.33</v>
+        <v>10.08</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.58</v>
+        <v>6.92</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.75</v>
+        <v>59.85</v>
       </c>
       <c r="DW7" t="n">
         <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>17.08</v>
+        <v>16.85</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.33</v>
+        <v>9.16</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.75</v>
+        <v>7.69</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.66</v>
+        <v>16.69</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="8">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0.29</v>
@@ -3885,133 +3885,133 @@
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>68.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>38</v>
+        <v>40.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>8.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.4</v>
+        <v>12.17</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>7.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.4</v>
+        <v>16.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.92</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY8" t="n">
         <v>4.07</v>
@@ -4020,55 +4020,55 @@
         <v>4.04</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4083,43 +4083,43 @@
         <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
         <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DH8" t="n">
-        <v>63.58</v>
+        <v>67.38</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
@@ -4128,61 +4128,61 @@
         <v>2.08</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.92</v>
+        <v>10.23</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.75</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DR8" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.42</v>
+        <v>51.15</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.59</v>
+        <v>10.08</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>4.31</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.33</v>
+        <v>14.23</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="9">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4282,139 +4282,139 @@
         <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>94</v>
+        <v>96.33</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.2</v>
+        <v>59.17</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>61.2</v>
+        <v>63</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.2</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.4</v>
+        <v>8.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.8</v>
+        <v>6.67</v>
       </c>
       <c r="BD9" t="n">
-        <v>12.8</v>
+        <v>13.17</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BF9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
         <v>2.28</v>
@@ -4423,43 +4423,43 @@
         <v>2.28</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="CE9" t="n">
         <v>1.23</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CH9" t="n">
         <v>1.63</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK9" t="n">
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN9" t="n">
         <v>1.96</v>
@@ -4486,16 +4486,16 @@
         <v>1.7</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.48</v>
@@ -4513,79 +4513,79 @@
         <v>2.27</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
         <v>2.08</v>
       </c>
-      <c r="DH9" t="n">
-        <v>89.16</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.25</v>
-      </c>
       <c r="DK9" t="n">
-        <v>6.17</v>
+        <v>6.62</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>52.83</v>
+        <v>54.85</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.42</v>
+        <v>12.39</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.25</v>
+        <v>5.92</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.17</v>
+        <v>62.92</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.67</v>
+        <v>14.46</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.25</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.41</v>
+        <v>5.85</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.25</v>
+        <v>16.15</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
@@ -4595,94 +4595,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>58.2</v>
+        <v>70.83</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>38.4</v>
+        <v>42.17</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.2</v>
+        <v>12.33</v>
       </c>
       <c r="R10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54.2</v>
+        <v>56.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.4</v>
+        <v>13.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.4</v>
+        <v>5.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>17.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0.29</v>
@@ -4769,67 +4769,67 @@
         <v>3.92</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
       <c r="BI10" t="n">
         <v>3.92</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1.08</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1</v>
-      </c>
       <c r="BM10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV10" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.44</v>
+        <v>4.39</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="CC10" t="n">
         <v>5.3</v>
@@ -4838,43 +4838,43 @@
         <v>5.66</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CK10" t="n">
         <v>1.47</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4889,10 +4889,10 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
@@ -4910,85 +4910,85 @@
         <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="DH10" t="n">
-        <v>57.58</v>
+        <v>63.46</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.16</v>
+        <v>4.54</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>32.75</v>
+        <v>34.92</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.67</v>
+        <v>12.31</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.67</v>
+        <v>8.31</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.83</v>
+        <v>51.15</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.75</v>
+        <v>13.15</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.33</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.42</v>
+        <v>4.77</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.75</v>
+        <v>15.61</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11">
@@ -4998,94 +4998,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="G11" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>74.83</v>
+        <v>74</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K11" t="n">
-        <v>4.83</v>
+        <v>4.29</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>40.67</v>
+        <v>38.14</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P11" t="n">
-        <v>13.33</v>
+        <v>12.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="R11" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="U11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.17</v>
+        <v>45.29</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>16.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5169,70 +5169,70 @@
         <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.83</v>
+        <v>5.08</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT11" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU11" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.85</v>
+        <v>4.37</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.49</v>
+        <v>4.54</v>
       </c>
       <c r="CC11" t="n">
         <v>5.65</v>
@@ -5244,16 +5244,16 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.71</v>
@@ -5262,7 +5262,7 @@
         <v>1.54</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CM11" t="n">
         <v>2.39</v>
@@ -5271,13 +5271,13 @@
         <v>1.89</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
@@ -5295,19 +5295,19 @@
         <v>2.08</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX11" t="n">
         <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.29</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
@@ -5319,46 +5319,46 @@
         <v>2.97</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="DH11" t="n">
-        <v>77.33</v>
+        <v>76.69</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.08</v>
+        <v>39.69</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.25</v>
+        <v>10.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.25</v>
+        <v>13.16</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.08</v>
+        <v>9.23</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5370,28 +5370,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.75</v>
+        <v>46.23</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>6</v>
+        <v>5.77</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.42</v>
+        <v>17.31</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="12">
@@ -5401,94 +5401,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>52.8</v>
+        <v>58.33</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>23.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.4</v>
+        <v>14.17</v>
       </c>
       <c r="R12" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>42.8</v>
+        <v>44.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.6</v>
+        <v>9.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.8</v>
+        <v>6.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.6</v>
+        <v>15.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5572,70 +5572,70 @@
         <v>2.14</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.08</v>
+        <v>10.69</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BM12" t="n">
         <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.08</v>
+        <v>4.85</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.9</v>
+        <v>7.28</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.93</v>
+        <v>7.34</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.54</v>
+        <v>4.46</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.04</v>
+        <v>4.93</v>
       </c>
       <c r="CC12" t="n">
         <v>5.27</v>
@@ -5644,19 +5644,19 @@
         <v>5.41</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.78</v>
@@ -5665,22 +5665,22 @@
         <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5695,10 +5695,10 @@
         <v>1.58</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5716,85 +5716,85 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="DE12" t="n">
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DH12" t="n">
-        <v>64.58</v>
+        <v>66.23</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>30.67</v>
+        <v>31</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.83</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.83</v>
+        <v>46.31</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.92</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.25</v>
+        <v>6.62</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.67</v>
+        <v>15.31</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="13">
@@ -5804,94 +5804,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G13" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="H13" t="n">
-        <v>110.67</v>
+        <v>112.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K13" t="n">
-        <v>9.17</v>
+        <v>8.43</v>
       </c>
       <c r="L13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M13" t="n">
-        <v>69.33</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O13" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.83</v>
+        <v>11.57</v>
       </c>
       <c r="R13" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="S13" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>62.67</v>
+        <v>61.57</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.33</v>
+        <v>19.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>15.83</v>
+        <v>17</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0.33</v>
@@ -5975,37 +5975,37 @@
         <v>1.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="n">
-        <v>11</v>
+        <v>10.54</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6014,31 +6014,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU13" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BV13" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BW13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.78</v>
+        <v>6.59</v>
       </c>
       <c r="CB13" t="n">
-        <v>8.69</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="CC13" t="n">
         <v>1.36</v>
@@ -6047,43 +6047,43 @@
         <v>1.42</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.06</v>
+        <v>0.98</v>
       </c>
       <c r="CF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CN13" t="n">
         <v>1.7</v>
       </c>
-      <c r="CG13" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.85</v>
-      </c>
       <c r="CO13" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6121,79 +6121,79 @@
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.67</v>
+        <v>3.61</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.92</v>
+        <v>109.85</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ13" t="n">
         <v>1.92</v>
       </c>
       <c r="DK13" t="n">
-        <v>8.25</v>
+        <v>7.92</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DM13" t="n">
-        <v>69.17</v>
+        <v>68.23</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.58</v>
+        <v>4.23</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.34</v>
+        <v>10.23</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12</v>
+        <v>12.31</v>
       </c>
       <c r="DR13" t="n">
         <v>4.08</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.58</v>
+        <v>61.08</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>21</v>
+        <v>20.61</v>
       </c>
       <c r="DY13" t="n">
-        <v>13.16</v>
+        <v>13.15</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7.84</v>
+        <v>7.46</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.33</v>
+        <v>16.92</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.5</v>
@@ -6293,196 +6293,196 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>108.67</v>
+        <v>105</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.83</v>
+        <v>5.14</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>56.67</v>
+        <v>53.29</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.83</v>
+        <v>12.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.17</v>
+        <v>55.43</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.67</v>
+        <v>6.86</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.33</v>
+        <v>13.71</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="BG14" t="n">
         <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.17</v>
+        <v>10.69</v>
       </c>
       <c r="BI14" t="n">
         <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.58</v>
+        <v>5.23</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.58</v>
+        <v>5.38</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY14" t="n">
         <v>1.38</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.21</v>
+        <v>4.22</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.56</v>
+        <v>2.91</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6524,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.84</v>
+        <v>1.15</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.67</v>
+        <v>3.39</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.25</v>
+        <v>100.77</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.75</v>
+        <v>7.23</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>62.17</v>
+        <v>59.93</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.08</v>
+        <v>3.85</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.08</v>
+        <v>12.46</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR14" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.67</v>
+        <v>57.62</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.25</v>
+        <v>12.77</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="15">
@@ -6606,61 +6606,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G15" t="n">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="H15" t="n">
-        <v>51.83</v>
+        <v>61.43</v>
       </c>
       <c r="I15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J15" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="K15" t="n">
-        <v>4.83</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M15" t="n">
-        <v>24.17</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="O15" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="R15" t="n">
-        <v>6.83</v>
+        <v>6.71</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6672,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>38.67</v>
+        <v>41.57</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.83</v>
+        <v>11.71</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.67</v>
+        <v>19.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,85 +6777,85 @@
         <v>1.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.33</v>
+        <v>11.69</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BP15" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.09</v>
+        <v>4.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="CC15" t="n">
         <v>11.17</v>
       </c>
       <c r="CD15" t="n">
-        <v>13.67</v>
+        <v>14.2</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CF15" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CH15" t="n">
         <v>1.3</v>
@@ -6864,40 +6864,40 @@
         <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CV15" t="n">
         <v>1.98</v>
@@ -6918,55 +6918,55 @@
         <v>1.88</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="DH15" t="n">
-        <v>61.58</v>
+        <v>66</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.83</v>
+        <v>5.46</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>31.25</v>
+        <v>33.31</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.25</v>
+        <v>13.46</v>
       </c>
       <c r="DQ15" t="n">
         <v>9.92</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.83</v>
+        <v>7.69</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>38.17</v>
+        <v>39.77</v>
       </c>
       <c r="DW15" t="n">
         <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.75</v>
+        <v>10.31</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.16</v>
+        <v>6.69</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.67</v>
+        <v>17.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.17</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>3.71</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN16" t="n">
-        <v>40</v>
+        <v>39.86</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.67</v>
+        <v>11.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.83</v>
+        <v>9.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40.83</v>
+        <v>39.29</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BD16" t="n">
-        <v>16</v>
+        <v>15.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.33</v>
+        <v>10.31</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.92</v>
+        <v>4.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.75</v>
+        <v>5.08</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT16" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY16" t="n">
         <v>2.32</v>
@@ -7240,169 +7240,169 @@
         <v>2.3</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.02</v>
+        <v>4.74</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.77</v>
       </c>
-      <c r="CM16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.76</v>
-      </c>
       <c r="CO16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CW16" t="n">
         <v>1.73</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB16" t="n">
         <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH16" t="n">
-        <v>72</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.92</v>
+        <v>38</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.5</v>
+        <v>11.23</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.25</v>
+        <v>7.77</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.5</v>
+        <v>44.31</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.08</v>
+        <v>17.46</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.17</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="17">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="H17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="K17" t="n">
-        <v>5.17</v>
+        <v>5.43</v>
       </c>
       <c r="L17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M17" t="n">
-        <v>38.17</v>
+        <v>42.43</v>
       </c>
       <c r="N17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P17" t="n">
         <v>11</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>6.17</v>
+        <v>6.43</v>
       </c>
       <c r="S17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V17" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>49.33</v>
+        <v>52.29</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.67</v>
+        <v>11.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.83</v>
+        <v>15.71</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.58</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BP17" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CC17" t="n">
         <v>2.88</v>
@@ -7658,16 +7658,16 @@
         <v>1.34</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.74</v>
@@ -7679,19 +7679,19 @@
         <v>2.05</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN17" t="n">
         <v>1.86</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7700,19 +7700,19 @@
         <v>2.78</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CU17" t="n">
         <v>1.44</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
@@ -7739,73 +7739,73 @@
         <v>0.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="DH17" t="n">
-        <v>67</v>
+        <v>68.92</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>32.25</v>
+        <v>35</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.66</v>
+        <v>11.61</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.16</v>
+        <v>49.85</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.08</v>
+        <v>11.69</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.08</v>
+        <v>7.69</v>
       </c>
       <c r="DZ17" t="n">
         <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>13.08</v>
+        <v>13.69</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,187 +7905,187 @@
         <v>2.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>43.5</v>
+        <v>46.57</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AL18" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>20.33</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.5</v>
+        <v>7.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="BD18" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="BQ18" t="n">
         <v>4.92</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY18" t="n">
         <v>4.34</v>
       </c>
       <c r="BZ18" t="n">
-        <v>4.48</v>
+        <v>4.23</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.08</v>
+        <v>5.1</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF18" t="n">
         <v>2.46</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CO18" t="n">
         <v>1.16</v>
@@ -8094,19 +8094,19 @@
         <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CT18" t="n">
         <v>3.04</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV18" t="n">
         <v>1.98</v>
@@ -8124,10 +8124,10 @@
         <v>2.14</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC18" t="n">
         <v>1.89</v>
@@ -8139,43 +8139,43 @@
         <v>0.16</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DH18" t="n">
-        <v>64.17</v>
+        <v>64.23</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM18" t="n">
-        <v>30.83</v>
+        <v>30.38</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.75</v>
+        <v>11.46</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.08</v>
+        <v>12</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="DS18" t="n">
         <v>0.16</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.75</v>
+        <v>47.54</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.58</v>
+        <v>9.08</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.25</v>
+        <v>6.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.25</v>
+        <v>20.08</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="19">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -8230,50 +8230,50 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="H19" t="n">
-        <v>66</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J19" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="K19" t="n">
-        <v>4.67</v>
+        <v>5.43</v>
       </c>
       <c r="L19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M19" t="n">
-        <v>33.67</v>
+        <v>35.57</v>
       </c>
       <c r="N19" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P19" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="P19" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>12.83</v>
-      </c>
-      <c r="R19" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51</v>
+        <v>51.86</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>18.43</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AF19" t="n">
         <v>0.33</v>
@@ -8389,88 +8389,88 @@
         <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.33</v>
+        <v>8.69</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.17</v>
+        <v>3.38</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU19" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="CC19" t="n">
         <v>2.86</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CE19" t="n">
         <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG19" t="n">
         <v>3.25</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI19" t="n">
         <v>2.1</v>
@@ -8482,40 +8482,40 @@
         <v>1.54</v>
       </c>
       <c r="CL19" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.68</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8524,94 +8524,94 @@
         <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="DH19" t="n">
-        <v>65.5</v>
+        <v>69.08</v>
       </c>
       <c r="DI19" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DK19" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM19" t="n">
-        <v>30.25</v>
+        <v>31.54</v>
       </c>
       <c r="DN19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.83</v>
+        <v>12.77</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.84</v>
+        <v>52.23</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.5</v>
+        <v>18.92</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1613,13 +1613,13 @@
         <v>4.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
       <c r="CC2" t="n">
         <v>1.54</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CE2" t="n">
         <v>1.08</v>
@@ -1664,10 +1664,10 @@
         <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CU2" t="n">
         <v>1.61</v>
@@ -1679,25 +1679,25 @@
         <v>1.83</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DE2" t="n">
         <v>0.23</v>
@@ -2010,13 +2010,13 @@
         <v>3.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.96</v>
+        <v>4.06</v>
       </c>
       <c r="CA3" t="n">
         <v>4.45</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="CC3" t="n">
         <v>9.41</v>
@@ -2067,10 +2067,10 @@
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU3" t="n">
         <v>1.57</v>
@@ -2079,28 +2079,28 @@
         <v>1.88</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA3" t="n">
         <v>1.95</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC3" t="n">
         <v>1.88</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>1.96</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
         <v>1.86</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>80.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>14.6</v>
+        <v>14.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.2</v>
+        <v>10.83</v>
       </c>
       <c r="R6" t="n">
-        <v>10.4</v>
+        <v>8.67</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.2</v>
+        <v>51.83</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.6</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.619999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="BR6" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.96</v>
+        <v>6.1</v>
       </c>
       <c r="BZ6" t="n">
-        <v>6.31</v>
+        <v>5.56</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="CC6" t="n">
         <v>4.57</v>
@@ -3240,7 +3240,7 @@
         <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
@@ -3249,58 +3249,58 @@
         <v>2.01</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CN6" t="n">
         <v>1.88</v>
       </c>
-      <c r="CM6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.89</v>
-      </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP6" t="n">
         <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
         <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
@@ -3309,82 +3309,82 @@
         <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="DH6" t="n">
-        <v>69.31</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.23</v>
+        <v>3.57</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.69</v>
+        <v>38.36</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.85</v>
+        <v>13.07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.15</v>
+        <v>10.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.92</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.38</v>
+        <v>47.36</v>
       </c>
       <c r="DW6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>11.07</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.46</v>
+        <v>7.28</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.54</v>
+        <v>3.79</v>
       </c>
       <c r="EA6" t="n">
-        <v>19</v>
+        <v>18.93</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H7" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K7" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>79.43000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>9.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="R7" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AB7" t="n">
         <v>7</v>
       </c>
-      <c r="S7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>62.86</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.57</v>
-      </c>
       <c r="AC7" t="n">
-        <v>19</v>
+        <v>18.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3565,70 +3565,70 @@
         <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BV7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.46</v>
+        <v>6.28</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.34</v>
+        <v>7.12</v>
       </c>
       <c r="CC7" t="n">
         <v>1.42</v>
@@ -3640,146 +3640,146 @@
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DF7" t="n">
         <v>1.36</v>
       </c>
-      <c r="DD7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>1.39</v>
-      </c>
       <c r="DG7" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.15</v>
+        <v>104.07</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DK7" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DM7" t="n">
-        <v>67.61</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.92</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.92</v>
+        <v>7.07</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.85</v>
+        <v>59.28</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.85</v>
+        <v>16.21</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.16</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.69</v>
+        <v>7.36</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.69</v>
+        <v>16.43</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8">
@@ -3789,94 +3789,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>66.14</v>
+        <v>67.12</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="L8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>28.57</v>
+        <v>28.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>9.859999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="R8" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>46.29</v>
+        <v>46.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.289999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.14</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3960,70 +3960,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="BZ8" t="n">
-        <v>4.04</v>
+        <v>3.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC8" t="n">
         <v>2.66</v>
@@ -4032,43 +4032,43 @@
         <v>2.68</v>
       </c>
       <c r="CE8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4083,106 +4083,106 @@
         <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY8" t="n">
         <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DA8" t="n">
         <v>1.87</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="DH8" t="n">
-        <v>67.38</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.23</v>
+        <v>4.15</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>34</v>
+        <v>33.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.23</v>
+        <v>10.36</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.390000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.15</v>
+        <v>50.93</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.77</v>
+        <v>5.71</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.23</v>
+        <v>14.29</v>
       </c>
       <c r="EB8" t="n">
         <v>1.11</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -4685,139 +4685,139 @@
         <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>57.14</v>
+        <v>62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>28.71</v>
+        <v>31.12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.43</v>
+        <v>2.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.29</v>
+        <v>11.88</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.29</v>
+        <v>12.12</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.29</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.71</v>
+        <v>47.38</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.43</v>
+        <v>4.88</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.14</v>
+        <v>14.25</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.38</v>
+        <v>3.86</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV10" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>2.29</v>
@@ -4826,46 +4826,46 @@
         <v>2.23</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.3</v>
+        <v>5.02</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.66</v>
+        <v>5.26</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM10" t="n">
         <v>2.48</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4874,7 +4874,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4889,22 +4889,22 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
@@ -4916,79 +4916,79 @@
         <v>2.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DH10" t="n">
-        <v>63.46</v>
+        <v>65.78</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DM10" t="n">
-        <v>34.92</v>
+        <v>35.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.77</v>
+        <v>10.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.31</v>
+        <v>12.21</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.31</v>
+        <v>8.07</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.15</v>
+        <v>51.22</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.15</v>
+        <v>13.28</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.390000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.77</v>
+        <v>5</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.61</v>
+        <v>15.57</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="11">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5491,139 +5491,139 @@
         <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>73</v>
+        <v>73.62</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.57</v>
+        <v>36.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.43</v>
+        <v>10.12</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.14</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.57</v>
+        <v>5.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="BE12" t="n">
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BN12" t="n">
         <v>2.14</v>
       </c>
-      <c r="BG12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU12" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW12" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>7.28</v>
@@ -5632,169 +5632,169 @@
         <v>7.34</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.93</v>
+        <v>4.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.27</v>
+        <v>5.16</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.41</v>
+        <v>5.26</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.78</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DH12" t="n">
-        <v>66.23</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>31</v>
+        <v>30.64</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.539999999999999</v>
+        <v>9</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.62</v>
+        <v>13.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.31</v>
+        <v>45.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.460000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.62</v>
+        <v>6.14</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.31</v>
+        <v>15.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.14</v>
@@ -5894,118 +5894,118 @@
         <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>107.17</v>
+        <v>105</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AL13" t="n">
-        <v>7.33</v>
+        <v>6.86</v>
       </c>
       <c r="AM13" t="n">
         <v>1</v>
       </c>
       <c r="AN13" t="n">
-        <v>69</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.17</v>
+        <v>12.29</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.33</v>
+        <v>5.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>60.5</v>
+        <v>58.71</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>21.67</v>
+        <v>19.86</v>
       </c>
       <c r="BB13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.67</v>
+        <v>5.86</v>
       </c>
       <c r="BD13" t="n">
-        <v>16.83</v>
+        <v>16</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.54</v>
+        <v>10.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6014,19 +6014,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BV13" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY13" t="n">
         <v>1.19</v>
@@ -6035,55 +6035,55 @@
         <v>1.18</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.59</v>
+        <v>6.4</v>
       </c>
       <c r="CB13" t="n">
-        <v>8.380000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="CF13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CL13" t="n">
         <v>1.57</v>
       </c>
-      <c r="CG13" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CM13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="CP13" t="n">
         <v>1.3</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6091,109 +6091,109 @@
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="CX13" t="n">
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DD13" t="n">
         <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.61</v>
+        <v>3.43</v>
       </c>
       <c r="DH13" t="n">
-        <v>109.85</v>
+        <v>108.57</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.92</v>
+        <v>7.64</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM13" t="n">
-        <v>68.23</v>
+        <v>66.14</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.23</v>
+        <v>10.29</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.31</v>
+        <v>11.93</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.08</v>
+        <v>4.5</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>61.08</v>
+        <v>60.14</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>20.61</v>
+        <v>19.78</v>
       </c>
       <c r="DY13" t="n">
-        <v>13.15</v>
+        <v>12.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7.46</v>
+        <v>7</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.92</v>
+        <v>16.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="14">
@@ -6906,7 +6906,7 @@
         <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY15" t="n">
         <v>1.96</v>
@@ -6915,7 +6915,7 @@
         <v>2.32</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB15" t="n">
         <v>1.25</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>86.29000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="K2" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>46.43</v>
+        <v>50.38</v>
       </c>
       <c r="N2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
-        <v>14.29</v>
+        <v>14.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.71</v>
+        <v>48.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.14</v>
+        <v>13.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AB2" t="n">
         <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AD2" t="n">
         <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
         <v>1.54</v>
@@ -1622,43 +1622,43 @@
         <v>1.58</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
@@ -1700,79 +1700,79 @@
         <v>2.52</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.16</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.23</v>
+        <v>50.36</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.47</v>
+        <v>14.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.77</v>
+        <v>10.79</v>
       </c>
       <c r="DR2" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.69</v>
+        <v>49.64</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.61</v>
+        <v>13.43</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="EA2" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="n">
-        <v>61.71</v>
+        <v>61.88</v>
       </c>
       <c r="I3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>27.86</v>
+        <v>29.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.43</v>
+        <v>10.62</v>
       </c>
       <c r="R3" t="n">
-        <v>8.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.86</v>
+        <v>46.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.29</v>
+        <v>10.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.43</v>
+        <v>21.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.62</v>
+        <v>10.36</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="CC3" t="n">
         <v>9.41</v>
@@ -2025,43 +2025,43 @@
         <v>10.81</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI3" t="n">
         <v>1.84</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CN3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CP3" t="n">
         <v>1.79</v>
       </c>
-      <c r="CO3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>1.77</v>
-      </c>
       <c r="CQ3" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2082,67 +2082,67 @@
         <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
         <v>1.88</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA3" t="n">
         <v>1.95</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>58.38</v>
+        <v>58.72</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DM3" t="n">
-        <v>24.77</v>
+        <v>25.93</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.08</v>
+        <v>11.57</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.77</v>
+        <v>9.15</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.77</v>
+        <v>41.71</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.85</v>
+        <v>8</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.77</v>
+        <v>5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.23</v>
+        <v>17.35</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="H4" t="n">
-        <v>86.67</v>
+        <v>83.14</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="K4" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>47.33</v>
+        <v>45.14</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>13.17</v>
+        <v>13.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.17</v>
+        <v>15.14</v>
       </c>
       <c r="R4" t="n">
-        <v>7.33</v>
+        <v>7.86</v>
       </c>
       <c r="S4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.5</v>
+        <v>48.29</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.67</v>
+        <v>13.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.83</v>
+        <v>15.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.77</v>
+        <v>11.14</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.62</v>
+        <v>3.29</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>2.93</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>3.09</v>
-      </c>
       <c r="CA4" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="CC4" t="n">
         <v>5.97</v>
@@ -2428,67 +2428,67 @@
         <v>6.62</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.54</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL4" t="n">
         <v>1.66</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN4" t="n">
         <v>1.9</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX4" t="n">
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.5</v>
@@ -2497,88 +2497,88 @@
         <v>2.11</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.62</v>
+        <v>72.78</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
         <v>3.07</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.77</v>
+        <v>4.93</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.38</v>
+        <v>43.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="EB4" t="n">
         <v>1.39</v>
       </c>
-      <c r="DP4" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="EC4" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AH5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>2.71</v>
       </c>
-      <c r="AI5" t="n">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.57</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU5" t="n">
+      <c r="BH5" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1.14</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="BR5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>2.67</v>
@@ -2819,55 +2819,55 @@
         <v>2.75</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.52</v>
+        <v>4.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.06</v>
+        <v>5.4</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2912,43 +2912,43 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="DH5" t="n">
-        <v>70.69</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.69</v>
+        <v>29.28</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.15</v>
+        <v>10.79</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.15</v>
+        <v>11.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.31</v>
+        <v>7.64</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.23</v>
+        <v>46.79</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.54</v>
+        <v>10</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.54</v>
+        <v>7.14</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.15</v>
+        <v>17.86</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.83</v>
+        <v>52</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.36</v>
+        <v>47.43</v>
       </c>
       <c r="DW6" t="n">
         <v>0.07000000000000001</v>
@@ -3691,11 +3691,11 @@
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4282,139 +4282,139 @@
         <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.33</v>
+        <v>101.43</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AL9" t="n">
-        <v>7</v>
+        <v>7.71</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>59.17</v>
+        <v>63</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.67</v>
+        <v>11.71</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>63</v>
+        <v>63.57</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>15.29</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.67</v>
+        <v>6.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.17</v>
+        <v>15.57</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.08</v>
+        <v>10.29</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.28</v>
@@ -4423,46 +4423,46 @@
         <v>2.28</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="CE9" t="n">
         <v>1.23</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CH9" t="n">
         <v>1.63</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
         <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
         <v>1.13</v>
@@ -4471,7 +4471,7 @@
         <v>1.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
@@ -4486,22 +4486,22 @@
         <v>1.7</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB9" t="n">
         <v>1.16</v>
@@ -4513,79 +4513,79 @@
         <v>2.27</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>90.61</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.62</v>
+        <v>7</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>54.85</v>
+        <v>57.07</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.39</v>
+        <v>12.36</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.92</v>
+        <v>5.78</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.92</v>
+        <v>63.22</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.46</v>
+        <v>14.64</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.15</v>
+        <v>17.14</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="10">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.43</v>
@@ -5088,52 +5088,52 @@
         <v>1.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AI11" t="n">
-        <v>79.83</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.5</v>
+        <v>44.86</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.17</v>
+        <v>8.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>12.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,82 +5145,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.33</v>
+        <v>49</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.33</v>
+        <v>18.43</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.46</v>
+        <v>3.29</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>4.37</v>
@@ -5229,55 +5229,55 @@
         <v>4.33</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.54</v>
+        <v>4.46</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.65</v>
+        <v>5.2</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.32</v>
+        <v>5.79</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.71</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
@@ -5292,106 +5292,106 @@
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DA11" t="n">
         <v>1.93</v>
       </c>
-      <c r="CZ11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="DA11" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DB11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="DH11" t="n">
-        <v>76.69</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.69</v>
+        <v>41.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.77</v>
+        <v>10.36</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.16</v>
+        <v>12.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.23</v>
+        <v>47.14</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.609999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>5.77</v>
+        <v>6.07</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.84</v>
+        <v>3.71</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.31</v>
+        <v>17.43</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="12">
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>47</v>
+        <v>46.88</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.12</v>
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.86</v>
+        <v>45.79</v>
       </c>
       <c r="DW12" t="n">
         <v>0.21</v>
@@ -6103,13 +6103,13 @@
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DB13" t="n">
         <v>1.1</v>
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="H14" t="n">
-        <v>95.83</v>
+        <v>97.14</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="K14" t="n">
-        <v>9.67</v>
+        <v>9.57</v>
       </c>
       <c r="L14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M14" t="n">
-        <v>67.67</v>
+        <v>63.14</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O14" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="P14" t="n">
-        <v>12.33</v>
+        <v>12.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T14" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="U14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60.17</v>
+        <v>61.86</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.83</v>
+        <v>15.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.67</v>
+        <v>18.57</v>
       </c>
       <c r="AD14" t="n">
         <v>1.81</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
         <v>0.14</v>
@@ -6374,61 +6374,61 @@
         <v>2.43</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.23</v>
+        <v>5.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BZ14" t="n">
         <v>1.37</v>
@@ -6437,7 +6437,7 @@
         <v>4.22</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="CC14" t="n">
         <v>2.91</v>
@@ -6446,43 +6446,43 @@
         <v>2.94</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6524,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.77</v>
+        <v>101.07</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.23</v>
+        <v>7.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.93</v>
+        <v>58.22</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.46</v>
+        <v>12.36</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.38</v>
+        <v>7.07</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>57.62</v>
+        <v>58.64</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.77</v>
+        <v>13.07</v>
       </c>
       <c r="DY14" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.77</v>
+        <v>4.92</v>
       </c>
       <c r="EA14" t="n">
-        <v>16</v>
+        <v>16.14</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6699,136 +6699,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AI15" t="n">
-        <v>71.33</v>
+        <v>78.86</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.33</v>
+        <v>38.71</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>13.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>11</v>
+        <v>11.71</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.83</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.67</v>
+        <v>39.86</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.67</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.83</v>
+        <v>4.57</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.67</v>
+        <v>15.29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.69</v>
+        <v>12</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.23</v>
+        <v>4.79</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.23</v>
+        <v>4.79</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
         <v>2.9</v>
@@ -6837,85 +6837,85 @@
         <v>2.92</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>11.17</v>
+        <v>10.13</v>
       </c>
       <c r="CD15" t="n">
-        <v>14.2</v>
+        <v>12.69</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL15" t="n">
         <v>1.68</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.6</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.32</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DB15" t="n">
         <v>1.25</v>
@@ -6924,82 +6924,82 @@
         <v>1.74</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="DH15" t="n">
-        <v>66</v>
+        <v>70.14</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.46</v>
+        <v>5.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>33.31</v>
+        <v>33.86</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.46</v>
+        <v>14</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.92</v>
+        <v>10.36</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.69</v>
+        <v>7.36</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>39.77</v>
+        <v>40.71</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.31</v>
+        <v>10.86</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.69</v>
+        <v>6.86</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.61</v>
+        <v>4</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.08</v>
+        <v>17.22</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="16">
@@ -7009,94 +7009,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
-        <v>65.83</v>
+        <v>63</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="K16" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M16" t="n">
-        <v>35.83</v>
+        <v>34.71</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O16" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>5.67</v>
+        <v>6.14</v>
       </c>
       <c r="S16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="U16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.17</v>
+        <v>49</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.17</v>
+        <v>14.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.17</v>
+        <v>5.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.17</v>
+        <v>19.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>2.57</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.31</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU16" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CC16" t="n">
         <v>4.74</v>
@@ -7252,13 +7252,13 @@
         <v>4.36</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="CG16" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH16" t="n">
         <v>1.4</v>
@@ -7273,49 +7273,49 @@
         <v>1.38</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
         <v>2.14</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DA16" t="n">
         <v>1.97</v>
@@ -7324,85 +7324,85 @@
         <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DH16" t="n">
-        <v>70.06999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM16" t="n">
-        <v>38</v>
+        <v>37.29</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.23</v>
+        <v>11.36</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.92</v>
+        <v>11.78</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.77</v>
+        <v>7.86</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.31</v>
+        <v>44.14</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.62</v>
+        <v>12.14</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.46</v>
+        <v>17.14</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7505,112 +7505,112 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.33</v>
+        <v>28.14</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.83</v>
+        <v>12.57</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47</v>
+        <v>47.57</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.5</v>
+        <v>10.57</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>11.33</v>
+        <v>13.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BQ17" t="n">
         <v>5</v>
@@ -7619,22 +7619,22 @@
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>3.07</v>
@@ -7643,55 +7643,55 @@
         <v>3.54</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.16</v>
+        <v>3.48</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="CG17" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="CI17" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7733,79 +7733,79 @@
         <v>3.11</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="DN17" t="n">
         <v>0.92</v>
       </c>
-      <c r="DG17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>68.92</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DK17" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="DL17" t="n">
-        <v>-0</v>
-      </c>
-      <c r="DM17" t="n">
-        <v>35</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>0.84</v>
-      </c>
       <c r="DO17" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.61</v>
+        <v>11.64</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.69</v>
+        <v>11.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.85</v>
+        <v>49.93</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.69</v>
+        <v>11.22</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="EA17" t="n">
-        <v>13.69</v>
+        <v>14.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>84.83</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J18" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>4.86</v>
       </c>
       <c r="L18" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M18" t="n">
-        <v>41.33</v>
+        <v>37.57</v>
       </c>
       <c r="N18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O18" t="n">
-        <v>3.33</v>
+        <v>2.86</v>
       </c>
       <c r="P18" t="n">
-        <v>12.17</v>
+        <v>11.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="R18" t="n">
-        <v>9.5</v>
+        <v>10.86</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.67</v>
+        <v>49</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.67</v>
+        <v>10.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC18" t="n">
-        <v>23.5</v>
+        <v>22.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AF18" t="n">
         <v>0.29</v>
@@ -7986,70 +7986,70 @@
         <v>1.71</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.38</v>
+        <v>10.57</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.92</v>
+        <v>5.21</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX18" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY18" t="n">
-        <v>4.34</v>
+        <v>5.12</v>
       </c>
       <c r="BZ18" t="n">
-        <v>4.23</v>
+        <v>5.48</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.21</v>
+        <v>4.43</v>
       </c>
       <c r="CC18" t="n">
         <v>5.01</v>
@@ -8061,154 +8061,154 @@
         <v>1.24</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK18" t="n">
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO18" t="n">
         <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="CT18" t="n">
         <v>3.04</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="DH18" t="n">
-        <v>64.23</v>
+        <v>65</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.08</v>
+        <v>3.86</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>30.38</v>
+        <v>29.28</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.46</v>
+        <v>11.08</v>
       </c>
       <c r="DQ18" t="n">
         <v>12</v>
       </c>
       <c r="DR18" t="n">
-        <v>10</v>
+        <v>10.64</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.54</v>
+        <v>46.5</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.93</v>
+        <v>6.72</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.08</v>
+        <v>19.86</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8308,139 +8308,139 @@
         <v>2.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>63.71</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.83</v>
+        <v>26.86</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.17</v>
+        <v>11.14</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.67</v>
+        <v>53.43</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.33</v>
+        <v>12.14</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.5</v>
+        <v>19.29</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.69</v>
+        <v>8.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
         <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY19" t="n">
         <v>3.03</v>
@@ -8449,25 +8449,25 @@
         <v>3.11</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="CE19" t="n">
         <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CH19" t="n">
         <v>1.5</v>
@@ -8479,13 +8479,13 @@
         <v>1.69</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
         <v>1.85</v>
@@ -8494,28 +8494,28 @@
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8524,7 +8524,7 @@
         <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
@@ -8533,85 +8533,85 @@
         <v>1.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DH19" t="n">
-        <v>69.08</v>
+        <v>68.14</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM19" t="n">
-        <v>31.54</v>
+        <v>31.22</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.23</v>
+        <v>12.14</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.77</v>
+        <v>12.78</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.23</v>
+        <v>52.64</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.53</v>
+        <v>12.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.92</v>
+        <v>18.86</v>
       </c>
       <c r="EB19" t="n">
         <v>1.23</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>54.5</v>
+        <v>54.71</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.17</v>
+        <v>21.57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.17</v>
+        <v>11.14</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.83</v>
+        <v>13.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.5</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>35.83</v>
+        <v>36.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="BB3" t="n">
         <v>3</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.33</v>
+        <v>12.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.36</v>
+        <v>10.07</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.43</v>
+        <v>4.27</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY3" t="n">
         <v>3.47</v>
@@ -2013,16 +2013,16 @@
         <v>3.89</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="CC3" t="n">
-        <v>9.41</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="CD3" t="n">
-        <v>10.81</v>
+        <v>10.09</v>
       </c>
       <c r="CE3" t="n">
         <v>1.23</v>
@@ -2031,16 +2031,16 @@
         <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
         <v>1.38</v>
@@ -2049,31 +2049,31 @@
         <v>1.73</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO3" t="n">
         <v>1.15</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
         <v>1.88</v>
@@ -2091,7 +2091,7 @@
         <v>2.4</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB3" t="n">
         <v>1.31</v>
@@ -2100,7 +2100,7 @@
         <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2109,40 +2109,40 @@
         <v>2.14</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>58.72</v>
+        <v>58.53</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>25.93</v>
+        <v>25.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.57</v>
+        <v>11.87</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.15</v>
+        <v>9.07</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.71</v>
+        <v>41.46</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX3" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DY3" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.35</v>
+        <v>17.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>2.86</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>62.43</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.86</v>
+        <v>40.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.14</v>
+        <v>11.88</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.43</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.71</v>
+        <v>11.12</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.57</v>
+        <v>6.88</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.57</v>
+        <v>17.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.14</v>
+        <v>11.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.57</v>
+        <v>5.13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>2.76</v>
@@ -2416,28 +2416,28 @@
         <v>2.93</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.14</v>
+        <v>5.05</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.97</v>
+        <v>5.46</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.62</v>
+        <v>6.03</v>
       </c>
       <c r="CE4" t="n">
         <v>1.16</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CG4" t="n">
         <v>3.43</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
         <v>2.33</v>
@@ -2452,19 +2452,19 @@
         <v>1.66</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
         <v>1.07</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
@@ -2488,7 +2488,7 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.5</v>
@@ -2500,85 +2500,85 @@
         <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.78</v>
+        <v>73.47</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.07</v>
+        <v>2.87</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.93</v>
+        <v>5.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.5</v>
+        <v>42.67</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.86</v>
+        <v>12.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.86</v>
+        <v>12.67</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.14</v>
+        <v>43.6</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.43</v>
+        <v>7.54</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.14</v>
+        <v>16.87</v>
       </c>
       <c r="EB4" t="n">
         <v>1.39</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="5">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.38</v>
@@ -3882,136 +3882,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="AO8" t="n">
         <v>1</v>
       </c>
-      <c r="AH8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>68.83</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>40.33</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AP8" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>10.71</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.67</v>
+        <v>9.43</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56.83</v>
+        <v>53.86</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.17</v>
+        <v>11.29</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.33</v>
+        <v>6.57</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.67</v>
+        <v>16.43</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.17</v>
+        <v>2.57</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.64</v>
+        <v>4.87</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>3.82</v>
@@ -4020,67 +4020,67 @@
         <v>3.86</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.93</v>
+        <v>4.12</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.68</v>
+        <v>3.51</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="CI8" t="n">
         <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="CT8" t="n">
         <v>3.04</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
         <v>2.13</v>
@@ -4092,97 +4092,97 @@
         <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.27</v>
       </c>
       <c r="DA8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>67</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DO8" t="n">
         <v>1.87</v>
       </c>
-      <c r="DB8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>67.84999999999999</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>33.64</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2</v>
-      </c>
       <c r="DP8" t="n">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.359999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.65</v>
+        <v>9.94</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.93</v>
+        <v>49.93</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>10</v>
+        <v>9.74</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.71</v>
+        <v>5.47</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.29</v>
+        <v>14.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="9">
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4207,46 +4207,46 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="H9" t="n">
-        <v>85.70999999999999</v>
+        <v>91.75</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>51.14</v>
+        <v>52.38</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.14</v>
+        <v>10.5</v>
       </c>
       <c r="R9" t="n">
-        <v>6.43</v>
+        <v>5.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>62.86</v>
+        <v>63</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.71</v>
+        <v>19.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0.29</v>
@@ -4363,70 +4363,70 @@
         <v>1.86</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.29</v>
+        <v>10.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BM9" t="n">
         <v>1.07</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.29</v>
+        <v>4.53</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.66</v>
+        <v>4.73</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.99</v>
+        <v>5.11</v>
       </c>
       <c r="CC9" t="n">
         <v>1.56</v>
@@ -4435,19 +4435,19 @@
         <v>1.57</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.6</v>
@@ -4468,91 +4468,91 @@
         <v>1.13</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="DH9" t="n">
-        <v>93.56999999999999</v>
+        <v>96.27</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="DK9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>57.07</v>
+        <v>57.34</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.36</v>
+        <v>12.33</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.07</v>
+        <v>9.33</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.78</v>
+        <v>5.53</v>
       </c>
       <c r="DS9" t="n">
         <v>0.07000000000000001</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>63.22</v>
+        <v>63.27</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.64</v>
+        <v>14.74</v>
       </c>
       <c r="DY9" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.14</v>
+        <v>17.67</v>
       </c>
       <c r="EB9" t="n">
         <v>1.68</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="10">
@@ -4595,94 +4595,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="H10" t="n">
-        <v>70.83</v>
+        <v>79.14</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>42.17</v>
+        <v>43.29</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.33</v>
+        <v>12.14</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>5.57</v>
       </c>
       <c r="S10" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.33</v>
+        <v>57.14</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.33</v>
+        <v>13.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.17</v>
+        <v>7.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.17</v>
+        <v>5.71</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.33</v>
+        <v>16.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
         <v>0.25</v>
@@ -4766,70 +4766,70 @@
         <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.859999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BV10" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="CC10" t="n">
         <v>5.02</v>
@@ -4841,28 +4841,28 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CH10" t="n">
         <v>1.57</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK10" t="n">
         <v>1.48</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN10" t="n">
         <v>1.94</v>
@@ -4880,115 +4880,115 @@
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.44</v>
       </c>
       <c r="DA10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DH10" t="n">
-        <v>65.78</v>
+        <v>70</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.86</v>
+        <v>36.8</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.65</v>
+        <v>11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.21</v>
+        <v>12.13</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.07</v>
+        <v>7.73</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.22</v>
+        <v>51.93</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.28</v>
+        <v>13.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.289999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.57</v>
+        <v>15.4</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="11">
@@ -5401,94 +5401,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="H12" t="n">
-        <v>58.33</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M12" t="n">
-        <v>23.33</v>
+        <v>30.43</v>
       </c>
       <c r="N12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0.67</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>7.5</v>
+        <v>7.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.17</v>
+        <v>13.57</v>
       </c>
       <c r="R12" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="U12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.33</v>
+        <v>47.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.83</v>
+        <v>10.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.67</v>
+        <v>7.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>15.67</v>
+        <v>16.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.91</v>
+        <v>1.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
         <v>0.12</v>
@@ -5572,70 +5572,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.71</v>
+        <v>11.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.93</v>
+        <v>5.47</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV12" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.28</v>
+        <v>6.77</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.34</v>
+        <v>6.82</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.85</v>
+        <v>4.78</v>
       </c>
       <c r="CC12" t="n">
         <v>5.16</v>
@@ -5644,43 +5644,43 @@
         <v>5.26</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5695,22 +5695,22 @@
         <v>1.57</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX12" t="n">
         <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.33</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB12" t="n">
         <v>1.23</v>
@@ -5719,82 +5719,82 @@
         <v>1.73</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DH12" t="n">
-        <v>67.06999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.29</v>
+        <v>3.67</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
-        <v>30.64</v>
+        <v>33.46</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="DP12" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="DR12" t="n">
         <v>9</v>
       </c>
-      <c r="DQ12" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>8.93</v>
-      </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>45.79</v>
+        <v>47</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.14</v>
+        <v>6.53</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.07</v>
+        <v>15.46</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13">
@@ -7021,7 +7021,7 @@
         <v>0.14</v>
       </c>
       <c r="F16" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="G16" t="n">
         <v>2.14</v>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>5.29</v>
@@ -7096,7 +7096,7 @@
         <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DG16" t="n">
         <v>1.92</v>
@@ -7345,7 +7345,7 @@
         <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DK16" t="n">
         <v>4.71</v>
@@ -7402,7 +7402,7 @@
         <v>1.14</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.38</v>
@@ -1472,46 +1472,46 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="AI2" t="n">
-        <v>86</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.83</v>
+        <v>6.14</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.33</v>
+        <v>52.29</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.67</v>
+        <v>15.14</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.83</v>
+        <v>6.29</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.83</v>
+        <v>51.43</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13</v>
+        <v>13.14</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.33</v>
+        <v>17.86</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.140000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="BR2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY2" t="n">
         <v>1.99</v>
@@ -1610,52 +1610,52 @@
         <v>1.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="CB2" t="n">
         <v>5.01</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CE2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.25</v>
@@ -1673,10 +1673,10 @@
         <v>1.61</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CX2" t="n">
         <v>1.53</v>
@@ -1700,79 +1700,79 @@
         <v>2.52</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.34999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.36</v>
+        <v>51.27</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.72</v>
+        <v>14.93</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.79</v>
+        <v>10.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.78</v>
+        <v>6.94</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.64</v>
+        <v>50</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.43</v>
+        <v>13.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ2" t="n">
         <v>5.14</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.71</v>
+        <v>15.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2600,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>76.5</v>
+        <v>81.86</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2618,64 +2618,64 @@
         <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>30.83</v>
+        <v>32.14</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O5" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="P5" t="n">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="R5" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.33</v>
+        <v>49.86</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>19.83</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.14</v>
+        <v>10.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>4.71</v>
@@ -2831,43 +2831,43 @@
         <v>5.4</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2882,31 +2882,31 @@
         <v>1.43</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2915,73 +2915,73 @@
         <v>0.93</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="DH5" t="n">
-        <v>68.56999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DK5" t="n">
         <v>5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DM5" t="n">
-        <v>29.28</v>
+        <v>30</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.64</v>
+        <v>7.33</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.79</v>
+        <v>47.2</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.14</v>
+        <v>7.13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>17.86</v>
+        <v>18.07</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -3003,61 +3003,61 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>80.5</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>45.5</v>
+        <v>44.29</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>14.83</v>
+        <v>14.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="R6" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="T6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52</v>
+        <v>49.57</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3066,19 +3066,19 @@
         <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.789999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.79</v>
+        <v>1.07</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="BR6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.1</v>
+        <v>6.23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.56</v>
+        <v>5.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="CC6" t="n">
         <v>4.57</v>
@@ -3237,10 +3237,10 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
@@ -3255,31 +3255,31 @@
         <v>1.51</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN6" t="n">
         <v>1.88</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CU6" t="n">
         <v>1.53</v>
@@ -3288,103 +3288,103 @@
         <v>2.04</v>
       </c>
       <c r="CW6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DC6" t="n">
         <v>1.79</v>
       </c>
-      <c r="CX6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="DD6" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DH6" t="n">
-        <v>72.06999999999999</v>
+        <v>73.66</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.36</v>
+        <v>38.27</v>
       </c>
       <c r="DN6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DO6" t="n">
         <v>1.14</v>
       </c>
-      <c r="DO6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="DP6" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.42</v>
+        <v>10.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.43</v>
+        <v>46.6</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.07</v>
+        <v>11.2</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.28</v>
+        <v>7.46</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.93</v>
+        <v>18.47</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
         <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.5</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.83</v>
+        <v>52.57</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.83</v>
+        <v>9.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.33</v>
+        <v>56.71</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.83</v>
+        <v>16.71</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.83</v>
+        <v>7.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="BE7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.07</v>
+        <v>10.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BL7" t="n">
         <v>0.93</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BM7" t="n">
         <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.93</v>
       </c>
       <c r="BN7" t="n">
         <v>1.93</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.64</v>
+        <v>4.93</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>1.31</v>
@@ -3625,40 +3625,40 @@
         <v>1.34</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.28</v>
+        <v>6.18</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CE7" t="n">
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM7" t="n">
         <v>2.69</v>
@@ -3670,116 +3670,116 @@
         <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW7" t="n">
         <v>1.72</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="DE7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="DH7" t="n">
-        <v>104.07</v>
+        <v>101.4</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>65.06999999999999</v>
+        <v>63.73</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.07</v>
+        <v>7.2</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.28</v>
+        <v>59.26</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.21</v>
+        <v>16.2</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.43</v>
+        <v>16.4</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -4264,10 +4264,10 @@
         <v>0.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.25</v>
+        <v>14.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.119999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB9" t="n">
         <v>5.12</v>
@@ -4276,7 +4276,7 @@
         <v>19.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
@@ -4570,10 +4570,10 @@
         <v>0.34</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.74</v>
+        <v>14.8</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.130000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ9" t="n">
         <v>5.6</v>
@@ -4582,7 +4582,7 @@
         <v>17.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
         <v>1.73</v>
@@ -4998,94 +4998,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="H11" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K11" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M11" t="n">
-        <v>38.14</v>
+        <v>38.75</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="P11" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.29</v>
+        <v>13.88</v>
       </c>
       <c r="R11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.29</v>
+        <v>45.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.710000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>5.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.43</v>
+        <v>16.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.14</v>
@@ -5169,70 +5169,70 @@
         <v>1.57</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.37</v>
+        <v>4.56</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="CC11" t="n">
         <v>5.2</v>
@@ -5244,22 +5244,22 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.71</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL11" t="n">
         <v>2</v>
@@ -5268,16 +5268,16 @@
         <v>2.41</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO11" t="n">
         <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CR11" t="n">
         <v>1.38</v>
@@ -5292,7 +5292,7 @@
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW11" t="n">
         <v>1.76</v>
@@ -5319,79 +5319,79 @@
         <v>3.05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>80.34999999999999</v>
+        <v>79.66</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.36</v>
+        <v>10.27</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.72</v>
+        <v>13.07</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.14</v>
+        <v>47</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.779999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.07</v>
+        <v>6.47</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.43</v>
+        <v>17.46</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -5804,94 +5804,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="n">
-        <v>112.14</v>
+        <v>111.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K13" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M13" t="n">
-        <v>67.56999999999999</v>
+        <v>65.88</v>
       </c>
       <c r="N13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
-        <v>10.29</v>
+        <v>10.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="R13" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="S13" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>61.57</v>
+        <v>61.38</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.71</v>
+        <v>19</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.57</v>
+        <v>11.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.140000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>17</v>
+        <v>16.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
         <v>0.29</v>
@@ -5975,37 +5975,37 @@
         <v>1.71</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.43</v>
+        <v>10.53</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BM13" t="n">
         <v>1.07</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6014,31 +6014,31 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU13" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BV13" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BW13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.4</v>
+        <v>6.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>8.09</v>
+        <v>7.9</v>
       </c>
       <c r="CC13" t="n">
         <v>1.61</v>
@@ -6047,19 +6047,19 @@
         <v>1.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CH13" t="n">
         <v>1.66</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.62</v>
@@ -6071,30 +6071,30 @@
         <v>1.57</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW13" t="n">
         <v>1.7</v>
@@ -6103,97 +6103,97 @@
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.57</v>
+        <v>108.33</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DM13" t="n">
-        <v>66.14</v>
+        <v>65.33</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.29</v>
+        <v>10.4</v>
       </c>
       <c r="DQ13" t="n">
         <v>11.93</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.14</v>
+        <v>60.13</v>
       </c>
       <c r="DW13" t="n">
         <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>19.78</v>
+        <v>19.4</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.78</v>
+        <v>12.53</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7</v>
+        <v>6.87</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.5</v>
+        <v>16.47</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.43</v>
@@ -6293,139 +6293,139 @@
         <v>1.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>105</v>
+        <v>107.25</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>53.29</v>
+        <v>55.12</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.57</v>
+        <v>11.75</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.14</v>
+        <v>10.38</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>55.43</v>
+        <v>56.62</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.86</v>
+        <v>7.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.79</v>
+        <v>10.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.57</v>
+        <v>0.87</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.43</v>
+        <v>5.2</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.29</v>
+        <v>5.13</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>1.39</v>
@@ -6434,85 +6434,85 @@
         <v>1.37</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.91</v>
+        <v>2.72</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="CL14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CN14" t="n">
         <v>1.27</v>
       </c>
-      <c r="CM14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="CO14" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CT14" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="CU14" t="n">
         <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB14" t="n">
         <v>1.21</v>
@@ -6524,79 +6524,79 @@
         <v>2.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
       <c r="DH14" t="n">
-        <v>101.07</v>
+        <v>102.53</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.36</v>
+        <v>7.07</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>58.22</v>
+        <v>58.86</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.36</v>
+        <v>11.93</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DR14" t="n">
         <v>7.07</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.64</v>
+        <v>59.07</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.07</v>
+        <v>13.13</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.14</v>
+        <v>15.93</v>
       </c>
       <c r="EB14" t="n">
         <v>1.6</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="15">
@@ -6606,61 +6606,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="G15" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="n">
-        <v>61.43</v>
+        <v>68.75</v>
       </c>
       <c r="I15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>35.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>14.29</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="R15" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6672,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.57</v>
+        <v>43.88</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.71</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.14</v>
+        <v>18.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6777,70 @@
         <v>1.29</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>12</v>
+        <v>11.87</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.79</v>
+        <v>4.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.79</v>
+        <v>4.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.86</v>
+        <v>4.76</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.55</v>
+        <v>5.43</v>
       </c>
       <c r="CC15" t="n">
         <v>10.13</v>
@@ -6849,13 +6849,13 @@
         <v>12.69</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH15" t="n">
         <v>1.31</v>
@@ -6864,55 +6864,55 @@
         <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="CV15" t="n">
         <v>2</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA15" t="n">
         <v>1.9</v>
@@ -6921,52 +6921,52 @@
         <v>1.25</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="DH15" t="n">
-        <v>70.14</v>
+        <v>73.47</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>37</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DO15" t="n">
         <v>1.93</v>
       </c>
-      <c r="DK15" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DP15" t="n">
-        <v>14</v>
+        <v>14.13</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.36</v>
+        <v>10.53</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.36</v>
+        <v>7.07</v>
       </c>
       <c r="DS15" t="n">
         <v>0.07000000000000001</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>40.71</v>
+        <v>42</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.86</v>
+        <v>11.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.86</v>
+        <v>7.6</v>
       </c>
       <c r="DZ15" t="n">
         <v>4</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.22</v>
+        <v>17.14</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.14</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>73.70999999999999</v>
+        <v>73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AN16" t="n">
-        <v>39.86</v>
+        <v>40</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.43</v>
+        <v>10.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.57</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>39.29</v>
+        <v>39.38</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.14</v>
+        <v>6.75</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.14</v>
+        <v>15.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>10</v>
+        <v>10.13</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ16" t="n">
         <v>4.93</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7240,16 +7240,16 @@
         <v>2.36</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.11</v>
+        <v>4.19</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.36</v>
+        <v>4.6</v>
       </c>
       <c r="CE16" t="n">
         <v>1.2</v>
@@ -7258,52 +7258,52 @@
         <v>2.26</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CI16" t="n">
         <v>2.05</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK16" t="n">
         <v>1.38</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CO16" t="n">
         <v>1.12</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CT16" t="n">
         <v>3.08</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW16" t="n">
         <v>1.72</v>
@@ -7312,97 +7312,97 @@
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.41</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB16" t="n">
         <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="DE16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DH16" t="n">
-        <v>68.34999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
         <v>2.86</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.71</v>
+        <v>4.74</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.29</v>
+        <v>37.53</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.36</v>
+        <v>11.4</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.14</v>
+        <v>43.87</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.14</v>
+        <v>11.8</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.140000000000001</v>
+        <v>7.87</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.14</v>
+        <v>17.07</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7502,139 +7502,139 @@
         <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>66.43000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>28.14</v>
+        <v>28.88</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.57</v>
+        <v>12.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.140000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>47.57</v>
+        <v>46.62</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>5.62</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.57</v>
+        <v>5.12</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN17" t="n">
         <v>2.07</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY17" t="n">
         <v>3.07</v>
@@ -7643,31 +7643,31 @@
         <v>3.54</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="CE17" t="n">
         <v>1.25</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.62</v>
@@ -7676,13 +7676,13 @@
         <v>1.42</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO17" t="n">
         <v>1.15</v>
@@ -7697,115 +7697,115 @@
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CT17" t="n">
         <v>3.02</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW17" t="n">
         <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB17" t="n">
         <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="DH17" t="n">
-        <v>70.22</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="DL17" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.29</v>
+        <v>35.2</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.64</v>
+        <v>11.74</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.14</v>
+        <v>11.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.79</v>
+        <v>8.4</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.93</v>
+        <v>49.27</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.22</v>
+        <v>11.27</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.14</v>
+        <v>6.87</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.07</v>
+        <v>4.4</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,139 +7905,139 @@
         <v>2.43</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>46.57</v>
+        <v>50.12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.86</v>
+        <v>3.38</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.86</v>
+        <v>10.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.71</v>
+        <v>11.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44</v>
+        <v>44.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.14</v>
+        <v>17.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.57</v>
+        <v>10.67</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.21</v>
+        <v>5.4</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY18" t="n">
         <v>5.12</v>
@@ -8046,55 +8046,55 @@
         <v>5.48</v>
       </c>
       <c r="CA18" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.01</v>
+        <v>4.91</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CH18" t="n">
         <v>1.33</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK18" t="n">
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8109,103 +8109,103 @@
         <v>1.51</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CX18" t="n">
         <v>1.7</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="DH18" t="n">
-        <v>65</v>
+        <v>65.66</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.86</v>
+        <v>4.07</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>29.28</v>
+        <v>28.87</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.64</v>
+        <v>10.6</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.5</v>
+        <v>46.54</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX18" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.72</v>
+        <v>6.53</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.86</v>
+        <v>19.87</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="EC18" t="n">
         <v>2.07</v>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -8230,46 +8230,46 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="H19" t="n">
-        <v>72.56999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="K19" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="L19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M19" t="n">
-        <v>35.57</v>
+        <v>35</v>
       </c>
       <c r="N19" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>13.14</v>
+        <v>12.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.71</v>
+        <v>12.5</v>
       </c>
       <c r="R19" t="n">
-        <v>8.289999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>51.86</v>
+        <v>50.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.71</v>
+        <v>12.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.43</v>
+        <v>18</v>
       </c>
       <c r="AD19" t="n">
         <v>1.37</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
         <v>0.43</v>
@@ -8392,67 +8392,67 @@
         <v>3.07</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.5</v>
+        <v>8.73</v>
       </c>
       <c r="BI19" t="n">
         <v>3.07</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.36</v>
+        <v>3.73</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.03</v>
+        <v>3.44</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.23</v>
+        <v>4.3</v>
       </c>
       <c r="CC19" t="n">
         <v>2.78</v>
@@ -8464,52 +8464,52 @@
         <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="CH19" t="n">
         <v>1.5</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CT19" t="n">
         <v>3.11</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV19" t="n">
         <v>2.13</v>
@@ -8521,64 +8521,64 @@
         <v>1.57</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.38</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB19" t="n">
         <v>1.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="DH19" t="n">
-        <v>68.14</v>
+        <v>67.33</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM19" t="n">
-        <v>31.22</v>
+        <v>31.2</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.14</v>
+        <v>11.93</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.78</v>
+        <v>12.67</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DS19" t="n">
         <v>0.14</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.64</v>
+        <v>51.87</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="DY19" t="n">
-        <v>8</v>
+        <v>7.93</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.86</v>
+        <v>18.6</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="H2" t="n">
-        <v>86.62</v>
+        <v>85.44</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="K2" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="L2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>50.38</v>
+        <v>48.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="P2" t="n">
-        <v>14.75</v>
+        <v>14.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.75</v>
+        <v>48.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.75</v>
+        <v>8.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.75</v>
+        <v>14.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.27</v>
+        <v>9.31</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="CC2" t="n">
         <v>1.53</v>
@@ -1622,43 +1622,43 @@
         <v>1.56</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CP2" t="n">
         <v>1.57</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
@@ -1673,106 +1673,106 @@
         <v>1.61</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX2" t="n">
         <v>1.53</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.40000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.27</v>
+        <v>50.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.67</v>
+        <v>11.06</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>50</v>
+        <v>49.88</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.47</v>
+        <v>13.62</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.14</v>
+        <v>5.37</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.67</v>
+        <v>15.87</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
-        <v>61.88</v>
+        <v>59.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>29.5</v>
+        <v>29.11</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="P3" t="n">
-        <v>8.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.62</v>
+        <v>10.89</v>
       </c>
       <c r="R3" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.12</v>
+        <v>46.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.25</v>
+        <v>10.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.12</v>
+        <v>21.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="BQ3" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CA3" t="n">
         <v>4.27</v>
       </c>
-      <c r="BR3" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>4.35</v>
-      </c>
       <c r="CB3" t="n">
-        <v>5.05</v>
+        <v>4.94</v>
       </c>
       <c r="CC3" t="n">
         <v>8.970000000000001</v>
@@ -2025,58 +2025,58 @@
         <v>10.09</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CN3" t="n">
         <v>1.82</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW3" t="n">
         <v>1.93</v>
@@ -2097,52 +2097,52 @@
         <v>1.31</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DH3" t="n">
-        <v>58.53</v>
+        <v>57.18</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>25.8</v>
+        <v>25.81</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.73</v>
+        <v>9.81</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.87</v>
+        <v>11.94</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.07</v>
+        <v>9.19</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.46</v>
+        <v>42.12</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.94</v>
+        <v>8</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.87</v>
+        <v>4.94</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.07</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.2</v>
+        <v>17.69</v>
       </c>
       <c r="EB3" t="n">
         <v>0.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="H4" t="n">
-        <v>83.14</v>
+        <v>85.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>45.14</v>
+        <v>47.38</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="P4" t="n">
-        <v>13.57</v>
+        <v>13.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.14</v>
+        <v>15.5</v>
       </c>
       <c r="R4" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.29</v>
+        <v>49.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.29</v>
+        <v>14.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.289999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>15.71</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>2.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.6</v>
+        <v>11.44</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.93</v>
+        <v>3.19</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="CC4" t="n">
         <v>5.46</v>
@@ -2428,10 +2428,10 @@
         <v>6.03</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CG4" t="n">
         <v>3.43</v>
@@ -2452,34 +2452,34 @@
         <v>1.66</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CP4" t="n">
         <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CR4" t="n">
         <v>1.32</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CT4" t="n">
         <v>3.26</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW4" t="n">
         <v>1.58</v>
@@ -2488,13 +2488,13 @@
         <v>1.51</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.5</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>
@@ -2509,76 +2509,76 @@
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.47</v>
+        <v>75.25</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.67</v>
+        <v>43.94</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.67</v>
+        <v>12.57</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.6</v>
+        <v>44.44</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.13</v>
+        <v>12.62</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.54</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.87</v>
+        <v>17.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -3789,94 +3789,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="H8" t="n">
-        <v>67.12</v>
+        <v>65.56</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="K8" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="L8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>28.62</v>
+        <v>28.89</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="P8" t="n">
-        <v>10.12</v>
+        <v>10.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.5</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>10.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>46.5</v>
+        <v>46.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>12.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3960,70 +3960,70 @@
         <v>2.57</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.73</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.87</v>
+        <v>4.81</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.87</v>
+        <v>4.81</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="BZ8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="CA8" t="n">
         <v>3.86</v>
       </c>
-      <c r="CA8" t="n">
-        <v>3.89</v>
-      </c>
       <c r="CB8" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CC8" t="n">
         <v>3.35</v>
@@ -4032,43 +4032,43 @@
         <v>3.51</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="CP8" t="n">
         <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4077,28 +4077,28 @@
         <v>2.51</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CU8" t="n">
         <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX8" t="n">
         <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.27</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
@@ -4107,82 +4107,82 @@
         <v>1.76</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DH8" t="n">
-        <v>67</v>
+        <v>66.13</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.86</v>
+        <v>32.75</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.53</v>
+        <v>10.88</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.94</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.93</v>
+        <v>49.94</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.33</v>
+        <v>14.38</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="9">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.43</v>
@@ -4685,139 +4685,139 @@
         <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
         <v>62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN10" t="n">
-        <v>31.12</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>47.38</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL10" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX10" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
         <v>2.19</v>
@@ -4826,16 +4826,16 @@
         <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.26</v>
+        <v>5.4</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
@@ -4844,16 +4844,16 @@
         <v>2.31</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
         <v>1.57</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK10" t="n">
         <v>1.48</v>
@@ -4862,10 +4862,10 @@
         <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4874,7 +4874,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4898,97 +4898,97 @@
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF10" t="n">
         <v>1.13</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DH10" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.67</v>
+        <v>4.38</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.8</v>
+        <v>35.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DO10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="EC10" t="n">
         <v>2</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>11</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>51.93</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="EB10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="EC10" t="n">
-        <v>2.07</v>
       </c>
     </row>
     <row r="11">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.38</v>
@@ -5088,52 +5088,52 @@
         <v>1.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>86.70999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.86</v>
+        <v>42.88</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,82 +5145,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49</v>
+        <v>48.25</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.43</v>
+        <v>17.12</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.73</v>
+        <v>9.69</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU11" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>4.56</v>
@@ -5229,169 +5229,169 @@
         <v>4.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.79</v>
+        <v>5.53</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.22</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CX11" t="n">
         <v>1.61</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.32</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DG11" t="n">
         <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>79.66</v>
+        <v>78.88</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="DL11" t="n">
         <v>0.06</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.6</v>
+        <v>40.82</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.27</v>
+        <v>10.82</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.07</v>
+        <v>12.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.34</v>
+        <v>9.44</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47</v>
+        <v>46.75</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.07</v>
+        <v>10.12</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.47</v>
+        <v>6.38</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.46</v>
+        <v>16.87</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.14</v>
@@ -5491,139 +5491,139 @@
         <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>73.62</v>
+        <v>72.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.12</v>
+        <v>36.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.12</v>
+        <v>10.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>12.89</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.88</v>
+        <v>46.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.62</v>
+        <v>15.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.2</v>
+        <v>11.38</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.47</v>
+        <v>5.31</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.87</v>
+        <v>5.25</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX12" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY12" t="n">
         <v>6.77</v>
@@ -5632,169 +5632,169 @@
         <v>6.82</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.16</v>
+        <v>5.26</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.26</v>
+        <v>5.36</v>
       </c>
       <c r="CE12" t="n">
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CH12" t="n">
         <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU12" t="n">
         <v>1.57</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX12" t="n">
         <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.33</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>70.40000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.46</v>
+        <v>33.94</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.07</v>
+        <v>9.25</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.53</v>
+        <v>13.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47</v>
+        <v>46.68</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.66</v>
+        <v>9.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="EA12" t="n">
-        <v>15.46</v>
+        <v>16.06</v>
       </c>
       <c r="EB12" t="n">
         <v>1.03</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5894,118 +5894,118 @@
         <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>105</v>
+        <v>102.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AN13" t="n">
-        <v>64.70999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.29</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.14</v>
+        <v>5.62</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>58.71</v>
+        <v>59</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>19.86</v>
+        <v>19.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="BD13" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.53</v>
+        <v>10.44</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.8</v>
+        <v>5.62</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
@@ -6014,19 +6014,19 @@
         <v>100</v>
       </c>
       <c r="BT13" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU13" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BV13" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY13" t="n">
         <v>1.21</v>
@@ -6035,69 +6035,69 @@
         <v>1.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.31</v>
+        <v>6.38</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="CE13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="CH13" t="n">
         <v>1.66</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CP13" t="n">
         <v>1.31</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
         <v>1.57</v>
@@ -6115,85 +6115,85 @@
         <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.33</v>
+        <v>107</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DM13" t="n">
-        <v>65.33</v>
+        <v>66.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.4</v>
+        <v>10.44</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.93</v>
+        <v>11.56</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.47</v>
+        <v>4.75</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.13</v>
+        <v>60.19</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>19.4</v>
+        <v>19.06</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.53</v>
+        <v>12.38</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.87</v>
+        <v>6.68</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.47</v>
+        <v>16.31</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="14">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6699,136 +6699,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AI15" t="n">
-        <v>78.86</v>
+        <v>74.62</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.71</v>
+        <v>38.12</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.71</v>
+        <v>11.62</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>39.86</v>
+        <v>40.88</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>11.12</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.43</v>
+        <v>6.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.29</v>
+        <v>16.25</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.87</v>
+        <v>11.69</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
         <v>3.03</v>
@@ -6837,73 +6837,73 @@
         <v>3.07</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.76</v>
+        <v>4.66</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.43</v>
+        <v>5.29</v>
       </c>
       <c r="CC15" t="n">
-        <v>10.13</v>
+        <v>9.19</v>
       </c>
       <c r="CD15" t="n">
-        <v>12.69</v>
+        <v>11.46</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH15" t="n">
         <v>1.31</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.79</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CV15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.59</v>
@@ -6918,88 +6918,88 @@
         <v>1.9</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="DG15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>8</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="EC15" t="n">
         <v>1.87</v>
-      </c>
-      <c r="DH15" t="n">
-        <v>73.47</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>37</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>14.13</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>42</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>4</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>1.73</v>
       </c>
     </row>
     <row r="16">
@@ -7009,94 +7009,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>63</v>
+        <v>70.62</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M16" t="n">
-        <v>34.71</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.14</v>
-      </c>
       <c r="P16" t="n">
-        <v>12.29</v>
+        <v>11.75</v>
       </c>
       <c r="Q16" t="n">
         <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>6.14</v>
+        <v>5.75</v>
       </c>
       <c r="S16" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="T16" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>49</v>
+        <v>50.12</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.86</v>
+        <v>15.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.140000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.14</v>
+        <v>20.62</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>2.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.13</v>
+        <v>10.38</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.93</v>
+        <v>5.31</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="CC16" t="n">
         <v>5.06</v>
@@ -7252,16 +7252,16 @@
         <v>4.6</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI16" t="n">
         <v>2.05</v>
@@ -7273,46 +7273,46 @@
         <v>1.38</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CO16" t="n">
         <v>1.12</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.41</v>
@@ -7321,88 +7321,88 @@
         <v>1.99</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="DH16" t="n">
-        <v>68.33</v>
+        <v>71.81</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM16" t="n">
-        <v>37.53</v>
+        <v>41.19</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.87</v>
+        <v>7.56</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.87</v>
+        <v>44.75</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.8</v>
+        <v>12.25</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.87</v>
+        <v>8.25</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.07</v>
+        <v>17.94</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="17">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
-        <v>83.43000000000001</v>
+        <v>78.88</v>
       </c>
       <c r="I18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="K18" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="L18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M18" t="n">
-        <v>37.57</v>
+        <v>37.88</v>
       </c>
       <c r="N18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>11.29</v>
+        <v>10.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.29</v>
+        <v>12.12</v>
       </c>
       <c r="R18" t="n">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>49</v>
+        <v>47.75</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.57</v>
+        <v>22</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
         <v>0.25</v>
@@ -7986,70 +7986,70 @@
         <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.67</v>
+        <v>10.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT18" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX18" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
-        <v>5.12</v>
+        <v>5.92</v>
       </c>
       <c r="BZ18" t="n">
-        <v>5.48</v>
+        <v>6.37</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.94</v>
+        <v>4.15</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.36</v>
+        <v>4.59</v>
       </c>
       <c r="CC18" t="n">
         <v>4.91</v>
@@ -8058,61 +8058,61 @@
         <v>5.09</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK18" t="n">
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="CT18" t="n">
         <v>3.04</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX18" t="n">
         <v>1.7</v>
@@ -8127,88 +8127,88 @@
         <v>1.77</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="DH18" t="n">
-        <v>65.66</v>
+        <v>64.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>28.87</v>
+        <v>29.56</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>11</v>
+        <v>10.68</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.93</v>
+        <v>11.87</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.6</v>
+        <v>10.44</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.54</v>
+        <v>46.06</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.53</v>
+        <v>6.44</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.87</v>
+        <v>19.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8308,139 +8308,139 @@
         <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>63.71</v>
+        <v>60.12</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>26.86</v>
+        <v>27.38</v>
       </c>
       <c r="AO19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>53</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BM19" t="n">
         <v>1</v>
       </c>
-      <c r="AP19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>12.86</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>53.43</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BN19" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY19" t="n">
         <v>3.44</v>
@@ -8449,19 +8449,19 @@
         <v>3.58</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF19" t="n">
         <v>2.45</v>
@@ -8473,7 +8473,7 @@
         <v>1.5</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.68</v>
@@ -8497,7 +8497,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
@@ -8512,10 +8512,10 @@
         <v>1.5</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX19" t="n">
         <v>1.57</v>
@@ -8524,10 +8524,10 @@
         <v>1.93</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB19" t="n">
         <v>1.22</v>
@@ -8539,79 +8539,79 @@
         <v>2.74</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH19" t="n">
-        <v>67.33</v>
+        <v>65.31</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM19" t="n">
-        <v>31.2</v>
+        <v>31.19</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.93</v>
+        <v>12.06</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.67</v>
+        <v>12.88</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.87</v>
+        <v>51.75</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.4</v>
+        <v>12.06</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.93</v>
+        <v>7.75</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.6</v>
+        <v>18.56</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
         <v>1.56</v>
@@ -1806,7 +1806,7 @@
         <v>0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="K3" t="n">
         <v>5</v>
@@ -1869,7 +1869,7 @@
         <v>0.98</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DG3" t="n">
         <v>1.88</v>
@@ -2118,7 +2118,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="DK3" t="n">
         <v>4.19</v>
@@ -2175,7 +2175,7 @@
         <v>0.84</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,46 +2681,46 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>62.62</v>
+        <v>59.33</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL5" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>28.12</v>
+        <v>26.11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.88</v>
+        <v>10.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44.88</v>
+        <v>43.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.38</v>
+        <v>16.44</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BF5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BN5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
         <v>2.54</v>
@@ -2819,70 +2819,70 @@
         <v>2.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.98</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.71</v>
+        <v>5.47</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.4</v>
+        <v>6.44</v>
       </c>
       <c r="CE5" t="n">
         <v>1.19</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
         <v>1.31</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="CO5" t="n">
         <v>1.12</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="CT5" t="n">
         <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW5" t="n">
         <v>1.92</v>
@@ -2891,97 +2891,97 @@
         <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.61</v>
+        <v>3.48</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DH5" t="n">
-        <v>71.59999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DK5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM5" t="n">
-        <v>30</v>
+        <v>28.75</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.8</v>
+        <v>10.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.33</v>
+        <v>7.75</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>47.2</v>
+        <v>46.38</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.93</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DY5" t="n">
         <v>7.13</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.07</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,55 +3084,55 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>65.75</v>
+        <v>59.56</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>33</v>
+        <v>32.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.75</v>
+        <v>11.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -3141,79 +3141,79 @@
         <v>44</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.88</v>
+        <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.529999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="BO6" t="n">
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BR6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>6.23</v>
@@ -3222,16 +3222,16 @@
         <v>5.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.57</v>
+        <v>4.51</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
@@ -3240,10 +3240,10 @@
         <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI6" t="n">
         <v>2.01</v>
@@ -3252,25 +3252,25 @@
         <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3288,19 +3288,19 @@
         <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.31</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3315,76 +3315,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="DH6" t="n">
-        <v>73.66</v>
+        <v>69.69</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.27</v>
+        <v>37.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DP6" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.13</v>
+        <v>10.06</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.33</v>
+        <v>7.93</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.6</v>
+        <v>46.44</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.46</v>
+        <v>7.31</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.47</v>
+        <v>18.56</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="H7" t="n">
-        <v>112</v>
+        <v>102.11</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>73.5</v>
+        <v>66.56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="O7" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="P7" t="n">
-        <v>9.380000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.12</v>
+        <v>9.56</v>
       </c>
       <c r="R7" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.75</v>
+        <v>16.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.75</v>
+        <v>9.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.25</v>
+        <v>17.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3565,70 +3565,70 @@
         <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.2</v>
+        <v>10.06</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.93</v>
+        <v>4.69</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.18</v>
+        <v>6.32</v>
       </c>
       <c r="CB7" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="CC7" t="n">
         <v>1.41</v>
@@ -3643,28 +3643,28 @@
         <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO7" t="n">
         <v>1.08</v>
@@ -3673,7 +3673,7 @@
         <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
@@ -3684,18 +3684,18 @@
         <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
@@ -3704,82 +3704,82 @@
         <v>1.36</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.4</v>
+        <v>96.5</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DK7" t="n">
         <v>6.87</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>63.73</v>
+        <v>60.44</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.2</v>
+        <v>7.06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.26</v>
+        <v>59.69</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.2</v>
+        <v>16.37</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.4</v>
+        <v>7.25</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="EB7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="8">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4282,139 +4282,139 @@
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI9" t="n">
-        <v>101.43</v>
+        <v>95.25</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.71</v>
+        <v>7.12</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>63</v>
+        <v>56.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.71</v>
+        <v>11.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>8</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.14</v>
+        <v>6.12</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>63.57</v>
+        <v>61.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.29</v>
+        <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.33</v>
+        <v>10.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.16</v>
@@ -4423,34 +4423,34 @@
         <v>2.15</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CH9" t="n">
         <v>1.64</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK9" t="n">
         <v>1.45</v>
@@ -4459,25 +4459,25 @@
         <v>1.94</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO9" t="n">
         <v>1.13</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
@@ -4486,10 +4486,10 @@
         <v>1.71</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
@@ -4507,85 +4507,85 @@
         <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.27</v>
+        <v>93.5</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.2</v>
+        <v>6.94</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM9" t="n">
-        <v>57.34</v>
+        <v>54.63</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.33</v>
+        <v>12.13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.33</v>
+        <v>9.56</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.53</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>63.27</v>
+        <v>62.06</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.8</v>
+        <v>14.44</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.6</v>
+        <v>5.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.67</v>
+        <v>17.38</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10">
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="H14" t="n">
-        <v>97.14</v>
+        <v>88.12</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="K14" t="n">
-        <v>9.57</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>63.14</v>
+        <v>57.62</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="P14" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>61.86</v>
+        <v>61.12</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.14</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.71</v>
+        <v>5.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.57</v>
+        <v>18.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6374,70 +6374,70 @@
         <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.4</v>
+        <v>10.25</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU14" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="CC14" t="n">
         <v>2.72</v>
@@ -6446,61 +6446,61 @@
         <v>2.74</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CP14" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CT14" t="n">
         <v>3.06</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6515,88 +6515,88 @@
         <v>1.93</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.53</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.07</v>
+        <v>6.94</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM14" t="n">
-        <v>58.86</v>
+        <v>56.37</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.93</v>
+        <v>12.07</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.07</v>
+        <v>6.82</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.07</v>
+        <v>58.87</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.13</v>
+        <v>12.94</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>15.93</v>
+        <v>16.18</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="15">
@@ -6699,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AH15" t="n">
         <v>1.88</v>
@@ -6711,7 +6711,7 @@
         <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>5.25</v>
@@ -6774,7 +6774,7 @@
         <v>1.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BG15" t="n">
         <v>3.25</v>
@@ -6930,7 +6930,7 @@
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="DG15" t="n">
         <v>1.88</v>
@@ -6942,7 +6942,7 @@
         <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
         <v>5.75</v>
@@ -6999,7 +6999,7 @@
         <v>1.23</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="H17" t="n">
-        <v>74</v>
+        <v>66.62</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K17" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="L17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>42.43</v>
+        <v>41.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="P17" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
         <v>11</v>
       </c>
-      <c r="Q17" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>11.86</v>
-      </c>
       <c r="AA17" t="n">
-        <v>8.289999999999999</v>
+        <v>7.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>15.71</v>
+        <v>16.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7583,70 +7583,70 @@
         <v>2.12</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC17" t="n">
         <v>3.06</v>
@@ -7655,43 +7655,43 @@
         <v>3.28</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH17" t="n">
         <v>1.34</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP17" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7706,106 +7706,106 @@
         <v>1.43</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW17" t="n">
         <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB17" t="n">
         <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>70.73999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.47</v>
+        <v>3.68</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.2</v>
+        <v>35.06</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DO17" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.74</v>
+        <v>11.57</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.33</v>
+        <v>11.18</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.4</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.27</v>
+        <v>49.68</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.27</v>
+        <v>10.88</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.87</v>
+        <v>6.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.33</v>
+        <v>14.68</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1475,133 +1475,133 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>88.29000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.29</v>
+        <v>50.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.14</v>
+        <v>15.62</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.43</v>
+        <v>51</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.14</v>
+        <v>12.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.86</v>
+        <v>7.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.86</v>
+        <v>17.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.31</v>
+        <v>9.18</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY2" t="n">
         <v>1.94</v>
@@ -1610,106 +1610,106 @@
         <v>1.89</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.99</v>
+        <v>4.93</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CD2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CN2" t="n">
         <v>1.56</v>
       </c>
-      <c r="CE2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.54</v>
-      </c>
       <c r="CO2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="CP2" t="n">
         <v>1.57</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CV2" t="n">
         <v>2.1</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="DH2" t="n">
-        <v>86.69</v>
+        <v>85.47</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
@@ -1721,58 +1721,58 @@
         <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.25</v>
+        <v>49.65</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.94</v>
+        <v>15.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="DR2" t="n">
         <v>6.88</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.88</v>
+        <v>49.77</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.62</v>
+        <v>13.41</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.25</v>
+        <v>8.06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.87</v>
+        <v>15.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>2.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>65.89</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.5</v>
+        <v>41.11</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.12</v>
+        <v>10.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.88</v>
+        <v>6.44</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.88</v>
+        <v>17.78</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.44</v>
+        <v>11.47</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>5.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT4" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY4" t="n">
         <v>2.64</v>
@@ -2416,40 +2416,40 @@
         <v>2.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.46</v>
+        <v>5.19</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.03</v>
+        <v>5.77</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM4" t="n">
         <v>2.53</v>
@@ -2458,127 +2458,127 @@
         <v>1.94</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG4" t="n">
         <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>75.25</v>
+        <v>75.12</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.94</v>
+        <v>44.06</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.57</v>
+        <v>12.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.41</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.44</v>
+        <v>44.41</v>
       </c>
       <c r="DW4" t="n">
         <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.62</v>
+        <v>12.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.130000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.69</v>
+        <v>17.65</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="H5" t="n">
-        <v>81.86</v>
+        <v>83.25</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2615,67 +2615,67 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>32.14</v>
+        <v>34.88</v>
       </c>
       <c r="N5" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O5" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>10.71</v>
+        <v>10.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="R5" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T5" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.86</v>
+        <v>50.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.43</v>
+        <v>10.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.44</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.12</v>
+        <v>10.24</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>2.54</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>2.61</v>
-      </c>
       <c r="CA5" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CC5" t="n">
         <v>5.47</v>
@@ -2831,43 +2831,43 @@
         <v>6.44</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
@@ -2876,28 +2876,28 @@
         <v>2.79</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB5" t="n">
         <v>1.32</v>
@@ -2906,49 +2906,49 @@
         <v>2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DH5" t="n">
-        <v>69.19</v>
+        <v>70.59</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.75</v>
+        <v>4.71</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.75</v>
+        <v>30.24</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.43</v>
+        <v>10.3</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.62</v>
+        <v>10.7</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.38</v>
+        <v>46.94</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.869999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.13</v>
+        <v>7.18</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>18.59</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,97 +3484,97 @@
         <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>89.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.57</v>
+        <v>7.38</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>52.57</v>
+        <v>54</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.71</v>
+        <v>57.75</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.71</v>
+        <v>16.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.86</v>
+        <v>7.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>14.29</v>
+        <v>14.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BK7" t="n">
         <v>0.88</v>
@@ -3583,40 +3583,40 @@
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.69</v>
+        <v>4.47</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT7" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BU7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY7" t="n">
         <v>1.29</v>
@@ -3625,34 +3625,34 @@
         <v>1.32</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.32</v>
+        <v>6.42</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.14</v>
+        <v>7.22</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CF7" t="n">
         <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK7" t="n">
         <v>1.38</v>
@@ -3670,7 +3670,7 @@
         <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CQ7" t="n">
         <v>1.94</v>
@@ -3684,10 +3684,10 @@
         <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="CZ7" t="inlineStr"/>
       <c r="DA7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
@@ -3710,76 +3710,76 @@
         <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.5</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.87</v>
+        <v>6.82</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>60.44</v>
+        <v>60.65</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.5</v>
+        <v>9.41</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.56</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.06</v>
+        <v>6.94</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.69</v>
+        <v>60</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.37</v>
+        <v>16.18</v>
       </c>
       <c r="DY7" t="n">
         <v>9.119999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.25</v>
+        <v>7.06</v>
       </c>
       <c r="EA7" t="n">
         <v>16</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="8">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3882,103 +3882,103 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>66.86</v>
+        <v>66</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.71</v>
+        <v>36.88</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>11.88</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.71</v>
+        <v>10.88</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>53.86</v>
+        <v>54.12</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.29</v>
+        <v>11.12</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.43</v>
+        <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="BG8" t="n">
         <v>3.12</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI8" t="n">
         <v>3.12</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BN8" t="n">
         <v>2</v>
@@ -3987,31 +3987,31 @@
         <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.81</v>
+        <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>3.68</v>
@@ -4020,82 +4020,82 @@
         <v>3.78</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="CF8" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CL8" t="n">
         <v>1.68</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="CP8" t="n">
         <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CY8" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DA8" t="n">
         <v>1.9</v>
@@ -4110,79 +4110,79 @@
         <v>2.85</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>66.13</v>
+        <v>65.77</v>
       </c>
       <c r="DI8" t="n">
         <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.93</v>
+        <v>4.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.75</v>
+        <v>32.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.88</v>
+        <v>11.3</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.81</v>
+        <v>9.94</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.94</v>
+        <v>50.29</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.5</v>
+        <v>5.41</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.38</v>
+        <v>14.77</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
@@ -4595,94 +4595,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F10" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>79.14</v>
+        <v>79.62</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="K10" t="n">
-        <v>4.86</v>
+        <v>5.12</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>43.29</v>
+        <v>43.38</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>5.57</v>
+        <v>6.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.14</v>
+        <v>56.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.57</v>
+        <v>12.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.71</v>
+        <v>5.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.71</v>
+        <v>16.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0.22</v>
@@ -4766,70 +4766,70 @@
         <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BM10" t="n">
         <v>1.06</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BN10" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BU10" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BV10" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="CC10" t="n">
         <v>5.08</v>
@@ -4841,13 +4841,13 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI10" t="n">
         <v>2.19</v>
@@ -4856,16 +4856,16 @@
         <v>1.6</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM10" t="n">
         <v>2.48</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4880,31 +4880,31 @@
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CT10" t="n">
         <v>3.11</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
@@ -4913,82 +4913,82 @@
         <v>1.65</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="DH10" t="n">
-        <v>69.5</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.38</v>
+        <v>4.53</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.38</v>
+        <v>35.88</v>
       </c>
       <c r="DN10" t="n">
         <v>1.06</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.37</v>
+        <v>11.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.31</v>
+        <v>12.23</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.5</v>
+        <v>7.71</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.87</v>
+        <v>12.53</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.88</v>
+        <v>7.76</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.43</v>
+        <v>15.41</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="11">
@@ -4998,94 +4998,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="G11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="H11" t="n">
-        <v>73.5</v>
+        <v>71.44</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K11" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="L11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M11" t="n">
-        <v>38.75</v>
+        <v>38.22</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P11" t="n">
-        <v>11.75</v>
+        <v>11.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.88</v>
+        <v>14.33</v>
       </c>
       <c r="R11" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="T11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.25</v>
+        <v>45.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.62</v>
+        <v>16.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5169,70 +5169,70 @@
         <v>1.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.69</v>
+        <v>9.76</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU11" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.56</v>
+        <v>4.31</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="CC11" t="n">
         <v>4.98</v>
@@ -5241,37 +5241,37 @@
         <v>5.53</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
         <v>2.47</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK11" t="n">
         <v>1.51</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM11" t="n">
         <v>2.43</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP11" t="n">
         <v>1.74</v>
@@ -5286,25 +5286,25 @@
         <v>2.58</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY11" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DA11" t="n">
         <v>1.97</v>
@@ -5313,52 +5313,52 @@
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DH11" t="n">
-        <v>78.88</v>
+        <v>77.47</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
         <v>0.06</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.82</v>
+        <v>40.41</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.82</v>
+        <v>10.89</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.94</v>
+        <v>13.23</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.44</v>
+        <v>9.24</v>
       </c>
       <c r="DS11" t="n">
         <v>0.12</v>
@@ -5370,28 +5370,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.75</v>
+        <v>46.59</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.12</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.87</v>
+        <v>16.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="12">
@@ -5401,94 +5401,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>66.70999999999999</v>
+        <v>67.38</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K12" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="L12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M12" t="n">
-        <v>30.43</v>
+        <v>31</v>
       </c>
       <c r="N12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>7.86</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.57</v>
+        <v>13.62</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.14</v>
+        <v>45.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.43</v>
+        <v>16.75</v>
       </c>
       <c r="AD12" t="n">
         <v>1.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5572,70 +5572,70 @@
         <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.38</v>
+        <v>11.12</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
         <v>1.12</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BO12" t="n">
         <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.31</v>
+        <v>5.24</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.77</v>
+        <v>7.11</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.82</v>
+        <v>7.22</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="CC12" t="n">
         <v>5.26</v>
@@ -5647,40 +5647,40 @@
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CK12" t="n">
         <v>1.52</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5701,100 +5701,100 @@
         <v>1.78</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DH12" t="n">
-        <v>70.06</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="DL12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>34</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="DW12" t="n">
         <v>0.18</v>
       </c>
-      <c r="DM12" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DP12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="DQ12" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>46.68</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0.19</v>
-      </c>
       <c r="DX12" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.06</v>
+        <v>16.24</v>
       </c>
       <c r="EB12" t="n">
         <v>1.03</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.38</v>
@@ -6293,139 +6293,139 @@
         <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>107.25</v>
+        <v>112</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.12</v>
+        <v>56.11</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.38</v>
+        <v>10.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.62</v>
+        <v>57.44</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.38</v>
+        <v>11.78</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.25</v>
+        <v>4.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.62</v>
+        <v>14.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.25</v>
+        <v>10.06</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BO14" t="n">
         <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX14" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>1.5</v>
@@ -6434,52 +6434,52 @@
         <v>1.46</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="CF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ14" t="n">
         <v>1.57</v>
       </c>
-      <c r="CG14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CK14" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.03</v>
@@ -6497,106 +6497,106 @@
         <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>97.68000000000001</v>
+        <v>100.76</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.94</v>
+        <v>6.71</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.37</v>
+        <v>56.82</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.07</v>
+        <v>12.18</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.380000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.87</v>
+        <v>59.17</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.94</v>
+        <v>13.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.75</v>
+        <v>4.94</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.18</v>
+        <v>16.35</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="15">
@@ -6606,61 +6606,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>68.75</v>
+        <v>69.89</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="K15" t="n">
-        <v>6.25</v>
+        <v>5.78</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>35.5</v>
+        <v>34.33</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>14.5</v>
+        <v>14.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="S15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="T15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6672,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>43.88</v>
+        <v>42.89</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.5</v>
+        <v>8.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.75</v>
+        <v>18.89</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6777,70 @@
         <v>1.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.69</v>
+        <v>11.47</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.31</v>
+        <v>4.12</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT15" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU15" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.03</v>
+        <v>4.03</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.07</v>
+        <v>3.99</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.66</v>
+        <v>4.85</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.29</v>
+        <v>5.48</v>
       </c>
       <c r="CC15" t="n">
         <v>9.19</v>
@@ -6852,55 +6852,55 @@
         <v>1.15</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.79</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO15" t="n">
         <v>1.07</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="CR15" t="n">
         <v>1.37</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="CT15" t="n">
         <v>3.03</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
         <v>1.85</v>
@@ -6909,64 +6909,64 @@
         <v>1.59</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="DG15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="DO15" t="n">
         <v>1.88</v>
       </c>
-      <c r="DH15" t="n">
-        <v>71.68000000000001</v>
-      </c>
-      <c r="DI15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DJ15" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="DL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>1.94</v>
-      </c>
       <c r="DP15" t="n">
-        <v>14.06</v>
+        <v>13.94</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.56</v>
+        <v>10.35</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>42.38</v>
+        <v>41.94</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.06</v>
+        <v>11.59</v>
       </c>
       <c r="DY15" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.5</v>
+        <v>17.65</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.12</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" t="n">
-        <v>73</v>
+        <v>73.56</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN16" t="n">
-        <v>40</v>
+        <v>38.89</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.62</v>
+        <v>11.67</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.380000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>39.38</v>
+        <v>40.11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.119999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.75</v>
+        <v>7.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.25</v>
+        <v>16.11</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.38</v>
+        <v>10.24</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY16" t="n">
         <v>2.25</v>
@@ -7240,43 +7240,43 @@
         <v>2.24</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CC16" t="n">
-        <v>5.06</v>
+        <v>4.78</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="CE16" t="n">
         <v>1.21</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH16" t="n">
         <v>1.43</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK16" t="n">
         <v>1.38</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN16" t="n">
         <v>1.82</v>
@@ -7294,7 +7294,7 @@
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CT16" t="n">
         <v>3.1</v>
@@ -7303,100 +7303,100 @@
         <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY16" t="n">
         <v>1.83</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DH16" t="n">
-        <v>71.81</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="DK16" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.19</v>
+        <v>40.53</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DP16" t="n">
         <v>11.18</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.81</v>
+        <v>11.83</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.56</v>
+        <v>7.41</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.75</v>
+        <v>44.82</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.25</v>
+        <v>12.36</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.94</v>
+        <v>18.23</v>
       </c>
       <c r="EB16" t="n">
         <v>1.2</v>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8230,49 +8230,49 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="H19" t="n">
-        <v>70.5</v>
+        <v>69.89</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J19" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="K19" t="n">
-        <v>5.38</v>
+        <v>4.89</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M19" t="n">
-        <v>35</v>
+        <v>34.22</v>
       </c>
       <c r="N19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="P19" t="n">
-        <v>12.62</v>
+        <v>12.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.5</v>
+        <v>13.22</v>
       </c>
       <c r="R19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,25 +8284,25 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.5</v>
+        <v>50.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.62</v>
+        <v>12.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -8392,67 +8392,67 @@
         <v>2.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.69</v>
+        <v>8.59</v>
       </c>
       <c r="BI19" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT19" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.44</v>
+        <v>3.57</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.58</v>
+        <v>3.71</v>
       </c>
       <c r="CA19" t="n">
         <v>4</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="CC19" t="n">
         <v>2.71</v>
@@ -8464,13 +8464,13 @@
         <v>1.29</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI19" t="n">
         <v>2.1</v>
@@ -8482,10 +8482,10 @@
         <v>1.52</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN19" t="n">
         <v>1.86</v>
@@ -8506,7 +8506,7 @@
         <v>2.58</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CU19" t="n">
         <v>1.5</v>
@@ -8521,10 +8521,10 @@
         <v>1.57</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
         <v>1.88</v>
@@ -8536,49 +8536,49 @@
         <v>1.71</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DH19" t="n">
-        <v>65.31</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.44</v>
+        <v>4.24</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM19" t="n">
-        <v>31.19</v>
+        <v>31</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.88</v>
+        <v>13.23</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.12</v>
@@ -8590,25 +8590,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.75</v>
+        <v>51.77</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.06</v>
+        <v>11.94</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.56</v>
+        <v>18.7</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC19" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>54.71</v>
+        <v>52.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.57</v>
+        <v>20.12</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.14</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>36.14</v>
+        <v>35.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="BB3" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.71</v>
+        <v>12.12</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH3" t="n">
         <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.44</v>
+        <v>4.59</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU3" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY3" t="n">
         <v>3.38</v>
@@ -2013,34 +2013,34 @@
         <v>3.74</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.27</v>
+        <v>4.46</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.94</v>
+        <v>5.21</v>
       </c>
       <c r="CC3" t="n">
-        <v>8.970000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="CD3" t="n">
-        <v>10.09</v>
+        <v>10.72</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.39</v>
@@ -2049,34 +2049,34 @@
         <v>1.74</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="CT3" t="n">
         <v>3.01</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW3" t="n">
         <v>1.93</v>
@@ -2085,64 +2085,64 @@
         <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.4</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="DH3" t="n">
-        <v>57.18</v>
+        <v>56</v>
       </c>
       <c r="DI3" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.19</v>
+        <v>3.94</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM3" t="n">
-        <v>25.81</v>
+        <v>24.88</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.81</v>
+        <v>9.82</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.19</v>
+        <v>9.35</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>42.12</v>
+        <v>41.29</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX3" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.69</v>
+        <v>17.12</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -2669,7 +2669,7 @@
         <v>3.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>21</v>
+        <v>21.12</v>
       </c>
       <c r="AD5" t="n">
         <v>1.17</v>
@@ -2975,7 +2975,7 @@
         <v>2.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.59</v>
+        <v>18.64</v>
       </c>
       <c r="EB5" t="n">
         <v>1.01</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>82.70999999999999</v>
+        <v>87.25</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="K6" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>44.29</v>
+        <v>47.5</v>
       </c>
       <c r="N6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P6" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>10.14</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.86</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.57</v>
+        <v>50.62</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.57</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>18</v>
+        <v>18.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,67 +3165,67 @@
         <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI6" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
         <v>1.12</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.23</v>
+        <v>5.71</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.84</v>
+        <v>5.36</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="CC6" t="n">
         <v>4.51</v>
@@ -3237,40 +3237,40 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3288,7 +3288,7 @@
         <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX6" t="n">
         <v>1.6</v>
@@ -3303,88 +3303,88 @@
         <v>1.9</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DH6" t="n">
-        <v>69.69</v>
+        <v>72.59</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.75</v>
+        <v>39.65</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.75</v>
+        <v>12.59</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.06</v>
+        <v>10.24</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.93</v>
+        <v>7.65</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.44</v>
+        <v>47.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.31</v>
+        <v>7.18</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.56</v>
+        <v>18.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.75</v>
+        <v>57.88</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60</v>
+        <v>60.06</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4204,49 +4204,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G9" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="H9" t="n">
-        <v>91.75</v>
+        <v>96.56</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="K9" t="n">
-        <v>6.75</v>
+        <v>7.11</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>52.38</v>
+        <v>56.11</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
-        <v>12.88</v>
+        <v>13.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="R9" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.38</v>
+        <v>14.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.12</v>
+        <v>5.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.5</v>
+        <v>19.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF9" t="n">
         <v>0.25</v>
@@ -4366,67 +4366,67 @@
         <v>3.06</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="BI9" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BM9" t="n">
         <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.66</v>
+        <v>4.83</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.05</v>
+        <v>5.31</v>
       </c>
       <c r="CC9" t="n">
         <v>1.69</v>
@@ -4435,124 +4435,124 @@
         <v>1.76</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CH9" t="n">
         <v>1.64</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB9" t="n">
         <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
         <v>3.12</v>
       </c>
       <c r="DH9" t="n">
-        <v>93.5</v>
+        <v>95.94</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM9" t="n">
-        <v>54.63</v>
+        <v>56.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.13</v>
+        <v>12.3</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.56</v>
+        <v>9.58</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.06</v>
+        <v>62.64</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.44</v>
+        <v>14.65</v>
       </c>
       <c r="DY9" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.56</v>
+        <v>5.77</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.38</v>
+        <v>17.53</v>
       </c>
       <c r="EB9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="EC9" t="n">
         <v>1.65</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>1.75</v>
       </c>
     </row>
     <row r="10">
@@ -5804,94 +5804,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="H13" t="n">
-        <v>111.25</v>
+        <v>112.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J13" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="K13" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>65.88</v>
+        <v>66.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="P13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.62</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>61.38</v>
+        <v>61.11</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>19</v>
+        <v>19.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.25</v>
+        <v>11.22</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.88</v>
+        <v>16.67</v>
       </c>
       <c r="AD13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
         <v>0.38</v>
@@ -5975,61 +5975,61 @@
         <v>1.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.44</v>
+        <v>10.29</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="BJ13" t="n">
         <v>0.88</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.62</v>
+        <v>5.53</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BT13" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BU13" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV13" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BZ13" t="n">
         <v>1.21</v>
@@ -6038,7 +6038,7 @@
         <v>6.38</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.91</v>
+        <v>7.88</v>
       </c>
       <c r="CC13" t="n">
         <v>1.54</v>
@@ -6047,37 +6047,37 @@
         <v>1.57</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.64</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL13" t="n">
         <v>1.59</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="CP13" t="n">
         <v>1.31</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW13" t="n">
         <v>1.72</v>
@@ -6103,97 +6103,97 @@
         <v>1.57</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.39</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DB13" t="n">
         <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DD13" t="n">
         <v>1.74</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>107</v>
+        <v>107.82</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DM13" t="n">
-        <v>66.25</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="DO13" t="n">
         <v>3.94</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.44</v>
+        <v>11.24</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.56</v>
+        <v>11.76</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.19</v>
+        <v>60.12</v>
       </c>
       <c r="DW13" t="n">
         <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>19.06</v>
+        <v>19.11</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.38</v>
+        <v>12.29</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.68</v>
+        <v>6.82</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.31</v>
+        <v>16.24</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6651,7 +6651,7 @@
         <v>14.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="R15" t="n">
         <v>6.56</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.89</v>
+        <v>42.78</v>
       </c>
       <c r="Y15" t="n">
         <v>0.33</v>
@@ -6963,7 +6963,7 @@
         <v>13.94</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="DR15" t="n">
         <v>6.88</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.94</v>
+        <v>41.89</v>
       </c>
       <c r="DW15" t="n">
         <v>0.17</v>
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7502,139 +7502,139 @@
         <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>67.88</v>
+        <v>67.11</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>28.88</v>
+        <v>28.22</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.38</v>
+        <v>12.67</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.75</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.12</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.62</v>
+        <v>46</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.12</v>
+        <v>4.56</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.12</v>
+        <v>13.89</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.44</v>
+        <v>9.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT17" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY17" t="n">
         <v>2.92</v>
@@ -7643,169 +7643,169 @@
         <v>3.32</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.28</v>
+        <v>3.99</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
         <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="CT17" t="n">
         <v>3.02</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CV17" t="n">
         <v>2.07</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX17" t="n">
         <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DH17" t="n">
-        <v>67.25</v>
+        <v>66.88</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.68</v>
+        <v>3.47</v>
       </c>
       <c r="DL17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.06</v>
+        <v>34.35</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.57</v>
+        <v>11.77</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.18</v>
+        <v>11.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.369999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.68</v>
+        <v>49.18</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.88</v>
+        <v>10.41</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.37</v>
+        <v>4.12</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.68</v>
+        <v>15</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,139 +7905,139 @@
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI18" t="n">
-        <v>50.12</v>
+        <v>53.11</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>21.25</v>
+        <v>21.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.62</v>
+        <v>11.44</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.38</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.38</v>
+        <v>44.11</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>17.22</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.56</v>
+        <v>10.41</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU18" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY18" t="n">
         <v>5.92</v>
@@ -8046,25 +8046,25 @@
         <v>6.37</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.09</v>
+        <v>4.97</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH18" t="n">
         <v>1.35</v>
@@ -8079,7 +8079,7 @@
         <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CM18" t="n">
         <v>2.15</v>
@@ -8088,13 +8088,13 @@
         <v>1.69</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8130,52 +8130,52 @@
         <v>1.28</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="DE18" t="n">
         <v>0.12</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH18" t="n">
-        <v>64.5</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="DK18" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM18" t="n">
-        <v>29.56</v>
+        <v>29.12</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.68</v>
+        <v>10.88</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.87</v>
+        <v>11.76</v>
       </c>
       <c r="DR18" t="n">
-        <v>10.44</v>
+        <v>10.18</v>
       </c>
       <c r="DS18" t="n">
         <v>0.12</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.06</v>
+        <v>45.82</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX18" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.75</v>
+        <v>19.47</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="H2" t="n">
-        <v>85.44</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>48.67</v>
+        <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="R2" t="n">
-        <v>7.33</v>
+        <v>6.9</v>
       </c>
       <c r="S2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>48.67</v>
+        <v>49.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.56</v>
+        <v>8.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.33</v>
+        <v>13.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.75</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.18</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="CC2" t="n">
         <v>1.55</v>
@@ -1622,16 +1622,16 @@
         <v>1.58</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CI2" t="n">
         <v>1.97</v>
@@ -1640,19 +1640,19 @@
         <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="CP2" t="n">
         <v>1.57</v>
@@ -1664,13 +1664,13 @@
         <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CT2" t="n">
         <v>3.25</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CV2" t="n">
         <v>2.1</v>
@@ -1685,7 +1685,7 @@
         <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
         <v>1.9</v>
@@ -1694,85 +1694,85 @@
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DE2" t="n">
         <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.47</v>
+        <v>84.33</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="DK2" t="n">
         <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.65</v>
+        <v>49.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.18</v>
+        <v>15.11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.77</v>
+        <v>49.94</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.41</v>
+        <v>13.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.06</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.94</v>
+        <v>15.44</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AT3" t="n">
         <v>2</v>
       </c>
-      <c r="AI3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AU3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>35.12</v>
+        <v>35.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.38</v>
+        <v>6.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.12</v>
+        <v>4.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.12</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>10.28</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.59</v>
+        <v>4.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.12</v>
+        <v>4.39</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>3.38</v>
@@ -2013,25 +2013,25 @@
         <v>3.74</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="CC3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="CD3" t="n">
-        <v>10.72</v>
+        <v>10.12</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH3" t="n">
         <v>1.41</v>
@@ -2046,7 +2046,7 @@
         <v>1.39</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM3" t="n">
         <v>2.36</v>
@@ -2058,22 +2058,22 @@
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV3" t="n">
         <v>1.88</v>
@@ -2082,16 +2082,16 @@
         <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
@@ -2100,49 +2100,49 @@
         <v>1.89</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DH3" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM3" t="n">
-        <v>24.88</v>
+        <v>25.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.82</v>
+        <v>10.06</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.12</v>
+        <v>12</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.35</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.88</v>
+        <v>8.44</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.88</v>
+        <v>5.44</v>
       </c>
       <c r="DZ3" t="n">
         <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.12</v>
+        <v>17.78</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="H4" t="n">
-        <v>85.5</v>
+        <v>84.78</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="K4" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M4" t="n">
-        <v>47.38</v>
+        <v>46.89</v>
       </c>
       <c r="N4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.5</v>
+        <v>14.56</v>
       </c>
       <c r="R4" t="n">
-        <v>7.62</v>
+        <v>7.89</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.38</v>
+        <v>48.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.12</v>
+        <v>13.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.11</v>
@@ -2356,70 +2356,70 @@
         <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.47</v>
+        <v>11.61</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.53</v>
+        <v>3.89</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW4" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="CC4" t="n">
         <v>5.19</v>
@@ -2434,10 +2434,10 @@
         <v>2.12</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
         <v>2.31</v>
@@ -2449,37 +2449,37 @@
         <v>1.31</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM4" t="n">
         <v>2.53</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO4" t="n">
         <v>1.09</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT4" t="n">
         <v>3.22</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW4" t="n">
         <v>1.59</v>
@@ -2497,88 +2497,88 @@
         <v>2.13</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
         <v>1.59</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="DH4" t="n">
-        <v>75.12</v>
+        <v>75.33</v>
       </c>
       <c r="DI4" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.06</v>
+        <v>44</v>
       </c>
       <c r="DN4" t="n">
         <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.53</v>
+        <v>12.44</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.7</v>
+        <v>12.39</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.41</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.41</v>
+        <v>44.06</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.35</v>
+        <v>12.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.82</v>
+        <v>7.61</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.65</v>
+        <v>17.73</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>83.25</v>
+        <v>81.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="K5" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>34.88</v>
+        <v>34</v>
       </c>
       <c r="N5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="P5" t="n">
-        <v>10.38</v>
+        <v>10.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="R5" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="S5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>48.89</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.12</v>
       </c>
-      <c r="T5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>50.62</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.44</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.24</v>
+        <v>10.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.65</v>
+        <v>4.83</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="BZ5" t="n">
         <v>2.54</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CC5" t="n">
         <v>5.47</v>
@@ -2831,13 +2831,13 @@
         <v>6.44</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH5" t="n">
         <v>1.25</v>
@@ -2855,100 +2855,100 @@
         <v>1.73</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CW5" t="n">
         <v>1.92</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>1.91</v>
       </c>
       <c r="CX5" t="n">
         <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
         <v>1.32</v>
       </c>
       <c r="DC5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="DH5" t="n">
-        <v>70.59</v>
+        <v>70.5</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.24</v>
+        <v>30.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.71</v>
+        <v>7.84</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.94</v>
+        <v>46.28</v>
       </c>
       <c r="DW5" t="n">
         <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.12</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.64</v>
+        <v>18.28</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="n">
-        <v>87.25</v>
+        <v>87.67</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>47.5</v>
+        <v>45.56</v>
       </c>
       <c r="N6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>13.88</v>
+        <v>13.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.62</v>
+        <v>50.11</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.38</v>
+        <v>11.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.38</v>
+        <v>17.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.470000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.71</v>
+        <v>5.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.36</v>
+        <v>5.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="CC6" t="n">
         <v>4.51</v>
@@ -3237,10 +3237,10 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
@@ -3249,10 +3249,10 @@
         <v>2</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL6" t="n">
         <v>1.95</v>
@@ -3267,31 +3267,31 @@
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.85</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CT6" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW6" t="n">
         <v>1.8</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY6" t="n">
         <v>1.93</v>
@@ -3306,85 +3306,85 @@
         <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DH6" t="n">
-        <v>72.59</v>
+        <v>73.61</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="DL6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>39.12</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="DW6" t="n">
         <v>0.11</v>
       </c>
-      <c r="DM6" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>47.12</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DX6" t="n">
-        <v>11</v>
+        <v>10.61</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.71</v>
+        <v>18.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>93.11</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>54</v>
+        <v>53.11</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AQ7" t="n">
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.880000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.88</v>
+        <v>6.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.88</v>
+        <v>57.67</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.25</v>
+        <v>16.56</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.880000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>14.5</v>
+        <v>15.33</v>
       </c>
       <c r="BE7" t="n">
         <v>1.93</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.94</v>
+        <v>10.06</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU7" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>1.29</v>
@@ -3625,52 +3625,52 @@
         <v>1.32</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.42</v>
+        <v>6.28</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.22</v>
+        <v>7.05</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CF7" t="n">
         <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM7" t="n">
         <v>2.71</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
         <v>1.08</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
         <v>1.94</v>
@@ -3684,10 +3684,10 @@
         <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
@@ -3701,85 +3701,85 @@
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.76000000000001</v>
+        <v>97.61</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>60.65</v>
+        <v>59.84</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.41</v>
+        <v>9.44</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.710000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.94</v>
+        <v>6.72</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.06</v>
+        <v>59.84</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.18</v>
+        <v>16.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="EA7" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="EB7" t="n">
         <v>1.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3882,136 +3882,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>66</v>
+        <v>65.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.88</v>
+        <v>37.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.88</v>
+        <v>12.22</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.88</v>
+        <v>11.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>54.12</v>
+        <v>53.33</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.12</v>
+        <v>10.44</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.25</v>
+        <v>5.89</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="BD8" t="n">
         <v>17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BN8" t="n">
         <v>2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
         <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV8" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY8" t="n">
         <v>3.68</v>
@@ -4020,28 +4020,28 @@
         <v>3.78</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.07</v>
+        <v>4.16</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="CI8" t="n">
         <v>2.07</v>
@@ -4050,22 +4050,22 @@
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.28</v>
@@ -4074,13 +4074,13 @@
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CT8" t="n">
         <v>3.07</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV8" t="n">
         <v>2.16</v>
@@ -4089,13 +4089,13 @@
         <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DA8" t="n">
         <v>1.9</v>
@@ -4104,85 +4104,85 @@
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
         <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>65.77</v>
+        <v>65.44</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DK8" t="n">
         <v>4.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>32.65</v>
+        <v>33.11</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>9.94</v>
+        <v>10.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.29</v>
+        <v>50.11</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.41</v>
+        <v>5.28</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.77</v>
+        <v>14.89</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4282,139 +4282,139 @@
         <v>1.44</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AI9" t="n">
-        <v>95.25</v>
+        <v>96.44</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.12</v>
+        <v>7.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>56.88</v>
+        <v>57.33</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>61.12</v>
+        <v>61.22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BC9" t="n">
         <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>15.25</v>
+        <v>16.11</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.18</v>
+        <v>10.39</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="BM9" t="n">
         <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.41</v>
+        <v>4.72</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>2.05</v>
@@ -4426,13 +4426,13 @@
         <v>4.83</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.31</v>
+        <v>5.26</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CE9" t="n">
         <v>1.22</v>
@@ -4441,10 +4441,10 @@
         <v>2.13</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CI9" t="n">
         <v>2.26</v>
@@ -4462,34 +4462,34 @@
         <v>2.54</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO9" t="n">
         <v>1.12</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
@@ -4507,85 +4507,85 @@
         <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="DH9" t="n">
-        <v>95.94</v>
+        <v>96.5</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.11</v>
+        <v>7.16</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM9" t="n">
-        <v>56.47</v>
+        <v>56.72</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.3</v>
+        <v>12.06</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.58</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.64</v>
+        <v>62.61</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.65</v>
+        <v>14.89</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.77</v>
+        <v>5.78</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.53</v>
+        <v>17.83</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="10">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.38</v>
@@ -4685,139 +4685,139 @@
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>62</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.44</v>
       </c>
-      <c r="AN10" t="n">
-        <v>29.22</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>47.89</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL10" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BM10" t="n">
         <v>1.06</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU10" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY10" t="n">
         <v>2.22</v>
@@ -4826,169 +4826,169 @@
         <v>2.16</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.08</v>
+        <v>4.83</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.4</v>
+        <v>5.15</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK10" t="n">
         <v>1.47</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN10" t="n">
         <v>1.94</v>
       </c>
       <c r="CO10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DF10" t="n">
         <v>1.17</v>
       </c>
-      <c r="CP10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="DG10" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="DH10" t="n">
-        <v>70.29000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.53</v>
+        <v>5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.88</v>
+        <v>38</v>
       </c>
       <c r="DN10" t="n">
         <v>1.06</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.23</v>
+        <v>12.11</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.71</v>
+        <v>7.56</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.06</v>
+        <v>52.78</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.53</v>
+        <v>12.89</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.76</v>
+        <v>7.89</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.76</v>
+        <v>5</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.41</v>
+        <v>15.72</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4998,94 +4998,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>71.44</v>
+        <v>68.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M11" t="n">
-        <v>38.22</v>
+        <v>36.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>11.78</v>
+        <v>11.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.33</v>
+        <v>13.7</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.11</v>
+        <v>44</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.56</v>
+        <v>16.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5169,31 +5169,31 @@
         <v>1.75</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.76</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BM11" t="n">
         <v>1</v>
       </c>
-      <c r="BL11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.88</v>
-      </c>
       <c r="BN11" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BP11" t="n">
         <v>3.94</v>
@@ -5205,34 +5205,34 @@
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU11" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.31</v>
+        <v>4.71</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.26</v>
+        <v>4.77</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.14</v>
+        <v>4.28</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.41</v>
+        <v>4.6</v>
       </c>
       <c r="CC11" t="n">
         <v>4.98</v>
@@ -5241,55 +5241,55 @@
         <v>5.53</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="CT11" t="n">
         <v>3.04</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CV11" t="n">
         <v>2.12</v>
@@ -5298,13 +5298,13 @@
         <v>1.73</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DA11" t="n">
         <v>1.97</v>
@@ -5319,79 +5319,79 @@
         <v>3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>77.47</v>
+        <v>75.39</v>
       </c>
       <c r="DI11" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="DL11" t="n">
         <v>0.06</v>
       </c>
       <c r="DM11" t="n">
-        <v>40.41</v>
+        <v>39.22</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.89</v>
+        <v>10.78</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.23</v>
+        <v>12.94</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.24</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.59</v>
+        <v>45.89</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.3</v>
+        <v>6.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.82</v>
+        <v>16.83</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
@@ -5401,94 +5401,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>67.38</v>
+        <v>67</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K12" t="n">
-        <v>3.88</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M12" t="n">
-        <v>31</v>
+        <v>34.11</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="P12" t="n">
-        <v>8.119999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.62</v>
+        <v>13.33</v>
       </c>
       <c r="R12" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.75</v>
+        <v>48.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.62</v>
+        <v>11</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.38</v>
+        <v>7.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5572,70 +5572,70 @@
         <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.12</v>
+        <v>11.22</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.12</v>
+        <v>5.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.11</v>
+        <v>6.64</v>
       </c>
       <c r="BZ12" t="n">
-        <v>7.22</v>
+        <v>6.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.91</v>
+        <v>4.84</v>
       </c>
       <c r="CC12" t="n">
         <v>5.26</v>
@@ -5647,58 +5647,58 @@
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL12" t="n">
         <v>2</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP12" t="n">
         <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CT12" t="n">
         <v>3.12</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5713,52 +5713,52 @@
         <v>1.87</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE12" t="n">
         <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>70.18000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>34</v>
+        <v>35.39</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.23</v>
+        <v>13.11</v>
       </c>
       <c r="DR12" t="n">
         <v>8.94</v>
@@ -5773,28 +5773,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.06</v>
+        <v>47.28</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.59</v>
+        <v>9.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.53</v>
+        <v>6.72</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.24</v>
+        <v>16.39</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5894,139 +5894,139 @@
         <v>2.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>102.75</v>
+        <v>103.44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.75</v>
+        <v>6.78</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN13" t="n">
-        <v>66.62</v>
+        <v>68.22</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.38</v>
+        <v>10.11</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.62</v>
+        <v>5.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>59</v>
+        <v>59.78</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>19.12</v>
+        <v>19.22</v>
       </c>
       <c r="BB13" t="n">
-        <v>13.5</v>
+        <v>12.89</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.62</v>
+        <v>6.33</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.75</v>
+        <v>15.56</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT13" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU13" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
         <v>1.22</v>
@@ -6035,31 +6035,31 @@
         <v>1.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.38</v>
+        <v>6.41</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.88</v>
+        <v>7.87</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CF13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="CH13" t="n">
         <v>1.68</v>
       </c>
-      <c r="CG13" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CI13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.64</v>
@@ -6068,13 +6068,13 @@
         <v>1.28</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO13" t="n">
         <v>0.95</v>
@@ -6083,7 +6083,7 @@
         <v>1.31</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6094,22 +6094,22 @@
         <v>1.97</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW13" t="n">
         <v>1.72</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB13" t="n">
         <v>1.11</v>
@@ -6121,79 +6121,79 @@
         <v>1.74</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.82</v>
+        <v>107.88</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.53</v>
+        <v>7.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DM13" t="n">
-        <v>66.76000000000001</v>
+        <v>67.56</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.24</v>
+        <v>11.06</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.76</v>
+        <v>11.56</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.12</v>
+        <v>60.44</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>19.11</v>
+        <v>19.17</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.29</v>
+        <v>12.06</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.82</v>
+        <v>7.11</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.24</v>
+        <v>16.12</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G14" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>88.12</v>
+        <v>86.78</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M14" t="n">
-        <v>57.62</v>
+        <v>54.67</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>4.88</v>
+        <v>4.44</v>
       </c>
       <c r="P14" t="n">
-        <v>12.38</v>
+        <v>12.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="R14" t="n">
-        <v>4.75</v>
+        <v>5.89</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>61.12</v>
+        <v>59.22</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>13.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.25</v>
+        <v>8.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.75</v>
+        <v>19.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AF14" t="n">
         <v>0.22</v>
@@ -6374,70 +6374,70 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.06</v>
+        <v>10.17</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP14" t="n">
         <v>5.06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT14" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="CC14" t="n">
         <v>2.55</v>
@@ -6446,40 +6446,40 @@
         <v>2.58</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.03</v>
@@ -6497,10 +6497,10 @@
         <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6518,85 +6518,85 @@
         <v>1.19</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG14" t="n">
         <v>3.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.76</v>
+        <v>99.39</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.82</v>
+        <v>55.39</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.18</v>
+        <v>12.44</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.41</v>
+        <v>9.44</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.83</v>
+        <v>7.28</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.17</v>
+        <v>58.33</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.06</v>
+        <v>12.73</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.35</v>
+        <v>16.77</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6699,136 +6699,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AI15" t="n">
-        <v>74.62</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.25</v>
+        <v>4.89</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.12</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.62</v>
+        <v>13.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.62</v>
+        <v>11.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.25</v>
+        <v>7.67</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>40.88</v>
+        <v>39.89</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.12</v>
+        <v>10.44</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.5</v>
+        <v>6.11</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.25</v>
+        <v>15.78</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.47</v>
+        <v>11.56</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY15" t="n">
         <v>4.03</v>
@@ -6837,73 +6837,73 @@
         <v>3.99</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.85</v>
+        <v>4.77</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="CC15" t="n">
-        <v>9.19</v>
+        <v>8.43</v>
       </c>
       <c r="CD15" t="n">
-        <v>11.46</v>
+        <v>10.45</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CG15" t="n">
         <v>2.95</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK15" t="n">
         <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CP15" t="n">
         <v>1.73</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX15" t="n">
         <v>1.59</v>
@@ -6930,43 +6930,43 @@
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>72.12</v>
+        <v>69.94</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.53</v>
+        <v>5.34</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>36.11</v>
+        <v>35.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.94</v>
+        <v>13.77</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.41</v>
+        <v>10.33</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.88</v>
+        <v>7.11</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.89</v>
+        <v>41.34</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.59</v>
+        <v>11.22</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.65</v>
+        <v>7.39</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.65</v>
+        <v>17.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.12</v>
@@ -7102,136 +7102,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>73.56</v>
+        <v>75.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="AL16" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.89</v>
+        <v>39.9</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK16" t="n">
         <v>0.44</v>
       </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>40.11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>10.24</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BL16" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.29</v>
+        <v>5.17</v>
       </c>
       <c r="BR16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT16" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>2.25</v>
@@ -7240,22 +7240,22 @@
         <v>2.24</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.78</v>
+        <v>4.53</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG16" t="n">
         <v>3.07</v>
@@ -7270,10 +7270,10 @@
         <v>1.68</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM16" t="n">
         <v>2.38</v>
@@ -7282,28 +7282,28 @@
         <v>1.82</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CW16" t="n">
         <v>1.7</v>
@@ -7315,94 +7315,94 @@
         <v>1.83</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DH16" t="n">
-        <v>72.18000000000001</v>
+        <v>73.44</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.77</v>
+        <v>4.89</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.53</v>
+        <v>41</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.41</v>
+        <v>7.33</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.82</v>
+        <v>45.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.36</v>
+        <v>12.61</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.470000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.23</v>
+        <v>18.11</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="17">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="H17" t="n">
-        <v>66.62</v>
+        <v>70.22</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="K17" t="n">
-        <v>5.62</v>
+        <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>41.25</v>
+        <v>41.11</v>
       </c>
       <c r="N17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="P17" t="n">
-        <v>10.75</v>
+        <v>10.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.619999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="R17" t="n">
-        <v>6.62</v>
+        <v>6.89</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>52.75</v>
+        <v>54</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.38</v>
+        <v>7.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7583,70 +7583,70 @@
         <v>2.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.24</v>
+        <v>3.11</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.35</v>
+        <v>9.67</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.24</v>
+        <v>3.11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.53</v>
+        <v>4.78</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="CA17" t="n">
         <v>3.89</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="CC17" t="n">
         <v>3.6</v>
@@ -7655,157 +7655,157 @@
         <v>3.99</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH17" t="n">
         <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU17" t="n">
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB17" t="n">
         <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="DH17" t="n">
-        <v>66.88</v>
+        <v>68.67</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.47</v>
+        <v>3.94</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="DM17" t="n">
-        <v>34.35</v>
+        <v>34.66</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.77</v>
+        <v>11.73</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.94</v>
+        <v>12.06</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.18</v>
+        <v>50</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="EA17" t="n">
-        <v>15</v>
+        <v>14.94</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,139 +7905,139 @@
         <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>53.11</v>
+        <v>56.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK18" t="n">
         <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>21.33</v>
+        <v>24.7</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.11</v>
+        <v>10.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.44</v>
+        <v>12.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.890000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.11</v>
+        <v>44.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.78</v>
+        <v>8.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.67</v>
+        <v>6.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.22</v>
+        <v>17.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.63</v>
+        <v>0.73</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.41</v>
+        <v>10.44</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT18" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY18" t="n">
         <v>5.92</v>
@@ -8046,22 +8046,22 @@
         <v>6.37</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="CC18" t="n">
-        <v>4.77</v>
+        <v>4.84</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="CE18" t="n">
         <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG18" t="n">
         <v>2.85</v>
@@ -8070,16 +8070,16 @@
         <v>1.35</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM18" t="n">
         <v>2.15</v>
@@ -8088,43 +8088,43 @@
         <v>1.69</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP18" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DB18" t="n">
         <v>1.28</v>
@@ -8133,82 +8133,82 @@
         <v>1.89</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DH18" t="n">
-        <v>65.23999999999999</v>
+        <v>66.61</v>
       </c>
       <c r="DI18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="DS18" t="n">
         <v>0.11</v>
       </c>
-      <c r="DJ18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0.12</v>
-      </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>45.82</v>
+        <v>46.17</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>8.82</v>
+        <v>9.17</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.41</v>
+        <v>6.67</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.47</v>
+        <v>19.5</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="19">
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
@@ -8230,79 +8230,79 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="n">
-        <v>69.89</v>
+        <v>72</v>
       </c>
       <c r="I19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.89</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>34.22</v>
+        <v>34</v>
       </c>
       <c r="N19" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>12.44</v>
+        <v>13.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.22</v>
+        <v>12.7</v>
       </c>
       <c r="R19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="T19" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.67</v>
+        <v>50.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.33</v>
+        <v>12.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.33</v>
+        <v>17.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -8389,70 +8389,70 @@
         <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.59</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP19" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT19" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.57</v>
+        <v>3.36</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.71</v>
+        <v>3.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="CC19" t="n">
         <v>2.71</v>
@@ -8461,31 +8461,31 @@
         <v>2.82</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH19" t="n">
         <v>1.49</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK19" t="n">
         <v>1.52</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN19" t="n">
         <v>1.86</v>
@@ -8494,16 +8494,16 @@
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT19" t="n">
         <v>3.13</v>
@@ -8512,13 +8512,13 @@
         <v>1.5</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY19" t="n">
         <v>1.94</v>
@@ -8527,88 +8527,88 @@
         <v>2.36</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB19" t="n">
         <v>1.22</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>65.29000000000001</v>
+        <v>66.72</v>
       </c>
       <c r="DI19" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.24</v>
+        <v>4.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="DM19" t="n">
-        <v>31</v>
+        <v>31.06</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DO19" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>12</v>
+        <v>12.39</v>
       </c>
       <c r="DQ19" t="n">
-        <v>13.23</v>
+        <v>12.94</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.77</v>
+        <v>51.56</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.94</v>
+        <v>12.06</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.77</v>
+        <v>7.61</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.17</v>
+        <v>4.44</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.7</v>
+        <v>18.44</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC19" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>84.78</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>46.89</v>
+        <v>47.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.56</v>
+        <v>15.7</v>
       </c>
       <c r="R4" t="n">
-        <v>7.89</v>
+        <v>7.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.11</v>
+        <v>49.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.67</v>
+        <v>17.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AF4" t="n">
         <v>0.11</v>
@@ -2356,70 +2356,70 @@
         <v>2.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL4" t="n">
         <v>1.11</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.17</v>
+        <v>5.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.89</v>
+        <v>4.11</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.03</v>
+        <v>2.91</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="CC4" t="n">
         <v>5.19</v>
@@ -2428,13 +2428,13 @@
         <v>5.77</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
@@ -2446,7 +2446,7 @@
         <v>1.55</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL4" t="n">
         <v>1.69</v>
@@ -2458,127 +2458,127 @@
         <v>1.95</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="DH4" t="n">
-        <v>75.33</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.5</v>
+        <v>5.63</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM4" t="n">
-        <v>44</v>
+        <v>44.42</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.44</v>
+        <v>12.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.39</v>
+        <v>13.1</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.06</v>
+        <v>44.89</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.17</v>
+        <v>12.21</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.61</v>
+        <v>7.73</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.73</v>
+        <v>17.84</v>
       </c>
       <c r="EB4" t="n">
         <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,136 +2681,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>59.33</v>
+        <v>53.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>26.11</v>
+        <v>23.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL5" t="n">
         <v>1</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BM5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY5" t="n">
         <v>2.53</v>
@@ -2819,67 +2819,67 @@
         <v>2.54</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.47</v>
+        <v>5.24</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.44</v>
+        <v>6.22</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CG5" t="n">
         <v>2.63</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI5" t="n">
         <v>1.8</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV5" t="n">
         <v>1.9</v>
@@ -2894,19 +2894,19 @@
         <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
         <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
@@ -2915,73 +2915,73 @@
         <v>0.84</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="DH5" t="n">
-        <v>70.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>30.06</v>
+        <v>28.53</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.27</v>
+        <v>10.21</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.73</v>
+        <v>10.63</v>
       </c>
       <c r="DR5" t="n">
         <v>7.84</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.28</v>
+        <v>46.32</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.880000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="DY5" t="n">
-        <v>7</v>
+        <v>7.16</v>
       </c>
       <c r="DZ5" t="n">
         <v>2.89</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
       <c r="EB5" t="n">
         <v>1</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>59.56</v>
+        <v>61.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>32.67</v>
+        <v>33.3</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.44</v>
+        <v>12.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.56</v>
+        <v>8.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO6" t="n">
         <v>0.89</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY6" t="n">
         <v>5.4</v>
@@ -3222,46 +3222,46 @@
         <v>5.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK6" t="n">
         <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
@@ -3270,37 +3270,37 @@
         <v>1.8</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CT6" t="n">
         <v>2.99</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
@@ -3315,76 +3315,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DH6" t="n">
-        <v>73.61</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.12</v>
+        <v>39.11</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.56</v>
+        <v>13.26</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.56</v>
+        <v>7.69</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.06</v>
+        <v>46.68</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.61</v>
+        <v>10.58</v>
       </c>
       <c r="DY6" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.06</v>
+        <v>18.42</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="7">
@@ -4192,61 +4192,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="H9" t="n">
-        <v>96.56</v>
+        <v>94.7</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>56.11</v>
+        <v>55.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>13.11</v>
+        <v>12.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.44</v>
+        <v>9.9</v>
       </c>
       <c r="R9" t="n">
-        <v>5.67</v>
+        <v>5.9</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4258,28 +4258,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>64</v>
+        <v>63.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.56</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
         <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4363,70 +4363,70 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.89</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.72</v>
+        <v>5.05</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.83</v>
+        <v>4.94</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.26</v>
+        <v>5.44</v>
       </c>
       <c r="CC9" t="n">
         <v>1.66</v>
@@ -4435,31 +4435,31 @@
         <v>1.74</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK9" t="n">
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN9" t="n">
         <v>1.98</v>
@@ -4468,25 +4468,25 @@
         <v>1.12</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW9" t="n">
         <v>1.66</v>
@@ -4495,34 +4495,34 @@
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DB9" t="n">
         <v>1.15</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.5</v>
+        <v>95.52</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
@@ -4531,28 +4531,28 @@
         <v>2.05</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.16</v>
+        <v>7.31</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM9" t="n">
-        <v>56.72</v>
+        <v>56.31</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.06</v>
+        <v>11.84</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.609999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4564,28 +4564,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.61</v>
+        <v>62.21</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.89</v>
+        <v>14.84</v>
       </c>
       <c r="DY9" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.83</v>
+        <v>17.63</v>
       </c>
       <c r="EB9" t="n">
         <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="10">
@@ -5226,13 +5226,13 @@
         <v>4.71</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="CA11" t="n">
         <v>4.28</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="CC11" t="n">
         <v>4.98</v>
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5491,139 +5491,139 @@
         <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.67</v>
+        <v>72.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.67</v>
+        <v>35.6</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.89</v>
+        <v>12.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.33</v>
+        <v>46.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>15.78</v>
+        <v>15.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.22</v>
+        <v>11.26</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BO12" t="n">
         <v>1.11</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.28</v>
+        <v>5.58</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU12" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY12" t="n">
         <v>6.64</v>
@@ -5632,28 +5632,28 @@
         <v>6.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.84</v>
+        <v>5.05</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.26</v>
+        <v>5.94</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.36</v>
+        <v>5.91</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI12" t="n">
         <v>1.98</v>
@@ -5665,34 +5665,34 @@
         <v>1.51</v>
       </c>
       <c r="CL12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="CT12" t="n">
         <v>3.12</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV12" t="n">
         <v>2.07</v>
@@ -5704,97 +5704,97 @@
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>69.83</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.39</v>
+        <v>34.89</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.27</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.11</v>
+        <v>12.84</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.94</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.28</v>
+        <v>47.16</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.72</v>
+        <v>6.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.39</v>
+        <v>16.26</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="13">
@@ -6103,7 +6103,7 @@
         <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
@@ -7009,94 +7009,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="H16" t="n">
-        <v>70.62</v>
+        <v>63.22</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.75</v>
+        <v>6.44</v>
       </c>
       <c r="L16" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>42.38</v>
+        <v>37.89</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P16" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>20.62</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>2.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.22</v>
+        <v>10.53</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BO16" t="n">
         <v>1.11</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.61</v>
+        <v>4.79</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.06</v>
+        <v>4.01</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CC16" t="n">
         <v>4.53</v>
@@ -7252,19 +7252,19 @@
         <v>4.2</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CH16" t="n">
         <v>1.43</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.68</v>
@@ -7273,136 +7273,136 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM16" t="n">
         <v>2.38</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="DH16" t="n">
-        <v>73.44</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.89</v>
+        <v>5.26</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM16" t="n">
-        <v>41</v>
+        <v>38.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.17</v>
+        <v>11.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.78</v>
+        <v>11.63</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.33</v>
+        <v>45.73</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.61</v>
+        <v>12.79</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.05</v>
+        <v>4.21</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.11</v>
+        <v>18.42</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.5</v>
+        <v>84.33</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.75</v>
+        <v>49.44</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.62</v>
+        <v>15.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51</v>
+        <v>50.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.25</v>
+        <v>4.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.75</v>
+        <v>17.56</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT2" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY2" t="n">
         <v>1.88</v>
@@ -1610,52 +1610,52 @@
         <v>1.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="CD2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CN2" t="n">
         <v>1.58</v>
       </c>
-      <c r="CE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.57</v>
-      </c>
       <c r="CO2" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.28</v>
@@ -1673,106 +1673,106 @@
         <v>1.61</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
       </c>
       <c r="CY2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="DH2" t="n">
-        <v>84.33</v>
+        <v>83.84</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="DK2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.78</v>
+        <v>49.21</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.11</v>
+        <v>14.95</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.11</v>
+        <v>11.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.67</v>
+        <v>6.74</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.94</v>
+        <v>49.68</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.5</v>
+        <v>13.21</v>
       </c>
       <c r="DY2" t="n">
         <v>8.109999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.39</v>
+        <v>5.11</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.44</v>
+        <v>15.48</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="n">
-        <v>59.11</v>
+        <v>59.7</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>29.11</v>
+        <v>29</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.78</v>
+        <v>45.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.56</v>
+        <v>20.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.28</v>
+        <v>10.16</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="BQ3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>68.42</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="CA3" t="n">
         <v>4.39</v>
       </c>
-      <c r="BR3" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>27.78</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>4.43</v>
-      </c>
       <c r="CB3" t="n">
-        <v>5.14</v>
+        <v>5.06</v>
       </c>
       <c r="CC3" t="n">
         <v>9.029999999999999</v>
@@ -2025,13 +2025,13 @@
         <v>10.12</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.41</v>
@@ -2043,37 +2043,37 @@
         <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT3" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV3" t="n">
         <v>1.88</v>
@@ -2082,67 +2082,67 @@
         <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB3" t="n">
         <v>1.3</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DH3" t="n">
-        <v>56.5</v>
+        <v>56.95</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DM3" t="n">
-        <v>25.89</v>
+        <v>26</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
       <c r="DQ3" t="n">
         <v>12</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41</v>
+        <v>40.53</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.78</v>
+        <v>17.53</v>
       </c>
       <c r="EB3" t="n">
         <v>0.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="Y4" t="n">
         <v>0.2</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.89</v>
+        <v>44.95</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.1</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.68</v>
+        <v>46.63</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>102.11</v>
+        <v>98.8</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>66.56</v>
+        <v>62.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.56</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.11</v>
+        <v>15.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.78</v>
+        <v>6.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.33</v>
+        <v>17.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>2</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU7" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.28</v>
+        <v>6.12</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.05</v>
+        <v>6.86</v>
       </c>
       <c r="CC7" t="n">
         <v>1.45</v>
@@ -3640,40 +3640,40 @@
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CP7" t="n">
         <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
@@ -3684,102 +3684,106 @@
         <v>1.88</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CX7" t="inlineStr"/>
+        <v>1.72</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.49</v>
+      </c>
       <c r="CY7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CZ7" t="inlineStr"/>
+        <v>1.66</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2.57</v>
+      </c>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.61</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ7" t="n">
         <v>1.89</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.89</v>
+        <v>6.68</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.84</v>
+        <v>58.26</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.06</v>
+        <v>10.16</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.72</v>
+        <v>6.84</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.84</v>
+        <v>59.58</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>16.33</v>
+        <v>15.79</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.33</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7</v>
+        <v>6.74</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.33</v>
+        <v>16.42</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8">
@@ -3789,94 +3793,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>65.56</v>
+        <v>66.3</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>28.89</v>
+        <v>30.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="P8" t="n">
-        <v>10.78</v>
+        <v>11.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>9.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>46.89</v>
+        <v>46.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.78</v>
+        <v>13.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3960,70 +3964,70 @@
         <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.720000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BN8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CC8" t="n">
         <v>3.65</v>
@@ -4032,13 +4036,13 @@
         <v>3.94</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH8" t="n">
         <v>1.25</v>
@@ -4047,40 +4051,40 @@
         <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CL8" t="n">
         <v>1.71</v>
       </c>
-      <c r="CK8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>1.69</v>
-      </c>
       <c r="CM8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="CP8" t="n">
         <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
         <v>2.16</v>
@@ -4089,10 +4093,10 @@
         <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.31</v>
@@ -4107,49 +4111,49 @@
         <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DE8" t="n">
         <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DH8" t="n">
-        <v>65.44</v>
+        <v>65.84</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DL8" t="n">
         <v>0.16</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.11</v>
+        <v>33.58</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="DO8" t="n">
         <v>2.05</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.5</v>
+        <v>11.68</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.16</v>
+        <v>10.05</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -4161,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.11</v>
+        <v>49.84</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.28</v>
+        <v>5.42</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.89</v>
+        <v>15.05</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="9">
@@ -4595,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>79.62</v>
+        <v>78.78</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K10" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>43.38</v>
+        <v>42.22</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O10" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>10.25</v>
+        <v>10.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>12.11</v>
       </c>
       <c r="R10" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.75</v>
+        <v>54.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.75</v>
+        <v>12.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.5</v>
+        <v>15.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4766,70 +4770,70 @@
         <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.78</v>
+        <v>3.63</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.890000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.78</v>
+        <v>3.63</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1.11</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BM10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.11</v>
+        <v>4.37</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT10" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BV10" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.16</v>
+        <v>2.48</v>
       </c>
       <c r="CA10" t="n">
         <v>4.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="CC10" t="n">
         <v>4.83</v>
@@ -4841,19 +4845,19 @@
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK10" t="n">
         <v>1.47</v>
@@ -4862,130 +4866,130 @@
         <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN10" t="n">
         <v>1.94</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA10" t="n">
         <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>72.94</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK10" t="n">
         <v>5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>38</v>
+        <v>37.74</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.39</v>
+        <v>11.42</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.11</v>
+        <v>12.16</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.56</v>
+        <v>7.74</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.78</v>
+        <v>52.11</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.89</v>
+        <v>12.73</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.72</v>
+        <v>15.47</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -4998,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.3</v>
@@ -5088,52 +5092,52 @@
         <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI11" t="n">
-        <v>84.25</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.88</v>
+        <v>41.89</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.5</v>
+        <v>9.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5145,82 +5149,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.25</v>
+        <v>48.78</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.12</v>
+        <v>17.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.720000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY11" t="n">
         <v>4.71</v>
@@ -5229,31 +5233,31 @@
         <v>4.79</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.61</v>
+        <v>4.55</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.98</v>
+        <v>4.73</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.53</v>
+        <v>5.21</v>
       </c>
       <c r="CE11" t="n">
         <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.69</v>
@@ -5262,22 +5266,22 @@
         <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5313,52 +5317,52 @@
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH11" t="n">
-        <v>75.39</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.22</v>
+        <v>38.95</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.78</v>
+        <v>10.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.94</v>
+        <v>12.79</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.390000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5370,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.89</v>
+        <v>46.26</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.609999999999999</v>
+        <v>9.84</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.17</v>
+        <v>6.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.83</v>
+        <v>16.95</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="12">
@@ -5804,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5894,139 +5898,139 @@
         <v>2.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>103.44</v>
+        <v>103.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.78</v>
+        <v>6.8</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>68.22</v>
+        <v>67.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.11</v>
       </c>
-      <c r="AU13" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BM13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.67</v>
+        <v>4.89</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BT13" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV13" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
         <v>1.22</v>
@@ -6035,22 +6039,22 @@
         <v>1.21</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="CE13" t="n">
         <v>1.03</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CG13" t="n">
         <v>3.99</v>
@@ -6059,45 +6063,45 @@
         <v>1.68</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="CP13" t="n">
         <v>1.31</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX13" t="n">
         <v>1.55</v>
@@ -6115,85 +6119,85 @@
         <v>1.11</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.88</v>
+        <v>107.58</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM13" t="n">
-        <v>67.56</v>
+        <v>67.05</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.06</v>
+        <v>11.16</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.56</v>
+        <v>11.47</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.44</v>
+        <v>60.63</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>19.17</v>
+        <v>18.84</v>
       </c>
       <c r="DY13" t="n">
-        <v>12.06</v>
+        <v>11.95</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7.11</v>
+        <v>6.9</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.12</v>
+        <v>15.79</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6207,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.44</v>
@@ -6293,139 +6297,139 @@
         <v>1.56</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>112</v>
+        <v>111.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.67</v>
+        <v>5.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN14" t="n">
-        <v>56.11</v>
+        <v>54.8</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.44</v>
+        <v>57.7</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.78</v>
+        <v>12.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.11</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.22</v>
+        <v>14.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.17</v>
+        <v>10.37</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.39</v>
+        <v>3.26</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="BO14" t="n">
         <v>1.11</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.06</v>
+        <v>5.26</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY14" t="n">
         <v>1.67</v>
@@ -6434,169 +6438,169 @@
         <v>1.64</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="CC14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CG14" t="n">
         <v>2.55</v>
       </c>
-      <c r="CD14" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>2.49</v>
-      </c>
       <c r="CH14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CT14" t="n">
         <v>3.06</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF14" t="n">
         <v>1.11</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.39</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.56</v>
+        <v>6.68</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM14" t="n">
-        <v>55.39</v>
+        <v>54.74</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.44</v>
+        <v>12.47</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.44</v>
+        <v>9.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.33</v>
+        <v>58.42</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.73</v>
+        <v>13</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.89</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.77</v>
+        <v>16.58</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="15">
@@ -6606,61 +6610,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="H15" t="n">
-        <v>69.89</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="K15" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>34.33</v>
+        <v>34.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>14.22</v>
+        <v>13.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6676,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.78</v>
+        <v>42.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.67</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.89</v>
+        <v>18.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6781,70 @@
         <v>1.33</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.56</v>
+        <v>11.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BT15" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.03</v>
+        <v>4.6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.99</v>
+        <v>4.58</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.77</v>
+        <v>4.83</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.38</v>
+        <v>5.45</v>
       </c>
       <c r="CC15" t="n">
         <v>8.43</v>
@@ -6852,55 +6856,55 @@
         <v>1.16</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
         <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK15" t="n">
         <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO15" t="n">
         <v>1.08</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CT15" t="n">
         <v>3.04</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW15" t="n">
         <v>1.84</v>
@@ -6909,97 +6913,97 @@
         <v>1.59</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.34</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DB15" t="n">
         <v>1.25</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.94</v>
+        <v>69</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.34</v>
+        <v>5.42</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>35.16</v>
+        <v>35.05</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.73</v>
+        <v>0.79</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.77</v>
+        <v>13.58</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.33</v>
+        <v>10.47</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.11</v>
+        <v>7.16</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.34</v>
+        <v>41.05</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.22</v>
+        <v>10.89</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.39</v>
+        <v>7.26</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.83</v>
+        <v>3.63</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.33</v>
+        <v>17.26</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="16">
@@ -7412,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7502,139 +7506,139 @@
         <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>67.11</v>
+        <v>70.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>28.22</v>
+        <v>30.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.67</v>
+        <v>12.2</v>
       </c>
       <c r="AR17" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD17" t="n">
         <v>14</v>
       </c>
-      <c r="AS17" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="AT17" t="n">
+      <c r="BE17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO17" t="n">
         <v>1.11</v>
       </c>
-      <c r="AU17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BP17" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY17" t="n">
         <v>2.77</v>
@@ -7643,16 +7647,16 @@
         <v>3.13</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
@@ -7667,13 +7671,13 @@
         <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.64</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL17" t="n">
         <v>1.92</v>
@@ -7688,7 +7692,7 @@
         <v>1.16</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.83</v>
@@ -7700,13 +7704,13 @@
         <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU17" t="n">
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW17" t="n">
         <v>1.77</v>
@@ -7715,13 +7719,13 @@
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB17" t="n">
         <v>1.26</v>
@@ -7730,82 +7734,82 @@
         <v>1.84</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DG17" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="DH17" t="n">
-        <v>68.67</v>
+        <v>70.53</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DK17" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DM17" t="n">
-        <v>34.66</v>
+        <v>35.53</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.73</v>
+        <v>11.53</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.06</v>
+        <v>12.21</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.34</v>
+        <v>8.26</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50</v>
+        <v>50.26</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.5</v>
+        <v>10.84</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.28</v>
+        <v>6.63</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.94</v>
+        <v>14.95</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7819,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7827,49 +7831,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H18" t="n">
-        <v>78.88</v>
+        <v>78.44</v>
       </c>
       <c r="I18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="K18" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="L18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>37.88</v>
+        <v>37.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="P18" t="n">
-        <v>10.62</v>
+        <v>10.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>12.12</v>
+        <v>11.78</v>
       </c>
       <c r="R18" t="n">
-        <v>10.5</v>
+        <v>10.44</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7885,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.75</v>
+        <v>47.67</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>10.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.25</v>
+        <v>7.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AC18" t="n">
-        <v>22</v>
+        <v>22.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AF18" t="n">
         <v>0.2</v>
@@ -7986,70 +7990,70 @@
         <v>2.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.44</v>
+        <v>10.42</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BS18" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX18" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY18" t="n">
-        <v>5.92</v>
+        <v>5.54</v>
       </c>
       <c r="BZ18" t="n">
-        <v>6.37</v>
+        <v>5.95</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="CC18" t="n">
         <v>4.84</v>
@@ -8058,13 +8062,13 @@
         <v>5.2</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG18" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH18" t="n">
         <v>1.35</v>
@@ -8079,13 +8083,13 @@
         <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO18" t="n">
         <v>1.19</v>
@@ -8094,7 +8098,7 @@
         <v>1.83</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8109,19 +8113,19 @@
         <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA18" t="n">
         <v>1.78</v>
@@ -8133,46 +8137,46 @@
         <v>1.89</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="DE18" t="n">
         <v>0.11</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DH18" t="n">
-        <v>66.61</v>
+        <v>67.05</v>
       </c>
       <c r="DI18" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM18" t="n">
-        <v>30.56</v>
+        <v>30.9</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.78</v>
+        <v>10.74</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.16</v>
+        <v>12</v>
       </c>
       <c r="DR18" t="n">
         <v>9.890000000000001</v>
@@ -8187,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.17</v>
+        <v>46.21</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.17</v>
+        <v>9.58</v>
       </c>
       <c r="DY18" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.5</v>
+        <v>19.74</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8308,139 +8312,139 @@
         <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="n">
-        <v>60.12</v>
+        <v>66.78</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>27.38</v>
+        <v>33.11</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.5</v>
+        <v>11.56</v>
       </c>
       <c r="AR19" t="n">
-        <v>13.25</v>
+        <v>12.78</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.25</v>
+        <v>8.56</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>53</v>
+        <v>54.67</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>12.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.38</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.12</v>
+        <v>19.44</v>
       </c>
       <c r="BE19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BM19" t="n">
         <v>1.05</v>
       </c>
-      <c r="BF19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BN19" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY19" t="n">
         <v>3.36</v>
@@ -8449,34 +8453,34 @@
         <v>3.48</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="CE19" t="n">
         <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK19" t="n">
         <v>1.52</v>
@@ -8485,133 +8489,133 @@
         <v>1.98</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CO19" t="n">
         <v>1.2</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX19" t="n">
         <v>1.58</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA19" t="n">
         <v>1.87</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="DH19" t="n">
-        <v>66.72</v>
+        <v>69.53</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.44</v>
+        <v>4.58</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM19" t="n">
-        <v>31.06</v>
+        <v>33.58</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.39</v>
+        <v>12.37</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.94</v>
+        <v>12.74</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.67</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>51.56</v>
+        <v>52.42</v>
       </c>
       <c r="DW19" t="n">
         <v>0.11</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.06</v>
+        <v>12.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.61</v>
+        <v>7.95</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.44</v>
+        <v>18.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>83.40000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>6.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>14.7</v>
+        <v>14.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.2</v>
+        <v>10.82</v>
       </c>
       <c r="R2" t="n">
-        <v>6.9</v>
+        <v>6.55</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.1</v>
+        <v>49.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.1</v>
+        <v>14.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.5</v>
+        <v>5.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.6</v>
+        <v>14.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.89</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BQ2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BW2" t="n">
         <v>5</v>
       </c>
-      <c r="BR2" t="n">
-        <v>89.47</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>63.16</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>42.11</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>15.79</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX2" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.9</v>
+        <v>5.02</v>
       </c>
       <c r="CC2" t="n">
         <v>1.78</v>
@@ -1622,34 +1622,34 @@
         <v>1.86</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CI2" t="n">
         <v>1.99</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CO2" t="n">
         <v>0.98</v>
@@ -1658,25 +1658,25 @@
         <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CT2" t="n">
         <v>3.25</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1691,25 +1691,25 @@
         <v>1.91</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="DH2" t="n">
-        <v>83.84</v>
+        <v>85.2</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
@@ -1718,61 +1718,61 @@
         <v>3.05</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.9</v>
+        <v>6.25</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.21</v>
+        <v>49.75</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="DP2" t="n">
         <v>14.95</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.05</v>
+        <v>10.85</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.74</v>
+        <v>6.55</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.68</v>
+        <v>49.85</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.21</v>
+        <v>13.4</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.48</v>
+        <v>15.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>59.7</v>
+        <v>59.55</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>29</v>
+        <v>28.09</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P3" t="n">
-        <v>8.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>11.09</v>
       </c>
       <c r="R3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.3</v>
+        <v>44.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.7</v>
+        <v>19.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.11</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.5</v>
+        <v>4.31</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.83</v>
+        <v>4.7</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.39</v>
+        <v>4.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.06</v>
+        <v>5.25</v>
       </c>
       <c r="CC3" t="n">
         <v>9.029999999999999</v>
@@ -2025,19 +2025,19 @@
         <v>10.12</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CG3" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.91</v>
@@ -2049,31 +2049,31 @@
         <v>1.78</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CO3" t="n">
         <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CT3" t="n">
         <v>2.99</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
         <v>1.88</v>
@@ -2085,64 +2085,64 @@
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DH3" t="n">
-        <v>56.95</v>
+        <v>57</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM3" t="n">
-        <v>26</v>
+        <v>25.65</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.05</v>
+        <v>9.75</v>
       </c>
       <c r="DQ3" t="n">
         <v>12</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.470000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.53</v>
+        <v>40.3</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.369999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.53</v>
+        <v>17.25</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>81.67</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>34</v>
+        <v>33.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>10.33</v>
+        <v>10.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.56</v>
+        <v>11.8</v>
       </c>
       <c r="R5" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="S5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>48.89</v>
+        <v>48.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.33</v>
+        <v>10.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.22</v>
+        <v>7.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.11</v>
+        <v>20.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>1.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.84</v>
+        <v>10.65</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU5" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CC5" t="n">
         <v>5.24</v>
@@ -2831,19 +2831,19 @@
         <v>6.22</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH5" t="n">
         <v>1.26</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.74</v>
@@ -2852,34 +2852,34 @@
         <v>1.33</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP5" t="n">
         <v>1.95</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS5" t="n">
         <v>2.87</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CV5" t="n">
         <v>1.9</v>
@@ -2888,13 +2888,13 @@
         <v>1.92</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
         <v>1.88</v>
@@ -2906,49 +2906,49 @@
         <v>2.03</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DH5" t="n">
-        <v>66.90000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.53</v>
+        <v>28.45</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.63</v>
+        <v>10.8</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.84</v>
+        <v>7.7</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.32</v>
+        <v>46.4</v>
       </c>
       <c r="DW5" t="n">
         <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.05</v>
+        <v>10.2</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.16</v>
+        <v>7.15</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.26</v>
+        <v>18.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.5</v>
+        <v>63.73</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.3</v>
+        <v>31.82</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.9</v>
+        <v>12.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.3</v>
+        <v>10.55</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.3</v>
       </c>
-      <c r="AW6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.32</v>
-      </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BN6" t="n">
         <v>2</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="BR6" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
         <v>5.4</v>
@@ -3222,34 +3222,34 @@
         <v>5.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.39</v>
+        <v>4.54</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.46</v>
+        <v>5.01</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.41</v>
+        <v>5.15</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CK6" t="n">
         <v>1.52</v>
@@ -3264,31 +3264,31 @@
         <v>1.86</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CT6" t="n">
         <v>2.99</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CX6" t="n">
         <v>1.58</v>
@@ -3303,88 +3303,88 @@
         <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="DH6" t="n">
-        <v>73.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.11</v>
+        <v>38</v>
       </c>
       <c r="DN6" t="n">
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.26</v>
+        <v>12.9</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.69</v>
+        <v>7.75</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.63</v>
+        <v>46.65</v>
       </c>
       <c r="DW6" t="n">
         <v>0.1</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.58</v>
+        <v>10.4</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.42</v>
+        <v>18.85</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>1.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.11</v>
+        <v>94.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.44</v>
+        <v>7.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>53.11</v>
+        <v>52.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.56</v>
+        <v>9.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57.67</v>
+        <v>58.3</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.56</v>
+        <v>16.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.22</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>15.33</v>
+        <v>14.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BX7" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>1.35</v>
@@ -3625,34 +3625,34 @@
         <v>1.38</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.86</v>
+        <v>6.96</v>
       </c>
       <c r="CC7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="CE7" t="n">
         <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="CH7" t="n">
         <v>1.78</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
@@ -3661,10 +3661,10 @@
         <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO7" t="n">
         <v>1.09</v>
@@ -3681,13 +3681,13 @@
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3699,91 +3699,91 @@
         <v>2.57</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB7" t="n">
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DE7" t="n">
         <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DG7" t="n">
         <v>3.05</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.09999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.68</v>
+        <v>6.55</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.26</v>
+        <v>57.9</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.16</v>
+        <v>9.85</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.84</v>
+        <v>6.8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.58</v>
+        <v>59.8</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.79</v>
+        <v>15.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.74</v>
+        <v>6.95</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.42</v>
+        <v>16.1</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -4075,13 +4075,13 @@
         <v>2.31</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU8" t="n">
         <v>1.55</v>
@@ -4096,13 +4096,13 @@
         <v>1.61</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
@@ -4111,7 +4111,7 @@
         <v>1.74</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE8" t="n">
         <v>0.16</v>
@@ -4827,13 +4827,13 @@
         <v>2.45</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="CA10" t="n">
         <v>4.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="CC10" t="n">
         <v>4.83</v>
@@ -4884,13 +4884,13 @@
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT10" t="n">
         <v>3.03</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV10" t="n">
         <v>2.27</v>
@@ -4911,13 +4911,13 @@
         <v>1.96</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DE10" t="n">
         <v>0.26</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.11</v>
@@ -5495,139 +5495,139 @@
         <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.3</v>
+        <v>74.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.6</v>
+        <v>36.27</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.4</v>
+        <v>12.64</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.1</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.2</v>
+        <v>46.73</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>15.6</v>
+        <v>15.45</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BG12" t="n">
         <v>2.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.26</v>
+        <v>11.05</v>
       </c>
       <c r="BI12" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
         <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU12" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY12" t="n">
         <v>6.64</v>
@@ -5636,28 +5636,28 @@
         <v>6.72</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.57</v>
+        <v>4.52</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.94</v>
+        <v>5.8</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.91</v>
+        <v>5.81</v>
       </c>
       <c r="CE12" t="n">
         <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI12" t="n">
         <v>1.98</v>
@@ -5666,52 +5666,52 @@
         <v>1.75</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL12" t="n">
         <v>1.98</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
         <v>1.9</v>
@@ -5720,52 +5720,52 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="DE12" t="n">
         <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="DG12" t="n">
         <v>2</v>
       </c>
       <c r="DH12" t="n">
-        <v>69.79000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DK12" t="n">
         <v>4.05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.89</v>
+        <v>35.3</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.050000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.84</v>
+        <v>12.95</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.050000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.16</v>
+        <v>47.4</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.74</v>
+        <v>6.6</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.05</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.26</v>
+        <v>16.15</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -6441,13 +6441,13 @@
         <v>4.27</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="CC14" t="n">
         <v>2.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CE14" t="n">
         <v>0.93</v>
@@ -6492,7 +6492,7 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CT14" t="n">
         <v>3.06</v>
@@ -6525,7 +6525,7 @@
         <v>1.59</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE14" t="n">
         <v>0.31</v>
@@ -7704,7 +7704,7 @@
         <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CU17" t="n">
         <v>1.46</v>
@@ -7716,16 +7716,16 @@
         <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DB17" t="n">
         <v>1.26</v>
@@ -7734,7 +7734,7 @@
         <v>1.84</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="DE17" t="n">
         <v>0.1</v>
@@ -8119,13 +8119,13 @@
         <v>1.89</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA18" t="n">
         <v>1.78</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>2.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>65.89</v>
+        <v>66.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.22</v>
+        <v>4.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.11</v>
+        <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.89</v>
+        <v>11.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.109999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.78</v>
+        <v>10.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.58</v>
+        <v>11.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
         <v>2.89</v>
@@ -2416,16 +2416,16 @@
         <v>2.91</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.22</v>
+        <v>4.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.82</v>
+        <v>4.84</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.19</v>
+        <v>5.32</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.77</v>
+        <v>5.85</v>
       </c>
       <c r="CE4" t="n">
         <v>1.19</v>
@@ -2434,16 +2434,16 @@
         <v>2.15</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK4" t="n">
         <v>1.32</v>
@@ -2452,25 +2452,25 @@
         <v>1.69</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO4" t="n">
         <v>1.1</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CT4" t="n">
         <v>3.2</v>
@@ -2479,106 +2479,106 @@
         <v>1.63</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.54</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DG4" t="n">
         <v>2.5</v>
       </c>
-      <c r="DE4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DG4" t="n">
-        <v>2.58</v>
-      </c>
       <c r="DH4" t="n">
-        <v>75.73999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.63</v>
+        <v>5.4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.42</v>
+        <v>43.7</v>
       </c>
       <c r="DN4" t="n">
         <v>1.05</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.53</v>
+        <v>12.4</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.1</v>
+        <v>12.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.369999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.95</v>
+        <v>44.25</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.21</v>
+        <v>11.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.73</v>
+        <v>7.55</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.84</v>
+        <v>17.9</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="5">
@@ -3793,94 +3793,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>66.3</v>
+        <v>66.64</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>30.2</v>
+        <v>30.91</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="P8" t="n">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>46.7</v>
+        <v>46.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>8.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.3</v>
+        <v>13.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3964,70 +3964,70 @@
         <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.58</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.74</v>
+        <v>4.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC8" t="n">
         <v>3.65</v>
@@ -4036,43 +4036,43 @@
         <v>3.94</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CG8" t="n">
         <v>2.72</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CP8" t="n">
         <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
@@ -4093,100 +4093,100 @@
         <v>1.71</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB8" t="n">
         <v>1.23</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>65.84</v>
+        <v>66.05</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.58</v>
+        <v>33.8</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.68</v>
+        <v>11.65</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.05</v>
+        <v>10.25</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.42</v>
+        <v>9.6</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.84</v>
+        <v>49.45</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.05</v>
+        <v>15.25</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
@@ -4286,139 +4286,139 @@
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.44</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.22</v>
+        <v>7.1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.33</v>
+        <v>55.7</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.11</v>
+        <v>6.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>61.22</v>
+        <v>60</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.11</v>
+        <v>16.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.47</v>
+        <v>10.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.21</v>
+        <v>4.55</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>1.96</v>
@@ -4427,22 +4427,22 @@
         <v>1.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.44</v>
+        <v>5.39</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="CD9" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="CE9" t="n">
         <v>1.21</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CG9" t="n">
         <v>3.78</v>
@@ -4451,22 +4451,22 @@
         <v>1.66</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL9" t="n">
         <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO9" t="n">
         <v>1.12</v>
@@ -4475,7 +4475,7 @@
         <v>1.45</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CR9" t="n">
         <v>1.31</v>
@@ -4490,7 +4490,7 @@
         <v>1.72</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW9" t="n">
         <v>1.66</v>
@@ -4517,79 +4517,79 @@
         <v>2.21</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="DH9" t="n">
-        <v>95.52</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.31</v>
+        <v>7.25</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>56.31</v>
+        <v>55.55</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.84</v>
+        <v>11.65</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.369999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR9" t="n">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>62.21</v>
+        <v>61.55</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.84</v>
+        <v>14.35</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.109999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.74</v>
+        <v>5.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.63</v>
+        <v>17.7</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4689,139 +4689,139 @@
         <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>67.59999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.9</v>
+        <v>5.27</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.7</v>
+        <v>33.27</v>
       </c>
       <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1.1</v>
       </c>
-      <c r="AP10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.37</v>
+        <v>4.65</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.05</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT10" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BU10" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BV10" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY10" t="n">
         <v>2.45</v>
@@ -4830,31 +4830,31 @@
         <v>2.41</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.83</v>
+        <v>4.63</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="CE10" t="n">
         <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.6</v>
@@ -4866,28 +4866,28 @@
         <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU10" t="n">
         <v>1.54</v>
@@ -4902,13 +4902,13 @@
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB10" t="n">
         <v>1.22</v>
@@ -4917,82 +4917,82 @@
         <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="DG10" t="n">
         <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>72.90000000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DK10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.74</v>
+        <v>37.3</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.42</v>
+        <v>11.85</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.16</v>
+        <v>12</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.74</v>
+        <v>8.25</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.11</v>
+        <v>51.45</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.73</v>
+        <v>12.55</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.47</v>
+        <v>15.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5002,94 +5002,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>68.3</v>
+        <v>66.73</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="K11" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M11" t="n">
-        <v>36.3</v>
+        <v>35.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>11.5</v>
+        <v>11.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.7</v>
+        <v>13.55</v>
       </c>
       <c r="R11" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>44</v>
+        <v>43.91</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.6</v>
+        <v>17.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5173,70 +5173,70 @@
         <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.74</v>
+        <v>9.65</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="CC11" t="n">
         <v>4.73</v>
@@ -5245,16 +5245,16 @@
         <v>5.21</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
         <v>2.45</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI11" t="n">
         <v>2.09</v>
@@ -5266,7 +5266,7 @@
         <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM11" t="n">
         <v>2.44</v>
@@ -5323,79 +5323,79 @@
         <v>3.03</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
         <v>0.95</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DH11" t="n">
-        <v>74.79000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="DI11" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
         <v>0.05</v>
       </c>
       <c r="DM11" t="n">
-        <v>38.95</v>
+        <v>38.15</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.69</v>
+        <v>10.7</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.79</v>
+        <v>12.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.48</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.26</v>
+        <v>46.1</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.84</v>
+        <v>9.65</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.42</v>
+        <v>6.3</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.95</v>
+        <v>17.55</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>112.33</v>
+        <v>110.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K13" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M13" t="n">
-        <v>66.89</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>61.11</v>
+        <v>60.1</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.11</v>
+        <v>18.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.89</v>
+        <v>7.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.67</v>
+        <v>17.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
         <v>0.3</v>
@@ -5979,70 +5979,70 @@
         <v>1.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.42</v>
+        <v>5.7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.89</v>
+        <v>4.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT13" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV13" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.39</v>
+        <v>6.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.81</v>
+        <v>7.64</v>
       </c>
       <c r="CC13" t="n">
         <v>1.48</v>
@@ -6051,43 +6051,43 @@
         <v>1.5</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CH13" t="n">
         <v>1.68</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.29</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6098,10 +6098,10 @@
         <v>1.96</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
         <v>1.55</v>
@@ -6116,88 +6116,88 @@
         <v>2.1</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.58</v>
+        <v>106.8</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ13" t="n">
         <v>2.1</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.47</v>
+        <v>7.45</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DM13" t="n">
-        <v>67.05</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.16</v>
+        <v>11.45</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.47</v>
+        <v>11.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.63</v>
+        <v>60.15</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>18.84</v>
+        <v>18.7</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.95</v>
+        <v>11.9</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.79</v>
+        <v>16.15</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -6207,94 +6207,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>86.78</v>
+        <v>90.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="K14" t="n">
-        <v>8.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>54.67</v>
+        <v>57.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="P14" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.56</v>
+        <v>9.1</v>
       </c>
       <c r="R14" t="n">
-        <v>5.89</v>
+        <v>5.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>59.22</v>
+        <v>60.2</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.67</v>
+        <v>14.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB14" t="n">
         <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.33</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6378,70 +6378,70 @@
         <v>2.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.37</v>
+        <v>10.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT14" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.27</v>
+        <v>4.31</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="CC14" t="n">
         <v>2.46</v>
@@ -6450,40 +6450,40 @@
         <v>2.49</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.04</v>
@@ -6492,7 +6492,7 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CT14" t="n">
         <v>3.06</v>
@@ -6501,22 +6501,22 @@
         <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="DB14" t="n">
         <v>1.18</v>
@@ -6525,82 +6525,82 @@
         <v>1.59</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.79000000000001</v>
+        <v>101.15</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.68</v>
+        <v>6.95</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>54.74</v>
+        <v>55.95</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.47</v>
+        <v>12.35</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.37</v>
+        <v>7.2</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.42</v>
+        <v>58.95</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.210000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.58</v>
+        <v>17.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.89</v>
+        <v>4.6</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>34.1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.67</v>
+        <v>7.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>39.89</v>
+        <v>39.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.44</v>
+        <v>10.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.78</v>
+        <v>15.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.68</v>
+        <v>11.35</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BY15" t="n">
         <v>4.6</v>
@@ -6841,25 +6841,25 @@
         <v>4.58</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.83</v>
+        <v>4.59</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="CC15" t="n">
-        <v>8.43</v>
+        <v>7.59</v>
       </c>
       <c r="CD15" t="n">
-        <v>10.45</v>
+        <v>10.04</v>
       </c>
       <c r="CE15" t="n">
         <v>1.16</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CG15" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
@@ -6877,13 +6877,13 @@
         <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CP15" t="n">
         <v>1.72</v>
@@ -6904,22 +6904,22 @@
         <v>1.58</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX15" t="n">
         <v>1.59</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB15" t="n">
         <v>1.25</v>
@@ -6934,43 +6934,43 @@
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="DG15" t="n">
         <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>69</v>
+        <v>66.25</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.42</v>
+        <v>5.25</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>35.05</v>
+        <v>34.15</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.58</v>
+        <v>13.6</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.16</v>
+        <v>7.05</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.05</v>
+        <v>40.85</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.63</v>
+        <v>3.75</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.26</v>
+        <v>16.95</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="16">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7109,133 +7109,133 @@
         <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI16" t="n">
-        <v>75.7</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN16" t="n">
-        <v>39.9</v>
+        <v>39.82</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.7</v>
+        <v>10.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.6</v>
+        <v>11.55</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AU16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BO16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="BR16" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY16" t="n">
         <v>2.21</v>
@@ -7244,28 +7244,28 @@
         <v>2.2</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.53</v>
+        <v>4.28</v>
       </c>
       <c r="CD16" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="CE16" t="n">
         <v>1.23</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG16" t="n">
         <v>3.04</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI16" t="n">
         <v>2.05</v>
@@ -7277,22 +7277,22 @@
         <v>1.39</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM16" t="n">
         <v>2.38</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7337,76 +7337,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DH16" t="n">
-        <v>69.79000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM16" t="n">
         <v>38.95</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.05</v>
+        <v>11.1</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.32</v>
+        <v>7.3</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>45.73</v>
+        <v>46.3</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.79</v>
+        <v>12.55</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.58</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.42</v>
+        <v>18.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -7416,94 +7416,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>70.22</v>
+        <v>75.8</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M17" t="n">
-        <v>41.11</v>
+        <v>43.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>10.78</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.11</v>
+        <v>11.3</v>
       </c>
       <c r="R17" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54</v>
+        <v>54.7</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.11</v>
+        <v>12</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.22</v>
+        <v>7.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
         <v>0.1</v>
@@ -7587,70 +7587,70 @@
         <v>2.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.529999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV17" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC17" t="n">
         <v>3.5</v>
@@ -7662,16 +7662,16 @@
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CH17" t="n">
         <v>1.37</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.64</v>
@@ -7689,7 +7689,7 @@
         <v>1.76</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP17" t="n">
         <v>1.8</v>
@@ -7704,19 +7704,19 @@
         <v>2.74</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU17" t="n">
         <v>1.46</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
         <v>1.95</v>
@@ -7740,73 +7740,73 @@
         <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="DG17" t="n">
         <v>2.05</v>
       </c>
       <c r="DH17" t="n">
-        <v>70.53</v>
+        <v>73.3</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="DL17" t="n">
         <v>0.05</v>
       </c>
       <c r="DM17" t="n">
-        <v>35.53</v>
+        <v>37.05</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.53</v>
+        <v>11.35</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.21</v>
+        <v>12.7</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.26</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.26</v>
+        <v>50.8</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.84</v>
+        <v>11.3</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.63</v>
+        <v>7</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.95</v>
+        <v>15.25</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC17" t="n">
         <v>2.05</v>
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7909,139 +7909,139 @@
         <v>1.89</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" t="n">
-        <v>56.8</v>
+        <v>60.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK18" t="n">
         <v>3</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>24.7</v>
+        <v>28.82</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
       <c r="AR18" t="n">
-        <v>12.2</v>
+        <v>12.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>44.9</v>
+        <v>46.09</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.5</v>
+        <v>9.09</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>6.82</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD18" t="n">
-        <v>17.5</v>
+        <v>17.64</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="BR18" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT18" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU18" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV18" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW18" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX18" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY18" t="n">
         <v>5.54</v>
@@ -8050,16 +8050,16 @@
         <v>5.95</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="CC18" t="n">
         <v>4.84</v>
       </c>
       <c r="CD18" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="CE18" t="n">
         <v>1.27</v>
@@ -8077,13 +8077,13 @@
         <v>1.9</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CM18" t="n">
         <v>2.16</v>
@@ -8092,7 +8092,7 @@
         <v>1.7</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP18" t="n">
         <v>1.83</v>
@@ -8113,22 +8113,22 @@
         <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX18" t="n">
         <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB18" t="n">
         <v>1.28</v>
@@ -8137,82 +8137,82 @@
         <v>1.89</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>67.05</v>
+        <v>68.7</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM18" t="n">
-        <v>30.9</v>
+        <v>32.85</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.890000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.21</v>
+        <v>46.8</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="DY18" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.74</v>
+        <v>19.7</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -8234,79 +8234,79 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>72</v>
+        <v>67.73</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M19" t="n">
-        <v>34</v>
+        <v>32.73</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="P19" t="n">
-        <v>13.1</v>
+        <v>12.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.7</v>
+        <v>12.64</v>
       </c>
       <c r="R19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.4</v>
+        <v>51.55</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.9</v>
+        <v>18.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -8393,70 +8393,70 @@
         <v>1.89</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.68</v>
+        <v>8.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="BQ19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="CA19" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="CC19" t="n">
         <v>2.6</v>
@@ -8480,22 +8480,22 @@
         <v>2.06</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CK19" t="n">
         <v>1.52</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP19" t="n">
         <v>1.71</v>
@@ -8516,22 +8516,22 @@
         <v>1.49</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX19" t="n">
         <v>1.58</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB19" t="n">
         <v>1.23</v>
@@ -8543,76 +8543,76 @@
         <v>2.8</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DH19" t="n">
-        <v>69.53</v>
+        <v>67.3</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>33.58</v>
+        <v>32.9</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.37</v>
+        <v>12.2</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.369999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.42</v>
+        <v>52.95</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.42</v>
+        <v>12.15</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.95</v>
+        <v>7.8</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.63</v>
+        <v>18.95</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EC19" t="n">
         <v>1.95</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>43.91</v>
+        <v>43.82</v>
       </c>
       <c r="Y11" t="n">
         <v>0.27</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.1</v>
+        <v>46.05</v>
       </c>
       <c r="DW11" t="n">
         <v>0.15</v>
@@ -6279,19 +6279,19 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="AA14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AC14" t="n">
         <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="n">
         <v>1.4</v>
@@ -6585,19 +6585,19 @@
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.3</v>
+        <v>13.35</v>
       </c>
       <c r="DY14" t="n">
         <v>8.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="EA14" t="n">
         <v>17.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC14" t="n">
         <v>1.75</v>
@@ -7160,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42.91</v>
+        <v>43</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.55</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.3</v>
+        <v>46.35</v>
       </c>
       <c r="DW16" t="n">
         <v>0.3</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>53.89</v>
+        <v>55.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.67</v>
+        <v>24.1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AT3" t="n">
         <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>35.22</v>
+        <v>37</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.1</v>
+        <v>10.43</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.55</v>
+        <v>4.76</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.45</v>
+        <v>4.62</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU3" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY3" t="n">
         <v>4.31</v>
@@ -2013,43 +2013,43 @@
         <v>4.7</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="CC3" t="n">
-        <v>9.029999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="CD3" t="n">
-        <v>10.12</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN3" t="n">
         <v>1.85</v>
@@ -2061,43 +2061,43 @@
         <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD3" t="n">
         <v>3.14</v>
@@ -2106,43 +2106,43 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DH3" t="n">
-        <v>57</v>
+        <v>57.76</v>
       </c>
       <c r="DI3" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="DM3" t="n">
-        <v>25.65</v>
+        <v>26.19</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.75</v>
+        <v>9.66</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.3</v>
+        <v>40.9</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DX3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="DZ3" t="n">
         <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.25</v>
+        <v>17.48</v>
       </c>
       <c r="EB3" t="n">
         <v>0.88</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="4">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>87.67</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>45.56</v>
+        <v>47.8</v>
       </c>
       <c r="N6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.89</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.11</v>
+        <v>49.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.44</v>
+        <v>12.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.44</v>
+        <v>8.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.11</v>
+        <v>16.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>2.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BN6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="BR6" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS6" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.4</v>
+        <v>5.05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.54</v>
+        <v>4.49</v>
       </c>
       <c r="CC6" t="n">
         <v>5.01</v>
@@ -3237,10 +3237,10 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
@@ -3252,55 +3252,55 @@
         <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN6" t="n">
         <v>1.86</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
         <v>2.62</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU6" t="n">
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX6" t="n">
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3315,76 +3315,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="DH6" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM6" t="n">
-        <v>38</v>
+        <v>39.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.55</v>
+        <v>10.43</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.75</v>
+        <v>7.53</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.65</v>
+        <v>46.67</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.4</v>
+        <v>10.86</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.85</v>
+        <v>18.52</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="7">
@@ -6207,94 +6207,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="H14" t="n">
-        <v>90.8</v>
+        <v>93.64</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M14" t="n">
-        <v>57.1</v>
+        <v>57.64</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="P14" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.1</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>5.7</v>
+        <v>5.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60.2</v>
+        <v>60.45</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.3</v>
+        <v>13.91</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.1</v>
+        <v>4.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>20.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6378,70 +6378,70 @@
         <v>2.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.3</v>
+        <v>5.24</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.15</v>
+        <v>5.29</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT14" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BV14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="CC14" t="n">
         <v>2.46</v>
@@ -6450,16 +6450,16 @@
         <v>2.49</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="CI14" t="n">
         <v>2.24</v>
@@ -6468,43 +6468,43 @@
         <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="CP14" t="n">
         <v>1.59</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6522,85 +6522,85 @@
         <v>1.18</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="DH14" t="n">
-        <v>101.15</v>
+        <v>102.14</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="DK14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="DR14" t="n">
         <v>6.95</v>
       </c>
-      <c r="DL14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>55.95</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="DR14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="DS14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>58.95</v>
+        <v>59.14</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.35</v>
+        <v>13.19</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.5</v>
+        <v>8.52</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.85</v>
+        <v>4.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.05</v>
+        <v>17.57</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="15">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7506,139 +7506,139 @@
         <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>70.8</v>
+        <v>71.09</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AN17" t="n">
-        <v>30.5</v>
+        <v>31.18</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.2</v>
+        <v>11.82</v>
       </c>
       <c r="AR17" t="n">
-        <v>14.1</v>
+        <v>14.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.5</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>46.9</v>
+        <v>47.73</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.6</v>
+        <v>10.09</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="BD17" t="n">
-        <v>14</v>
+        <v>14.36</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG17" t="n">
         <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU17" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY17" t="n">
         <v>2.74</v>
@@ -7647,22 +7647,22 @@
         <v>3.1</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CG17" t="n">
         <v>2.9</v>
@@ -7674,10 +7674,10 @@
         <v>1.91</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL17" t="n">
         <v>1.92</v>
@@ -7686,40 +7686,40 @@
         <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO17" t="n">
         <v>1.17</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.34</v>
@@ -7731,85 +7731,85 @@
         <v>1.26</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH17" t="n">
-        <v>73.3</v>
+        <v>73.33</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL17" t="n">
         <v>0.05</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.05</v>
+        <v>37.09</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.35</v>
+        <v>11.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>12.7</v>
+        <v>13.05</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.8</v>
+        <v>51.05</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="DY17" t="n">
-        <v>7</v>
+        <v>6.76</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.25</v>
+        <v>15.38</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="18">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -7831,49 +7831,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H18" t="n">
-        <v>78.44</v>
+        <v>79.2</v>
       </c>
       <c r="I18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>37.78</v>
+        <v>37.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>10.56</v>
+        <v>10.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.78</v>
+        <v>12.2</v>
       </c>
       <c r="R18" t="n">
-        <v>10.44</v>
+        <v>9.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7885,28 +7885,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47.67</v>
+        <v>47.3</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.89</v>
+        <v>7.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.22</v>
+        <v>21.6</v>
       </c>
       <c r="AD18" t="n">
         <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AF18" t="n">
         <v>0.18</v>
@@ -7990,70 +7990,70 @@
         <v>2.27</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.25</v>
+        <v>10.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="BR18" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS18" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU18" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW18" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>5.54</v>
+        <v>5.39</v>
       </c>
       <c r="BZ18" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="CC18" t="n">
         <v>4.84</v>
@@ -8062,10 +8062,10 @@
         <v>5.12</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG18" t="n">
         <v>2.84</v>
@@ -8083,7 +8083,7 @@
         <v>1.51</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM18" t="n">
         <v>2.16</v>
@@ -8095,22 +8095,22 @@
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ18" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CV18" t="n">
         <v>1.94</v>
@@ -8122,10 +8122,10 @@
         <v>1.69</v>
       </c>
       <c r="CY18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA18" t="n">
         <v>1.77</v>
@@ -8134,85 +8134,85 @@
         <v>1.28</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DG18" t="n">
         <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>68.7</v>
+        <v>69.53</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK18" t="n">
         <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>32.85</v>
+        <v>33.1</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.75</v>
+        <v>10.76</v>
       </c>
       <c r="DQ18" t="n">
-        <v>12.05</v>
+        <v>12.24</v>
       </c>
       <c r="DR18" t="n">
-        <v>9.65</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>46.8</v>
+        <v>46.67</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX18" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="DZ18" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.7</v>
+        <v>19.53</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="19">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -8312,139 +8312,139 @@
         <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
-        <v>66.78</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.11</v>
+        <v>32.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11.56</v>
+        <v>11.7</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.78</v>
+        <v>13.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.56</v>
+        <v>8.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>54.67</v>
+        <v>52.9</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.109999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>19.44</v>
+        <v>19</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BH19" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="BR19" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU19" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY19" t="n">
         <v>3.06</v>
@@ -8453,55 +8453,55 @@
         <v>3.3</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="CE19" t="n">
         <v>1.3</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH19" t="n">
         <v>1.48</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP19" t="n">
         <v>1.71</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
@@ -8510,13 +8510,13 @@
         <v>2.62</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CU19" t="n">
         <v>1.49</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW19" t="n">
         <v>1.75</v>
@@ -8543,73 +8543,73 @@
         <v>2.8</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DH19" t="n">
-        <v>67.3</v>
+        <v>67.81</v>
       </c>
       <c r="DI19" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>32.9</v>
+        <v>32.62</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DP19" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.7</v>
+        <v>12.91</v>
       </c>
       <c r="DR19" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.95</v>
+        <v>52.19</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.15</v>
+        <v>12</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.8</v>
+        <v>7.53</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.35</v>
+        <v>4.47</v>
       </c>
       <c r="EA19" t="n">
-        <v>18.95</v>
+        <v>18.76</v>
       </c>
       <c r="EB19" t="n">
         <v>1.25</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.27</v>
@@ -1469,139 +1469,139 @@
         <v>2.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>84.33</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.44</v>
+        <v>48.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.22</v>
+        <v>14.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.33</v>
+        <v>49.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.22</v>
+        <v>12.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.56</v>
+        <v>17.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="BR2" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
         <v>1.82</v>
@@ -1610,55 +1610,55 @@
         <v>1.77</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH2" t="n">
         <v>1.33</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="CP2" t="n">
         <v>1.56</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
@@ -1700,79 +1700,79 @@
         <v>2.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="DH2" t="n">
-        <v>85.2</v>
+        <v>84</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.25</v>
+        <v>6.19</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.75</v>
+        <v>49.29</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.95</v>
+        <v>14.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.55</v>
+        <v>6.53</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.85</v>
+        <v>49.47</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.4</v>
+        <v>13.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.1</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.95</v>
+        <v>16.14</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="3">
@@ -2070,7 +2070,7 @@
         <v>2.56</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU3" t="n">
         <v>1.55</v>
@@ -2085,13 +2085,13 @@
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>84.59999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>47.4</v>
+        <v>46.82</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="P4" t="n">
-        <v>13.1</v>
+        <v>12.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.7</v>
+        <v>15.82</v>
       </c>
       <c r="R4" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.4</v>
+        <v>49.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.5</v>
+        <v>13.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.9</v>
+        <v>17.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,70 +2356,70 @@
         <v>2.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>11.65</v>
+        <v>11.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BR4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW4" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.89</v>
+        <v>3.31</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.91</v>
+        <v>3.36</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.84</v>
+        <v>4.91</v>
       </c>
       <c r="CC4" t="n">
         <v>5.32</v>
@@ -2431,40 +2431,40 @@
         <v>1.19</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
         <v>2.3</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK4" t="n">
         <v>1.32</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="CO4" t="n">
         <v>1.1</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
@@ -2488,97 +2488,97 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.54</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DH4" t="n">
-        <v>75.65000000000001</v>
+        <v>76.14</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.4</v>
+        <v>5.52</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.7</v>
+        <v>43.57</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.4</v>
+        <v>12.29</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.95</v>
+        <v>13.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.25</v>
+        <v>44.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.85</v>
+        <v>11.81</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.55</v>
+        <v>7.53</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.9</v>
+        <v>17.76</v>
       </c>
       <c r="EB4" t="n">
         <v>1.36</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>53.6</v>
+        <v>55.82</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.6</v>
+        <v>24.82</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44</v>
+        <v>43.36</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.6</v>
+        <v>16.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.65</v>
+        <v>10.52</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS5" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY5" t="n">
         <v>2.46</v>
@@ -2819,16 +2819,16 @@
         <v>2.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.24</v>
+        <v>5.42</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.22</v>
+        <v>6.19</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
@@ -2837,46 +2837,46 @@
         <v>2.54</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL5" t="n">
         <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CO5" t="n">
         <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
         <v>1.44</v>
@@ -2891,64 +2891,64 @@
         <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DH5" t="n">
-        <v>67.84999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.45</v>
+        <v>28.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.7</v>
+        <v>7.95</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>46.4</v>
+        <v>45.95</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.2</v>
+        <v>10.24</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.15</v>
+        <v>7.19</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.5</v>
+        <v>18.19</v>
       </c>
       <c r="EB5" t="n">
         <v>1.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
@@ -3294,13 +3294,13 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
@@ -3309,7 +3309,7 @@
         <v>1.81</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="H7" t="n">
-        <v>98.8</v>
+        <v>95.27</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>62.9</v>
+        <v>61.91</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>7.2</v>
+        <v>7.09</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.3</v>
+        <v>61.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.1</v>
+        <v>15.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.4</v>
+        <v>17.09</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3565,70 +3565,70 @@
         <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW7" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>1.35</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CA7" t="n">
-        <v>6.26</v>
+        <v>6.33</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.96</v>
+        <v>7.06</v>
       </c>
       <c r="CC7" t="n">
         <v>1.42</v>
@@ -3637,19 +3637,19 @@
         <v>1.48</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.73</v>
@@ -3661,7 +3661,7 @@
         <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
         <v>2.09</v>
@@ -3673,7 +3673,7 @@
         <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
@@ -3684,10 +3684,10 @@
         <v>1.87</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX7" t="n">
         <v>1.49</v>
@@ -3714,76 +3714,76 @@
         <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="DG7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>95</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DO7" t="n">
         <v>3.05</v>
       </c>
-      <c r="DH7" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>2.95</v>
-      </c>
       <c r="DP7" t="n">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.85</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.8</v>
+        <v>6.76</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.8</v>
+        <v>59.76</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.95</v>
+        <v>16</v>
       </c>
       <c r="DY7" t="n">
         <v>9</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="EB7" t="n">
         <v>1.91</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.27</v>
@@ -3886,136 +3886,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>65.33</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.33</v>
+        <v>37.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.22</v>
+        <v>11.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.109999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>53.33</v>
+        <v>52.1</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.44</v>
+        <v>10.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.89</v>
+        <v>6.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>17</v>
+        <v>16.3</v>
       </c>
       <c r="BE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.14</v>
       </c>
-      <c r="BF8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
         <v>3.39</v>
@@ -4024,28 +4024,28 @@
         <v>3.47</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.1</v>
+        <v>4.34</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.65</v>
+        <v>4.58</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.94</v>
+        <v>4.91</v>
       </c>
       <c r="CE8" t="n">
         <v>1.1</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
         <v>2.06</v>
@@ -4054,139 +4054,139 @@
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="CT8" t="n">
         <v>3.07</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX8" t="n">
         <v>1.62</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.28</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>66.05</v>
+        <v>65.81</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>33.8</v>
+        <v>34.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO8" t="n">
         <v>1.95</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.65</v>
+        <v>11.28</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.6</v>
+        <v>9.76</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.45</v>
+        <v>49.05</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.45</v>
+        <v>5.57</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="H9" t="n">
-        <v>94.7</v>
+        <v>94.73</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="K9" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>55.4</v>
+        <v>57.27</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>63.1</v>
+        <v>63.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.7</v>
+        <v>14.73</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="AC9" t="n">
         <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4370,67 +4370,67 @@
         <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.6</v>
+        <v>10.48</v>
       </c>
       <c r="BI9" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM9" t="n">
         <v>0.9</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CA9" t="n">
         <v>4.9</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="CC9" t="n">
         <v>1.92</v>
@@ -4442,154 +4442,154 @@
         <v>1.21</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK9" t="n">
         <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO9" t="n">
         <v>1.12</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
         <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.65000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>55.55</v>
+        <v>56.52</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.65</v>
+        <v>11.76</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>61.55</v>
+        <v>61.62</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.35</v>
+        <v>14.38</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.85</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.7</v>
+        <v>17.76</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4689,139 +4689,139 @@
         <v>1.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AI10" t="n">
-        <v>66.73</v>
+        <v>68.92</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN10" t="n">
-        <v>33.27</v>
+        <v>34.92</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>12.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.91</v>
+        <v>12.17</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.64</v>
+        <v>49.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.82</v>
+        <v>15.42</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.3</v>
+        <v>10.19</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="BJ10" t="n">
         <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM10" t="n">
         <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.65</v>
+        <v>4.52</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT10" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>2.45</v>
@@ -4830,76 +4830,76 @@
         <v>2.41</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.63</v>
+        <v>4.4</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.6</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL10" t="n">
         <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
         <v>1.66</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
         <v>1.87</v>
@@ -4914,85 +4914,85 @@
         <v>1.22</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="DG10" t="n">
         <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>72.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.3</v>
+        <v>38.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.85</v>
+        <v>11.52</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12</v>
+        <v>12.14</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.45</v>
+        <v>51.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.55</v>
+        <v>12.38</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.8</v>
+        <v>4.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.3</v>
+        <v>15.62</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="11">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.27</v>
@@ -5092,139 +5092,139 @@
         <v>1.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>82</v>
+        <v>85.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.89</v>
+        <v>44.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.78</v>
+        <v>11.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.78</v>
+        <v>49.9</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.44</v>
+        <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.33</v>
+        <v>17.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BG11" t="n">
         <v>3.05</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI11" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM11" t="n">
         <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY11" t="n">
         <v>4.6</v>
@@ -5233,16 +5233,16 @@
         <v>4.75</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.73</v>
+        <v>4.48</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.21</v>
+        <v>4.9</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
@@ -5266,10 +5266,10 @@
         <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5284,19 +5284,19 @@
         <v>2.78</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CU11" t="n">
         <v>1.57</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CW11" t="n">
         <v>1.73</v>
@@ -5305,97 +5305,97 @@
         <v>1.59</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.36</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DH11" t="n">
-        <v>73.59999999999999</v>
+        <v>75.81</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>38.15</v>
+        <v>39.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.7</v>
+        <v>10.66</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.05</v>
+        <v>46.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>9.65</v>
+        <v>10.19</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.3</v>
+        <v>6.66</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.35</v>
+        <v>3.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.55</v>
+        <v>17.76</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
@@ -5405,94 +5405,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>34.11</v>
+        <v>33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="P12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.22</v>
+        <v>47.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.67</v>
+        <v>7.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="AD12" t="n">
         <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5579,67 +5579,67 @@
         <v>2.95</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.05</v>
+        <v>10.95</v>
       </c>
       <c r="BI12" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
         <v>1.05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU12" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX12" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.64</v>
+        <v>6.27</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.72</v>
+        <v>6.37</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.52</v>
+        <v>4.47</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="CC12" t="n">
         <v>5.8</v>
@@ -5648,19 +5648,19 @@
         <v>5.81</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
         <v>2.43</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CH12" t="n">
         <v>1.52</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.75</v>
@@ -5669,46 +5669,46 @@
         <v>1.5</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU12" t="n">
         <v>1.57</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX12" t="n">
         <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.36</v>
@@ -5720,85 +5720,85 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD12" t="n">
         <v>2.72</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH12" t="n">
-        <v>71.25</v>
+        <v>71.38</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.3</v>
+        <v>34.71</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.95</v>
+        <v>12.81</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.75</v>
+        <v>8.76</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.4</v>
+        <v>47.05</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.65</v>
+        <v>9.57</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.6</v>
+        <v>6.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.15</v>
+        <v>16.14</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5898,139 +5898,139 @@
         <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" t="n">
-        <v>103.3</v>
+        <v>100.27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK13" t="n">
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AN13" t="n">
-        <v>67.2</v>
+        <v>65.55</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.4</v>
+        <v>10.82</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.4</v>
+        <v>5.73</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>60.2</v>
+        <v>59.18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>18.6</v>
+        <v>18.36</v>
       </c>
       <c r="BB13" t="n">
-        <v>12.6</v>
+        <v>12.55</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>15.91</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.55</v>
+        <v>10.62</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BM13" t="n">
         <v>1</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.7</v>
+        <v>5.76</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT13" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV13" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY13" t="n">
         <v>1.25</v>
@@ -6039,34 +6039,34 @@
         <v>1.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="CC13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CD13" t="n">
         <v>1.48</v>
       </c>
-      <c r="CD13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="CE13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="CF13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.98</v>
+        <v>4.01</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK13" t="n">
         <v>1.29</v>
@@ -6075,10 +6075,10 @@
         <v>1.63</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CO13" t="n">
         <v>0.97</v>
@@ -6087,7 +6087,7 @@
         <v>1.32</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
@@ -6098,22 +6098,22 @@
         <v>1.96</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX13" t="n">
         <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DB13" t="n">
         <v>1.12</v>
@@ -6122,82 +6122,82 @@
         <v>1.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.8</v>
+        <v>105.05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ13" t="n">
         <v>2.1</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.45</v>
+        <v>7.29</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="DM13" t="n">
-        <v>67.40000000000001</v>
+        <v>66.53</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.45</v>
+        <v>11.62</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>60.15</v>
+        <v>59.62</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>18.7</v>
+        <v>18.57</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.15</v>
+        <v>16.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14">
@@ -6219,7 +6219,7 @@
         <v>0.36</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G14" t="n">
         <v>4.55</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="K14" t="n">
         <v>8.91</v>
@@ -6273,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>60.45</v>
+        <v>60.36</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AF14" t="n">
         <v>0.2</v>
@@ -6492,7 +6492,7 @@
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT14" t="n">
         <v>3.12</v>
@@ -6504,13 +6504,13 @@
         <v>2.23</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.46</v>
@@ -6525,13 +6525,13 @@
         <v>1.6</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="DE14" t="n">
         <v>0.28</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="DG14" t="n">
         <v>3.43</v>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DK14" t="n">
         <v>7.1</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.14</v>
+        <v>59.09</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>1.57</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="15">
@@ -6610,58 +6610,58 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="H15" t="n">
-        <v>68.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>34.2</v>
+        <v>34.91</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>13.8</v>
+        <v>13.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="R15" t="n">
-        <v>6.7</v>
+        <v>7.09</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -6676,28 +6676,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.1</v>
+        <v>42.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>18.6</v>
+        <v>18.27</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>1.7</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.35</v>
+        <v>11.19</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.29</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU15" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.59</v>
+        <v>4.53</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.42</v>
+        <v>5.33</v>
       </c>
       <c r="CC15" t="n">
         <v>7.59</v>
@@ -6853,28 +6853,28 @@
         <v>10.04</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM15" t="n">
         <v>2.21</v>
@@ -6883,40 +6883,40 @@
         <v>1.74</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CP15" t="n">
         <v>1.72</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CX15" t="n">
         <v>1.58</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>1.59</v>
       </c>
       <c r="CY15" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA15" t="n">
         <v>1.96</v>
@@ -6928,49 +6928,49 @@
         <v>1.75</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE15" t="n">
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.25</v>
+        <v>67.33</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.15</v>
+        <v>34.52</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.6</v>
+        <v>13.28</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.05</v>
+        <v>7.24</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>40.85</v>
+        <v>41</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX15" t="n">
         <v>11</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.95</v>
+        <v>16.86</v>
       </c>
       <c r="EB15" t="n">
         <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -7013,94 +7013,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="H16" t="n">
-        <v>63.22</v>
+        <v>62.1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>37.89</v>
+        <v>37.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="P16" t="n">
-        <v>11.44</v>
+        <v>11.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="R16" t="n">
-        <v>5.89</v>
+        <v>6.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.44</v>
+        <v>51.2</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.44</v>
+        <v>14.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.67</v>
+        <v>9.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.78</v>
+        <v>5.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>21</v>
+        <v>20.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7184,64 +7184,64 @@
         <v>2.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="BR16" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="CA16" t="n">
         <v>4</v>
@@ -7256,25 +7256,25 @@
         <v>3.98</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG16" t="n">
         <v>3.04</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.68</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL16" t="n">
         <v>1.83</v>
@@ -7286,13 +7286,13 @@
         <v>1.84</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP16" t="n">
         <v>1.7</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CR16" t="n">
         <v>1.37</v>
@@ -7337,76 +7337,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DH16" t="n">
-        <v>70.25</v>
+        <v>69.38</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.15</v>
+        <v>5.09</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.95</v>
+        <v>38.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.1</v>
+        <v>11.14</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.6</v>
+        <v>11.76</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.35</v>
+        <v>46.9</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.55</v>
+        <v>12.24</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.5</v>
+        <v>18.19</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="17">
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
@@ -8507,7 +8507,7 @@
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CT19" t="n">
         <v>3.13</v>
@@ -8525,19 +8525,19 @@
         <v>1.58</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.36</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB19" t="n">
         <v>1.23</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD19" t="n">
         <v>2.8</v>
@@ -8594,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>52.19</v>
+        <v>52.24</v>
       </c>
       <c r="DW19" t="n">
         <v>0.09</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -2470,13 +2470,13 @@
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CT4" t="n">
         <v>3.2</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CV4" t="n">
         <v>2.34</v>
@@ -6091,11 +6091,11 @@
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CV13" t="n">
         <v>2.23</v>

--- a/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Saudi_Pro_League_2025-2026.xlsx
@@ -1379,304 +1379,304 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
         <v>11</v>
       </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="G2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="H2" t="n">
+        <v>84.33</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M2" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>85.91</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="AI2" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0.18</v>
       </c>
-      <c r="M2" t="n">
-        <v>50</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P2" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="AW2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>65.22</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CQ2" t="n">
         <v>2.27</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>90.48</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>2.29</v>
       </c>
       <c r="CR2" t="n">
         <v>1.32</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CT2" t="n">
         <v>3.25</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CX2" t="n">
         <v>1.54</v>
@@ -1685,7 +1685,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA2" t="n">
         <v>1.91</v>
@@ -1700,79 +1700,79 @@
         <v>2.46</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
         <v>2.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="DH2" t="n">
-        <v>84</v>
+        <v>81.61</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.19</v>
+        <v>6.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.29</v>
+        <v>55.96</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="DP2" t="n">
-        <v>14.72</v>
+        <v>14.78</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.81</v>
+        <v>10.78</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.53</v>
+        <v>6.39</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>49.47</v>
+        <v>49.44</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.47</v>
+        <v>13.09</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.050000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.14</v>
+        <v>16.22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
         <v>11</v>
       </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="H3" t="n">
-        <v>59.55</v>
+        <v>58.25</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>28.09</v>
+        <v>27.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.09</v>
+        <v>11.58</v>
       </c>
       <c r="R3" t="n">
-        <v>9.73</v>
+        <v>10.25</v>
       </c>
       <c r="S3" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,76 +1848,76 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.45</v>
+        <v>43.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.82</v>
+        <v>9.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.91</v>
+        <v>19.33</v>
       </c>
       <c r="AD3" t="n">
         <v>0.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AI3" t="n">
-        <v>55.8</v>
+        <v>57.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AL3" t="n">
         <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>24.1</v>
+        <v>25.82</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.1</v>
+        <v>13.55</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.1</v>
+        <v>9.27</v>
       </c>
       <c r="AT3" t="n">
         <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,220 +1929,220 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>37</v>
+        <v>38.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.9</v>
+        <v>7.18</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>14.8</v>
+        <v>14.73</v>
       </c>
       <c r="BE3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0.78</v>
       </c>
-      <c r="BF3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.76</v>
+        <v>4.48</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>73.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.38</v>
+        <v>56.52</v>
       </c>
       <c r="BU3" t="n">
-        <v>28.57</v>
+        <v>30.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>19.05</v>
+        <v>21.74</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.52</v>
+        <v>13.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.38</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.31</v>
+        <v>4.83</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.7</v>
+        <v>5.19</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="CC3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="CD3" t="n">
-        <v>9.380000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI3" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK3" t="n">
         <v>1.42</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CO3" t="n">
         <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="DH3" t="n">
-        <v>57.76</v>
+        <v>58</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.86</v>
+        <v>3.69</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>26.19</v>
+        <v>26.83</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.66</v>
+        <v>9.48</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.05</v>
+        <v>12.52</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.43</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>40.9</v>
+        <v>41.13</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX3" t="n">
         <v>8.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.48</v>
+        <v>17.13</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4">
@@ -2185,298 +2185,298 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
         <v>11</v>
       </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="H4" t="n">
-        <v>84.73</v>
+        <v>84.17</v>
       </c>
       <c r="I4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M4" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>67.45</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.09</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="AK4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41.45</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0.18</v>
       </c>
-      <c r="M4" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.82</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="AW4" t="n">
         <v>0.18</v>
       </c>
-      <c r="V4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>49.55</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL4" t="n">
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="CB4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>80.95</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>4.91</v>
-      </c>
       <c r="CC4" t="n">
-        <v>5.32</v>
+        <v>5.07</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.85</v>
+        <v>5.54</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.33</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV4" t="n">
         <v>2.34</v>
@@ -2488,97 +2488,97 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.54</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DH4" t="n">
-        <v>76.14</v>
+        <v>76.17</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.52</v>
+        <v>5.65</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.57</v>
+        <v>44.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.29</v>
+        <v>12.44</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.57</v>
+        <v>45.05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.81</v>
+        <v>12.57</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.53</v>
+        <v>7.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.29</v>
+        <v>4.74</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.76</v>
+        <v>17.39</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,49 +2681,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>55.82</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>24.82</v>
+        <v>25.42</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.09</v>
+        <v>10.42</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>43.36</v>
+        <v>42.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.91</v>
+        <v>9.58</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.18</v>
+        <v>6.83</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.18</v>
+        <v>16.67</v>
       </c>
       <c r="BE5" t="n">
         <v>0.91</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.52</v>
+        <v>10.45</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>2.46</v>
@@ -2819,43 +2819,43 @@
         <v>2.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.42</v>
+        <v>5.22</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.19</v>
+        <v>5.99</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN5" t="n">
         <v>1.74</v>
@@ -2867,13 +2867,13 @@
         <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CT5" t="n">
         <v>2.85</v>
@@ -2894,61 +2894,61 @@
         <v>1.93</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
         <v>1.9</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC5" t="n">
         <v>2.02</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="DH5" t="n">
-        <v>68.33</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>28.86</v>
+        <v>29</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.19</v>
+        <v>10.37</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.9</v>
+        <v>10.86</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.95</v>
+        <v>8.09</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>45.95</v>
+        <v>45.46</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.24</v>
+        <v>10.04</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.19</v>
+        <v>7</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.19</v>
+        <v>18.37</v>
       </c>
       <c r="EB5" t="n">
         <v>1.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>63.73</v>
+        <v>65.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.82</v>
+        <v>31.42</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>12.27</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AV6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.82</v>
+        <v>43.83</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.27</v>
+        <v>19.58</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.380000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BN6" t="n">
         <v>1.95</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="BR6" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY6" t="n">
         <v>5.05</v>
@@ -3222,70 +3222,70 @@
         <v>4.85</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.49</v>
+        <v>4.87</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.01</v>
+        <v>5.84</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.15</v>
+        <v>6.27</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.18</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.75</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
         <v>3.01</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW6" t="n">
         <v>1.8</v>
@@ -3294,97 +3294,97 @@
         <v>1.58</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.34</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DH6" t="n">
-        <v>75</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.43</v>
+        <v>38.87</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.81</v>
+        <v>12.54</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.43</v>
+        <v>10.55</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.53</v>
+        <v>7.45</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.67</v>
+        <v>46.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.86</v>
+        <v>10.64</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.95</v>
+        <v>6.82</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.52</v>
+        <v>18.23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>95.27</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="L7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>61.91</v>
+        <v>65.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="R7" t="n">
-        <v>7.09</v>
+        <v>6.83</v>
       </c>
       <c r="S7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.09</v>
+        <v>61.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.27</v>
+        <v>15.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.82</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.09</v>
+        <v>16.92</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3565,70 +3565,70 @@
         <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.949999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU7" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CA7" t="n">
-        <v>6.33</v>
+        <v>6.26</v>
       </c>
       <c r="CB7" t="n">
-        <v>7.06</v>
+        <v>6.97</v>
       </c>
       <c r="CC7" t="n">
         <v>1.42</v>
@@ -3637,22 +3637,22 @@
         <v>1.48</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CF7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CG7" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK7" t="n">
         <v>1.39</v>
@@ -3661,7 +3661,7 @@
         <v>1.74</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN7" t="n">
         <v>2.09</v>
@@ -3673,15 +3673,15 @@
         <v>1.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CV7" t="n">
         <v>2.21</v>
@@ -3693,7 +3693,7 @@
         <v>1.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.57</v>
@@ -3705,85 +3705,85 @@
         <v>1.12</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DH7" t="n">
-        <v>95</v>
+        <v>97.59</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.57</v>
+        <v>6.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM7" t="n">
-        <v>57.62</v>
+        <v>59.68</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DO7" t="n">
         <v>3.05</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.48</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.76</v>
+        <v>6.63</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>59.76</v>
+        <v>59.87</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>16</v>
+        <v>16.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="DZ7" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="EA7" t="n">
-        <v>16</v>
+        <v>15.96</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="8">
@@ -3793,301 +3793,301 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
         <v>11</v>
       </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H8" t="n">
-        <v>66.64</v>
+        <v>67</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="K8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>30.91</v>
+        <v>31.58</v>
       </c>
       <c r="N8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.64</v>
       </c>
-      <c r="P8" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="R8" t="n">
-        <v>10</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="AH8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>1.36</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AV8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>0.09</v>
       </c>
-      <c r="V8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>46.27</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
       <c r="BA8" t="n">
-        <v>10.4</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>3.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.3</v>
+        <v>16.36</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.57</v>
+        <v>9.35</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.76</v>
+        <v>0.91</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="BM8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.48</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.95</v>
+        <v>82.61</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>60.87</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.1</v>
+        <v>43.48</v>
       </c>
       <c r="BV8" t="n">
-        <v>19.05</v>
+        <v>21.74</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.38</v>
+        <v>52.17</v>
       </c>
       <c r="BY8" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.58</v>
+        <v>4.89</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.91</v>
+        <v>5.22</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CF8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CI8" t="n">
         <v>2.07</v>
       </c>
-      <c r="CG8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK8" t="n">
         <v>1.32</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CU8" t="n">
         <v>1.58</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
         <v>1.72</v>
@@ -4108,85 +4108,85 @@
         <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="DH8" t="n">
-        <v>65.81</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="DM8" t="n">
-        <v>34.05</v>
+        <v>33.56</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.28</v>
+        <v>11.04</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.28</v>
+        <v>10.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>9.76</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.05</v>
+        <v>48.7</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="DY8" t="n">
         <v>5.57</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>15</v>
+        <v>15.48</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4286,139 +4286,139 @@
         <v>1.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>94.59999999999999</v>
+        <v>92.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.1</v>
+        <v>6.73</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>55.7</v>
+        <v>52.73</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.7</v>
+        <v>10.55</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>6.82</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA9" t="n">
-        <v>14</v>
+        <v>13.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.5</v>
+        <v>8.09</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.48</v>
+        <v>10.32</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.81</v>
+        <v>4.68</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
         <v>1.9</v>
@@ -4427,16 +4427,16 @@
         <v>1.91</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="CE9" t="n">
         <v>1.21</v>
@@ -4451,7 +4451,7 @@
         <v>1.65</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.62</v>
@@ -4460,7 +4460,7 @@
         <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM9" t="n">
         <v>2.58</v>
@@ -4475,7 +4475,7 @@
         <v>1.46</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CR9" t="n">
         <v>1.33</v>
@@ -4505,7 +4505,7 @@
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB9" t="n">
         <v>1.16</v>
@@ -4517,46 +4517,46 @@
         <v>2.25</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="DH9" t="n">
-        <v>94.67</v>
+        <v>93.64</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.24</v>
+        <v>7.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>56.52</v>
+        <v>55</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.76</v>
+        <v>11.64</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.859999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.1</v>
+        <v>6.32</v>
       </c>
       <c r="DS9" t="n">
         <v>0.14</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>61.62</v>
+        <v>60.54</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.38</v>
+        <v>14.04</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.76</v>
+        <v>17.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>78.78</v>
+        <v>77.7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>42.22</v>
+        <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>10.44</v>
+        <v>10.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="R10" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54.89</v>
+        <v>53.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.44</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.67</v>
+        <v>7.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.78</v>
+        <v>4.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.89</v>
+        <v>16.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4770,70 +4770,70 @@
         <v>2.08</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.19</v>
+        <v>10.23</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="BJ10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.05</v>
       </c>
       <c r="BM10" t="n">
         <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="BQ10" t="n">
         <v>4.14</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU10" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CC10" t="n">
         <v>4.4</v>
@@ -4848,13 +4848,13 @@
         <v>2.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CH10" t="n">
         <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.6</v>
@@ -4878,7 +4878,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4893,13 +4893,13 @@
         <v>1.53</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
         <v>1.66</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY10" t="n">
         <v>1.87</v>
@@ -4917,79 +4917,79 @@
         <v>1.69</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DH10" t="n">
-        <v>73.15000000000001</v>
+        <v>72.91</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.05</v>
+        <v>38.14</v>
       </c>
       <c r="DN10" t="n">
         <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.52</v>
+        <v>11.45</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.14</v>
+        <v>12.18</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.33</v>
+        <v>8.41</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.67</v>
+        <v>51.09</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.38</v>
+        <v>11.95</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.67</v>
+        <v>7.46</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.62</v>
+        <v>15.77</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
         <v>1.95</v>
@@ -5002,94 +5002,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G11" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>66.73</v>
+        <v>66.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="K11" t="n">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="M11" t="n">
-        <v>35.09</v>
+        <v>35.58</v>
       </c>
       <c r="N11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="P11" t="n">
-        <v>11.45</v>
+        <v>11.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.55</v>
+        <v>13.5</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>43.82</v>
+        <v>45.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5173,70 +5173,70 @@
         <v>1.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.24</v>
+        <v>5.27</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.6</v>
+        <v>4.38</v>
       </c>
       <c r="BZ11" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.47</v>
+        <v>4.42</v>
       </c>
       <c r="CC11" t="n">
         <v>4.48</v>
@@ -5248,10 +5248,10 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
@@ -5266,10 +5266,10 @@
         <v>1.5</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5281,19 +5281,19 @@
         <v>1.73</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV11" t="n">
         <v>2.13</v>
@@ -5302,67 +5302,67 @@
         <v>1.73</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
         <v>3.02</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
         <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="DH11" t="n">
-        <v>75.81</v>
+        <v>75.37</v>
       </c>
       <c r="DI11" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.09</v>
+        <v>4.27</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.38</v>
+        <v>39.45</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.66</v>
+        <v>10.91</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.62</v>
+        <v>12.64</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.140000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DS11" t="n">
         <v>0.14</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.72</v>
+        <v>47.32</v>
       </c>
       <c r="DW11" t="n">
         <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.19</v>
+        <v>10.32</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.66</v>
+        <v>6.73</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="EA11" t="n">
-        <v>17.76</v>
+        <v>17.91</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.1</v>
@@ -5495,139 +5495,139 @@
         <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>74.73</v>
+        <v>73.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.27</v>
+        <v>37</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.82</v>
+        <v>9.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.64</v>
+        <v>12.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.73</v>
+        <v>46.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>15.45</v>
+        <v>15.92</v>
       </c>
       <c r="BE12" t="n">
         <v>1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.95</v>
+        <v>11.14</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BO12" t="n">
         <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.86</v>
+        <v>5.14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU12" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW12" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>6.27</v>
@@ -5636,73 +5636,73 @@
         <v>6.37</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.92</v>
+        <v>5.25</v>
       </c>
       <c r="CC12" t="n">
-        <v>5.8</v>
+        <v>6.73</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.81</v>
+        <v>6.94</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL12" t="n">
         <v>1.96</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CT12" t="n">
         <v>3.12</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CX12" t="n">
         <v>1.57</v>
@@ -5720,52 +5720,52 @@
         <v>1.22</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="DE12" t="n">
         <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="DH12" t="n">
-        <v>71.38</v>
+        <v>70.86</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.71</v>
+        <v>35.18</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DP12" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.81</v>
+        <v>12.63</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.76</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.09</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.05</v>
+        <v>46.82</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.57</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.43</v>
+        <v>6.32</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.14</v>
+        <v>16.37</v>
       </c>
       <c r="EB12" t="n">
         <v>1.05</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>110.3</v>
+        <v>108.45</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K13" t="n">
-        <v>8.1</v>
+        <v>7.64</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M13" t="n">
-        <v>67.59999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O13" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>12.5</v>
+        <v>12.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.5</v>
+        <v>11.09</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>60.1</v>
+        <v>59.73</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>18.8</v>
+        <v>18.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>11.2</v>
+        <v>10.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.3</v>
+        <v>17.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF13" t="n">
         <v>0.27</v>
@@ -5979,70 +5979,70 @@
         <v>1.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.62</v>
+        <v>10.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BM13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.76</v>
+        <v>5.64</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV13" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.26</v>
+        <v>6.48</v>
       </c>
       <c r="CB13" t="n">
-        <v>7.57</v>
+        <v>7.81</v>
       </c>
       <c r="CC13" t="n">
         <v>1.47</v>
@@ -6057,51 +6057,51 @@
         <v>1.74</v>
       </c>
       <c r="CG13" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL13" t="n">
         <v>1.63</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CQ13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CR13" t="inlineStr"/>
       <c r="CS13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CT13" t="inlineStr"/>
       <c r="CU13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX13" t="n">
         <v>1.55</v>
@@ -6113,7 +6113,7 @@
         <v>2.42</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB13" t="n">
         <v>1.12</v>
@@ -6122,76 +6122,76 @@
         <v>1.3</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.05</v>
+        <v>104.36</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK13" t="n">
-        <v>7.29</v>
+        <v>7.09</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM13" t="n">
-        <v>66.53</v>
+        <v>66.14</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.62</v>
+        <v>11.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="DR13" t="n">
         <v>4.91</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>59.62</v>
+        <v>59.46</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>18.57</v>
+        <v>18.45</v>
       </c>
       <c r="DY13" t="n">
-        <v>11.91</v>
+        <v>11.55</v>
       </c>
       <c r="DZ13" t="n">
-        <v>6.67</v>
+        <v>6.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.57</v>
+        <v>16.73</v>
       </c>
       <c r="EB13" t="n">
         <v>2.12</v>
@@ -6207,304 +6207,304 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
         <v>11</v>
       </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
       <c r="E14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="H14" t="n">
-        <v>93.64</v>
+        <v>92.08</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="K14" t="n">
-        <v>8.91</v>
+        <v>8.42</v>
       </c>
       <c r="L14" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>57.64</v>
+        <v>57.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O14" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="P14" t="n">
-        <v>12.82</v>
+        <v>12.92</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="R14" t="n">
-        <v>5.36</v>
+        <v>5.17</v>
       </c>
       <c r="S14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="T14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>108.91</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU14" t="n">
         <v>2.27</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>60.36</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>111.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.7</v>
+        <v>58.09</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.4</v>
+        <v>13.27</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.1</v>
+        <v>14.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.57</v>
+        <v>10.13</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
       <c r="BK14" t="n">
         <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.24</v>
+        <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.29</v>
+        <v>5.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>80.95</v>
+        <v>82.61</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.62</v>
+        <v>52.17</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.29</v>
+        <v>17.39</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.76</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX14" t="n">
-        <v>61.9</v>
+        <v>60.87</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.77</v>
+        <v>4.89</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="CD14" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CR14" t="n">
         <v>1.34</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CT14" t="n">
         <v>3.12</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
@@ -6522,85 +6522,85 @@
         <v>1.18</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="DH14" t="n">
-        <v>102.14</v>
+        <v>100.13</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.1</v>
+        <v>6.91</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>56.29</v>
+        <v>56.35</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.48</v>
+        <v>12.65</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.9</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.95</v>
+        <v>6.61</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.09</v>
+        <v>59.31</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.19</v>
+        <v>13.95</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.52</v>
+        <v>8.91</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.67</v>
+        <v>5.05</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.57</v>
+        <v>17.48</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.09</v>
@@ -6700,139 +6700,139 @@
         <v>2.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AI15" t="n">
-        <v>64.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>34.1</v>
+        <v>35.17</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.4</v>
+        <v>12.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.2</v>
+        <v>11.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.4</v>
+        <v>7.08</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>39.6</v>
+        <v>40.83</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.7</v>
+        <v>11.83</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.2</v>
+        <v>7.33</v>
       </c>
       <c r="BC15" t="n">
         <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.3</v>
+        <v>17</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.19</v>
+        <v>11.26</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.29</v>
+        <v>4.35</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.67</v>
+        <v>4.87</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>85.70999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.62</v>
+        <v>47.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>34.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>13.04</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>71.43000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY15" t="n">
         <v>4.53</v>
@@ -6841,28 +6841,28 @@
         <v>4.51</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="CB15" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.59</v>
+        <v>7.08</v>
       </c>
       <c r="CD15" t="n">
-        <v>10.04</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CG15" t="n">
         <v>3.02</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
         <v>1.94</v>
@@ -6871,139 +6871,139 @@
         <v>1.78</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CP15" t="n">
         <v>1.73</v>
       </c>
-      <c r="CM15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="CQ15" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
         <v>1.58</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.36</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DB15" t="n">
         <v>1.25</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="DH15" t="n">
-        <v>67.33</v>
+        <v>66.31</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.29</v>
+        <v>5.3</v>
       </c>
       <c r="DL15" t="n">
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.52</v>
+        <v>35.05</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.28</v>
+        <v>12.69</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.43</v>
+        <v>10.52</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.24</v>
+        <v>7.08</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41</v>
+        <v>41.52</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX15" t="n">
-        <v>11</v>
+        <v>11.56</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.33</v>
+        <v>7.82</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.86</v>
+        <v>17.61</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="16">
@@ -7013,187 +7013,187 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="H16" t="n">
-        <v>62.1</v>
+        <v>59.64</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="L16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>0.5</v>
       </c>
-      <c r="M16" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>76</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>43</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.55</v>
-      </c>
       <c r="BA16" t="n">
-        <v>10.18</v>
+        <v>10.08</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.45</v>
+        <v>7.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BD16" t="n">
-        <v>16.45</v>
+        <v>15.92</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.33</v>
+        <v>10.61</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BK16" t="n">
         <v>0.57</v>
@@ -7202,115 +7202,115 @@
         <v>0.52</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.52</v>
+        <v>4.65</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.43</v>
+        <v>5.61</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>66.67</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>33.33</v>
+        <v>39.13</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>34.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.81</v>
+        <v>21.74</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>47.62</v>
+        <v>52.17</v>
       </c>
       <c r="BY16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>2.42</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="CA16" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CC16" t="n">
-        <v>4.28</v>
+        <v>4.08</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CG16" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CT16" t="n">
         <v>3.04</v>
       </c>
-      <c r="CH16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>3.03</v>
-      </c>
       <c r="CU16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7319,94 +7319,94 @@
         <v>1.84</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
         <v>1.98</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="DH16" t="n">
-        <v>69.38</v>
+        <v>67.39</v>
       </c>
       <c r="DI16" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM16" t="n">
-        <v>38.62</v>
+        <v>39.43</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.14</v>
+        <v>10.79</v>
       </c>
       <c r="DQ16" t="n">
-        <v>11.76</v>
+        <v>11.44</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.38</v>
+        <v>7.78</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>46.9</v>
+        <v>47.09</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.24</v>
+        <v>12.22</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.24</v>
+        <v>8.09</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.19</v>
+        <v>17.7</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="17">
@@ -7416,94 +7416,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="H17" t="n">
-        <v>75.8</v>
+        <v>76.27</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="K17" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M17" t="n">
-        <v>43.6</v>
+        <v>45.27</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>10.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.3</v>
+        <v>11.45</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>54.7</v>
+        <v>55.64</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>12.18</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.5</v>
+        <v>17.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7587,70 +7587,70 @@
         <v>2.36</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL17" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BO17" t="n">
         <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT17" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="CC17" t="n">
         <v>3.35</v>
@@ -7659,13 +7659,13 @@
         <v>3.71</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH17" t="n">
         <v>1.37</v>
@@ -7680,31 +7680,31 @@
         <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CM17" t="n">
         <v>2.25</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CU17" t="n">
         <v>1.45</v>
@@ -7725,91 +7725,91 @@
         <v>2.34</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DE17" t="n">
         <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH17" t="n">
-        <v>73.33</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DK17" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.09</v>
+        <v>38.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.19</v>
+        <v>11.14</v>
       </c>
       <c r="DQ17" t="n">
-        <v>13.05</v>
+        <v>13.04</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.15</v>
+        <v>8</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.05</v>
+        <v>51.68</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>11</v>
+        <v>11.13</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.76</v>
+        <v>6.95</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>15.38</v>
+        <v>15.77</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.26<